--- a/opex/OPEX_정리.xlsx
+++ b/opex/OPEX_정리.xlsx
@@ -14,7 +14,7 @@
     <sheet name="설정" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'OPEX 상세'!$A$4:$S$230</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'OPEX 상세'!$A$4:$S$254</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="151">
   <si>
     <r>
       <rPr>
@@ -810,6 +810,170 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">옥슨앤파트너스 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">스탬프</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">작업복</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안전화 등</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">): 9/3~9/22 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">작업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일자는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 기재</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">네오맥스 </t>
     </r>
     <r>
@@ -2110,6 +2274,149 @@
       </rPr>
       <t xml:space="preserve">추가 가능성</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">작업복</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구매 진행 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">작업기간 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/3~9/22) - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">선박별 스탬프</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">작업복</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안전화 등</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">사관용 작업복</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helmet Earmuffs</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Stamp (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">바뀐 선명</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Safety boots &amp; Goggle</t>
   </si>
   <si>
     <r>
@@ -4146,7 +4453,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A2:O35"/>
+  <dimension ref="A2:O36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -4228,27 +4535,27 @@
         <v>16</v>
       </c>
       <c r="C6" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B6,'OPEX 상세'!$D$5:$D$230,C$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B6,'OPEX 상세'!$D$5:$D$254,C$5)</f>
         <v>0</v>
       </c>
       <c r="D6" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B6,'OPEX 상세'!$D$5:$D$230,D$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B6,'OPEX 상세'!$D$5:$D$254,D$5)</f>
         <v>0</v>
       </c>
       <c r="E6" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B6,'OPEX 상세'!$D$5:$D$230,E$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B6,'OPEX 상세'!$D$5:$D$254,E$5)</f>
         <v>0</v>
       </c>
       <c r="F6" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B6,'OPEX 상세'!$D$5:$D$230,F$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B6,'OPEX 상세'!$D$5:$D$254,F$5)</f>
         <v>0</v>
       </c>
       <c r="G6" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B6,'OPEX 상세'!$D$5:$D$230,G$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B6,'OPEX 상세'!$D$5:$D$254,G$5)</f>
         <v>0</v>
       </c>
       <c r="H6" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B6,'OPEX 상세'!$D$5:$D$230,H$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B6,'OPEX 상세'!$D$5:$D$254,H$5)</f>
         <v>1302400</v>
       </c>
       <c r="I6" s="9" t="n">
@@ -4256,15 +4563,15 @@
         <v>1302400</v>
       </c>
       <c r="K6" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$230,'OPEX 상세'!$C$5:$C$230,$B6)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$254,'OPEX 상세'!$C$5:$C$254,$B6)</f>
         <v>1184000</v>
       </c>
       <c r="L6" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$230,'OPEX 상세'!$C$5:$C$230,$B6)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$254,'OPEX 상세'!$C$5:$C$254,$B6)</f>
         <v>118400</v>
       </c>
       <c r="M6" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$230,'OPEX 상세'!$C$5:$C$230,$B6)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$254,'OPEX 상세'!$C$5:$C$254,$B6)</f>
         <v>0</v>
       </c>
       <c r="N6" s="8" t="n">
@@ -4272,7 +4579,7 @@
         <v>1302400</v>
       </c>
       <c r="O6" s="10" t="str">
-        <f aca="false">IF(COUNTIF('OPEX 상세'!$C$5:$C$230,$B6)=0,"입력대기",IF(M6&gt;0,"VAT 추가 가능",""))</f>
+        <f aca="false">IF(COUNTIF('OPEX 상세'!$C$5:$C$254,$B6)=0,"입력대기",IF(M6&gt;0,"VAT 추가 가능",""))</f>
         <v/>
       </c>
     </row>
@@ -4284,27 +4591,27 @@
         <v>17</v>
       </c>
       <c r="C7" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B7,'OPEX 상세'!$D$5:$D$230,C$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B7,'OPEX 상세'!$D$5:$D$254,C$5)</f>
         <v>0</v>
       </c>
       <c r="D7" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B7,'OPEX 상세'!$D$5:$D$230,D$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B7,'OPEX 상세'!$D$5:$D$254,D$5)</f>
         <v>0</v>
       </c>
       <c r="E7" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B7,'OPEX 상세'!$D$5:$D$230,E$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B7,'OPEX 상세'!$D$5:$D$254,E$5)</f>
         <v>0</v>
       </c>
       <c r="F7" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B7,'OPEX 상세'!$D$5:$D$230,F$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B7,'OPEX 상세'!$D$5:$D$254,F$5)</f>
         <v>0</v>
       </c>
       <c r="G7" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B7,'OPEX 상세'!$D$5:$D$230,G$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B7,'OPEX 상세'!$D$5:$D$254,G$5)</f>
         <v>0</v>
       </c>
       <c r="H7" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B7,'OPEX 상세'!$D$5:$D$230,H$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B7,'OPEX 상세'!$D$5:$D$254,H$5)</f>
         <v>0</v>
       </c>
       <c r="I7" s="9" t="n">
@@ -4312,15 +4619,15 @@
         <v>0</v>
       </c>
       <c r="K7" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$230,'OPEX 상세'!$C$5:$C$230,$B7)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$254,'OPEX 상세'!$C$5:$C$254,$B7)</f>
         <v>0</v>
       </c>
       <c r="L7" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$230,'OPEX 상세'!$C$5:$C$230,$B7)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$254,'OPEX 상세'!$C$5:$C$254,$B7)</f>
         <v>0</v>
       </c>
       <c r="M7" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$230,'OPEX 상세'!$C$5:$C$230,$B7)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$254,'OPEX 상세'!$C$5:$C$254,$B7)</f>
         <v>0</v>
       </c>
       <c r="N7" s="8" t="n">
@@ -4328,7 +4635,7 @@
         <v>0</v>
       </c>
       <c r="O7" s="10" t="str">
-        <f aca="false">IF(COUNTIF('OPEX 상세'!$C$5:$C$230,$B7)=0,"입력대기",IF(M7&gt;0,"VAT 추가 가능",""))</f>
+        <f aca="false">IF(COUNTIF('OPEX 상세'!$C$5:$C$254,$B7)=0,"입력대기",IF(M7&gt;0,"VAT 추가 가능",""))</f>
         <v>입력대기</v>
       </c>
     </row>
@@ -4340,27 +4647,27 @@
         <v>18</v>
       </c>
       <c r="C8" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B8,'OPEX 상세'!$D$5:$D$230,C$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B8,'OPEX 상세'!$D$5:$D$254,C$5)</f>
         <v>7620000</v>
       </c>
       <c r="D8" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B8,'OPEX 상세'!$D$5:$D$230,D$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B8,'OPEX 상세'!$D$5:$D$254,D$5)</f>
         <v>7620000</v>
       </c>
       <c r="E8" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B8,'OPEX 상세'!$D$5:$D$230,E$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B8,'OPEX 상세'!$D$5:$D$254,E$5)</f>
         <v>38880000</v>
       </c>
       <c r="F8" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B8,'OPEX 상세'!$D$5:$D$230,F$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B8,'OPEX 상세'!$D$5:$D$254,F$5)</f>
         <v>38880000</v>
       </c>
       <c r="G8" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B8,'OPEX 상세'!$D$5:$D$230,G$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B8,'OPEX 상세'!$D$5:$D$254,G$5)</f>
         <v>0</v>
       </c>
       <c r="H8" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B8,'OPEX 상세'!$D$5:$D$230,H$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B8,'OPEX 상세'!$D$5:$D$254,H$5)</f>
         <v>0</v>
       </c>
       <c r="I8" s="9" t="n">
@@ -4368,15 +4675,15 @@
         <v>93000000</v>
       </c>
       <c r="K8" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$230,'OPEX 상세'!$C$5:$C$230,$B8)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$254,'OPEX 상세'!$C$5:$C$254,$B8)</f>
         <v>93000000</v>
       </c>
       <c r="L8" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$230,'OPEX 상세'!$C$5:$C$230,$B8)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$254,'OPEX 상세'!$C$5:$C$254,$B8)</f>
         <v>0</v>
       </c>
       <c r="M8" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$230,'OPEX 상세'!$C$5:$C$230,$B8)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$254,'OPEX 상세'!$C$5:$C$254,$B8)</f>
         <v>0</v>
       </c>
       <c r="N8" s="8" t="n">
@@ -4384,7 +4691,7 @@
         <v>93000000</v>
       </c>
       <c r="O8" s="10" t="str">
-        <f aca="false">IF(COUNTIF('OPEX 상세'!$C$5:$C$230,$B8)=0,"입력대기",IF(M8&gt;0,"VAT 추가 가능",""))</f>
+        <f aca="false">IF(COUNTIF('OPEX 상세'!$C$5:$C$254,$B8)=0,"입력대기",IF(M8&gt;0,"VAT 추가 가능",""))</f>
         <v/>
       </c>
     </row>
@@ -4396,27 +4703,27 @@
         <v>19</v>
       </c>
       <c r="C9" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B9,'OPEX 상세'!$D$5:$D$230,C$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B9,'OPEX 상세'!$D$5:$D$254,C$5)</f>
         <v>41790000</v>
       </c>
       <c r="D9" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B9,'OPEX 상세'!$D$5:$D$230,D$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B9,'OPEX 상세'!$D$5:$D$254,D$5)</f>
         <v>41090000</v>
       </c>
       <c r="E9" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B9,'OPEX 상세'!$D$5:$D$230,E$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B9,'OPEX 상세'!$D$5:$D$254,E$5)</f>
         <v>40840000</v>
       </c>
       <c r="F9" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B9,'OPEX 상세'!$D$5:$D$230,F$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B9,'OPEX 상세'!$D$5:$D$254,F$5)</f>
         <v>42500000</v>
       </c>
       <c r="G9" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B9,'OPEX 상세'!$D$5:$D$230,G$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B9,'OPEX 상세'!$D$5:$D$254,G$5)</f>
         <v>0</v>
       </c>
       <c r="H9" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B9,'OPEX 상세'!$D$5:$D$230,H$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B9,'OPEX 상세'!$D$5:$D$254,H$5)</f>
         <v>0</v>
       </c>
       <c r="I9" s="9" t="n">
@@ -4424,15 +4731,15 @@
         <v>166220000</v>
       </c>
       <c r="K9" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$230,'OPEX 상세'!$C$5:$C$230,$B9)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$254,'OPEX 상세'!$C$5:$C$254,$B9)</f>
         <v>166220000</v>
       </c>
       <c r="L9" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$230,'OPEX 상세'!$C$5:$C$230,$B9)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$254,'OPEX 상세'!$C$5:$C$254,$B9)</f>
         <v>0</v>
       </c>
       <c r="M9" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$230,'OPEX 상세'!$C$5:$C$230,$B9)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$254,'OPEX 상세'!$C$5:$C$254,$B9)</f>
         <v>0</v>
       </c>
       <c r="N9" s="8" t="n">
@@ -4440,7 +4747,7 @@
         <v>166220000</v>
       </c>
       <c r="O9" s="10" t="str">
-        <f aca="false">IF(COUNTIF('OPEX 상세'!$C$5:$C$230,$B9)=0,"입력대기",IF(M9&gt;0,"VAT 추가 가능",""))</f>
+        <f aca="false">IF(COUNTIF('OPEX 상세'!$C$5:$C$254,$B9)=0,"입력대기",IF(M9&gt;0,"VAT 추가 가능",""))</f>
         <v/>
       </c>
     </row>
@@ -4452,27 +4759,27 @@
         <v>20</v>
       </c>
       <c r="C10" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B10,'OPEX 상세'!$D$5:$D$230,C$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B10,'OPEX 상세'!$D$5:$D$254,C$5)</f>
         <v>0</v>
       </c>
       <c r="D10" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B10,'OPEX 상세'!$D$5:$D$230,D$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B10,'OPEX 상세'!$D$5:$D$254,D$5)</f>
         <v>0</v>
       </c>
       <c r="E10" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B10,'OPEX 상세'!$D$5:$D$230,E$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B10,'OPEX 상세'!$D$5:$D$254,E$5)</f>
         <v>0</v>
       </c>
       <c r="F10" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B10,'OPEX 상세'!$D$5:$D$230,F$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B10,'OPEX 상세'!$D$5:$D$254,F$5)</f>
         <v>0</v>
       </c>
       <c r="G10" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B10,'OPEX 상세'!$D$5:$D$230,G$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B10,'OPEX 상세'!$D$5:$D$254,G$5)</f>
         <v>0</v>
       </c>
       <c r="H10" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B10,'OPEX 상세'!$D$5:$D$230,H$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B10,'OPEX 상세'!$D$5:$D$254,H$5)</f>
         <v>27300000</v>
       </c>
       <c r="I10" s="9" t="n">
@@ -4480,15 +4787,15 @@
         <v>27300000</v>
       </c>
       <c r="K10" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$230,'OPEX 상세'!$C$5:$C$230,$B10)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$254,'OPEX 상세'!$C$5:$C$254,$B10)</f>
         <v>27300000</v>
       </c>
       <c r="L10" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$230,'OPEX 상세'!$C$5:$C$230,$B10)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$254,'OPEX 상세'!$C$5:$C$254,$B10)</f>
         <v>0</v>
       </c>
       <c r="M10" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$230,'OPEX 상세'!$C$5:$C$230,$B10)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$254,'OPEX 상세'!$C$5:$C$254,$B10)</f>
         <v>2730000</v>
       </c>
       <c r="N10" s="8" t="n">
@@ -4496,7 +4803,7 @@
         <v>30030000</v>
       </c>
       <c r="O10" s="10" t="str">
-        <f aca="false">IF(COUNTIF('OPEX 상세'!$C$5:$C$230,$B10)=0,"입력대기",IF(M10&gt;0,"VAT 추가 가능",""))</f>
+        <f aca="false">IF(COUNTIF('OPEX 상세'!$C$5:$C$254,$B10)=0,"입력대기",IF(M10&gt;0,"VAT 추가 가능",""))</f>
         <v>VAT 추가 가능</v>
       </c>
     </row>
@@ -4508,51 +4815,51 @@
         <v>21</v>
       </c>
       <c r="C11" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B11,'OPEX 상세'!$D$5:$D$230,C$5)</f>
-        <v>41193000</v>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B11,'OPEX 상세'!$D$5:$D$254,C$5)</f>
+        <v>60705641</v>
       </c>
       <c r="D11" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B11,'OPEX 상세'!$D$5:$D$230,D$5)</f>
-        <v>58516552</v>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B11,'OPEX 상세'!$D$5:$D$254,D$5)</f>
+        <v>77011377</v>
       </c>
       <c r="E11" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B11,'OPEX 상세'!$D$5:$D$230,E$5)</f>
-        <v>48436793</v>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B11,'OPEX 상세'!$D$5:$D$254,E$5)</f>
+        <v>67930234</v>
       </c>
       <c r="F11" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B11,'OPEX 상세'!$D$5:$D$230,F$5)</f>
-        <v>17571853</v>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B11,'OPEX 상세'!$D$5:$D$254,F$5)</f>
+        <v>35919442</v>
       </c>
       <c r="G11" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B11,'OPEX 상세'!$D$5:$D$230,G$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B11,'OPEX 상세'!$D$5:$D$254,G$5)</f>
         <v>241500</v>
       </c>
       <c r="H11" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B11,'OPEX 상세'!$D$5:$D$230,H$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B11,'OPEX 상세'!$D$5:$D$254,H$5)</f>
         <v>4931300</v>
       </c>
       <c r="I11" s="9" t="n">
         <f aca="false">SUM(C11:H11)</f>
-        <v>170890998</v>
+        <v>246739494</v>
       </c>
       <c r="K11" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$230,'OPEX 상세'!$C$5:$C$230,$B11)</f>
-        <v>170890998</v>
+        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$254,'OPEX 상세'!$C$5:$C$254,$B11)</f>
+        <v>246739494</v>
       </c>
       <c r="L11" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$230,'OPEX 상세'!$C$5:$C$230,$B11)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$254,'OPEX 상세'!$C$5:$C$254,$B11)</f>
         <v>0</v>
       </c>
       <c r="M11" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$230,'OPEX 상세'!$C$5:$C$230,$B11)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$254,'OPEX 상세'!$C$5:$C$254,$B11)</f>
         <v>0</v>
       </c>
       <c r="N11" s="8" t="n">
         <f aca="false">I11+M11</f>
-        <v>170890998</v>
+        <v>246739494</v>
       </c>
       <c r="O11" s="10" t="str">
-        <f aca="false">IF(COUNTIF('OPEX 상세'!$C$5:$C$230,$B11)=0,"입력대기",IF(M11&gt;0,"VAT 추가 가능",""))</f>
+        <f aca="false">IF(COUNTIF('OPEX 상세'!$C$5:$C$254,$B11)=0,"입력대기",IF(M11&gt;0,"VAT 추가 가능",""))</f>
         <v/>
       </c>
     </row>
@@ -4564,27 +4871,27 @@
         <v>22</v>
       </c>
       <c r="C12" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B12,'OPEX 상세'!$D$5:$D$230,C$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B12,'OPEX 상세'!$D$5:$D$254,C$5)</f>
         <v>36551070</v>
       </c>
       <c r="D12" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B12,'OPEX 상세'!$D$5:$D$230,D$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B12,'OPEX 상세'!$D$5:$D$254,D$5)</f>
         <v>45255564</v>
       </c>
       <c r="E12" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B12,'OPEX 상세'!$D$5:$D$230,E$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B12,'OPEX 상세'!$D$5:$D$254,E$5)</f>
         <v>59556592</v>
       </c>
       <c r="F12" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B12,'OPEX 상세'!$D$5:$D$230,F$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B12,'OPEX 상세'!$D$5:$D$254,F$5)</f>
         <v>53916216</v>
       </c>
       <c r="G12" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B12,'OPEX 상세'!$D$5:$D$230,G$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B12,'OPEX 상세'!$D$5:$D$254,G$5)</f>
         <v>0</v>
       </c>
       <c r="H12" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B12,'OPEX 상세'!$D$5:$D$230,H$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B12,'OPEX 상세'!$D$5:$D$254,H$5)</f>
         <v>0</v>
       </c>
       <c r="I12" s="9" t="n">
@@ -4592,15 +4899,15 @@
         <v>195279442</v>
       </c>
       <c r="K12" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$230,'OPEX 상세'!$C$5:$C$230,$B12)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$254,'OPEX 상세'!$C$5:$C$254,$B12)</f>
         <v>195279442</v>
       </c>
       <c r="L12" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$230,'OPEX 상세'!$C$5:$C$230,$B12)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$254,'OPEX 상세'!$C$5:$C$254,$B12)</f>
         <v>0</v>
       </c>
       <c r="M12" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$230,'OPEX 상세'!$C$5:$C$230,$B12)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$254,'OPEX 상세'!$C$5:$C$254,$B12)</f>
         <v>0</v>
       </c>
       <c r="N12" s="8" t="n">
@@ -4608,7 +4915,7 @@
         <v>195279442</v>
       </c>
       <c r="O12" s="10" t="str">
-        <f aca="false">IF(COUNTIF('OPEX 상세'!$C$5:$C$230,$B12)=0,"입력대기",IF(M12&gt;0,"VAT 추가 가능",""))</f>
+        <f aca="false">IF(COUNTIF('OPEX 상세'!$C$5:$C$254,$B12)=0,"입력대기",IF(M12&gt;0,"VAT 추가 가능",""))</f>
         <v/>
       </c>
     </row>
@@ -4620,27 +4927,27 @@
         <v>23</v>
       </c>
       <c r="C13" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B13,'OPEX 상세'!$D$5:$D$230,C$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B13,'OPEX 상세'!$D$5:$D$254,C$5)</f>
         <v>1030200</v>
       </c>
       <c r="D13" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B13,'OPEX 상세'!$D$5:$D$230,D$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B13,'OPEX 상세'!$D$5:$D$254,D$5)</f>
         <v>1809200</v>
       </c>
       <c r="E13" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B13,'OPEX 상세'!$D$5:$D$230,E$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B13,'OPEX 상세'!$D$5:$D$254,E$5)</f>
         <v>1809200</v>
       </c>
       <c r="F13" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B13,'OPEX 상세'!$D$5:$D$230,F$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B13,'OPEX 상세'!$D$5:$D$254,F$5)</f>
         <v>1809200</v>
       </c>
       <c r="G13" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B13,'OPEX 상세'!$D$5:$D$230,G$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B13,'OPEX 상세'!$D$5:$D$254,G$5)</f>
         <v>0</v>
       </c>
       <c r="H13" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B13,'OPEX 상세'!$D$5:$D$230,H$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B13,'OPEX 상세'!$D$5:$D$254,H$5)</f>
         <v>0</v>
       </c>
       <c r="I13" s="9" t="n">
@@ -4648,15 +4955,15 @@
         <v>6457800</v>
       </c>
       <c r="K13" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$230,'OPEX 상세'!$C$5:$C$230,$B13)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$254,'OPEX 상세'!$C$5:$C$254,$B13)</f>
         <v>6421000</v>
       </c>
       <c r="L13" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$230,'OPEX 상세'!$C$5:$C$230,$B13)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$254,'OPEX 상세'!$C$5:$C$254,$B13)</f>
         <v>36800</v>
       </c>
       <c r="M13" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$230,'OPEX 상세'!$C$5:$C$230,$B13)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$254,'OPEX 상세'!$C$5:$C$254,$B13)</f>
         <v>0</v>
       </c>
       <c r="N13" s="8" t="n">
@@ -4664,7 +4971,7 @@
         <v>6457800</v>
       </c>
       <c r="O13" s="10" t="str">
-        <f aca="false">IF(COUNTIF('OPEX 상세'!$C$5:$C$230,$B13)=0,"입력대기",IF(M13&gt;0,"VAT 추가 가능",""))</f>
+        <f aca="false">IF(COUNTIF('OPEX 상세'!$C$5:$C$254,$B13)=0,"입력대기",IF(M13&gt;0,"VAT 추가 가능",""))</f>
         <v/>
       </c>
     </row>
@@ -4676,27 +4983,27 @@
         <v>24</v>
       </c>
       <c r="C14" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B14,'OPEX 상세'!$D$5:$D$230,C$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B14,'OPEX 상세'!$D$5:$D$254,C$5)</f>
         <v>0</v>
       </c>
       <c r="D14" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B14,'OPEX 상세'!$D$5:$D$230,D$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B14,'OPEX 상세'!$D$5:$D$254,D$5)</f>
         <v>0</v>
       </c>
       <c r="E14" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B14,'OPEX 상세'!$D$5:$D$230,E$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B14,'OPEX 상세'!$D$5:$D$254,E$5)</f>
         <v>0</v>
       </c>
       <c r="F14" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B14,'OPEX 상세'!$D$5:$D$230,F$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B14,'OPEX 상세'!$D$5:$D$254,F$5)</f>
         <v>0</v>
       </c>
       <c r="G14" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B14,'OPEX 상세'!$D$5:$D$230,G$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B14,'OPEX 상세'!$D$5:$D$254,G$5)</f>
         <v>0</v>
       </c>
       <c r="H14" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B14,'OPEX 상세'!$D$5:$D$230,H$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B14,'OPEX 상세'!$D$5:$D$254,H$5)</f>
         <v>0</v>
       </c>
       <c r="I14" s="9" t="n">
@@ -4704,15 +5011,15 @@
         <v>0</v>
       </c>
       <c r="K14" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$230,'OPEX 상세'!$C$5:$C$230,$B14)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$254,'OPEX 상세'!$C$5:$C$254,$B14)</f>
         <v>0</v>
       </c>
       <c r="L14" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$230,'OPEX 상세'!$C$5:$C$230,$B14)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$254,'OPEX 상세'!$C$5:$C$254,$B14)</f>
         <v>0</v>
       </c>
       <c r="M14" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$230,'OPEX 상세'!$C$5:$C$230,$B14)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$254,'OPEX 상세'!$C$5:$C$254,$B14)</f>
         <v>0</v>
       </c>
       <c r="N14" s="8" t="n">
@@ -4720,7 +5027,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="10" t="str">
-        <f aca="false">IF(COUNTIF('OPEX 상세'!$C$5:$C$230,$B14)=0,"입력대기",IF(M14&gt;0,"VAT 추가 가능",""))</f>
+        <f aca="false">IF(COUNTIF('OPEX 상세'!$C$5:$C$254,$B14)=0,"입력대기",IF(M14&gt;0,"VAT 추가 가능",""))</f>
         <v>입력대기</v>
       </c>
     </row>
@@ -4732,27 +5039,27 @@
         <v>25</v>
       </c>
       <c r="C15" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B15,'OPEX 상세'!$D$5:$D$230,C$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B15,'OPEX 상세'!$D$5:$D$254,C$5)</f>
         <v>10206800</v>
       </c>
       <c r="D15" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B15,'OPEX 상세'!$D$5:$D$230,D$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B15,'OPEX 상세'!$D$5:$D$254,D$5)</f>
         <v>3120000</v>
       </c>
       <c r="E15" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B15,'OPEX 상세'!$D$5:$D$230,E$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B15,'OPEX 상세'!$D$5:$D$254,E$5)</f>
         <v>18017500</v>
       </c>
       <c r="F15" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B15,'OPEX 상세'!$D$5:$D$230,F$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B15,'OPEX 상세'!$D$5:$D$254,F$5)</f>
         <v>9932500</v>
       </c>
       <c r="G15" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B15,'OPEX 상세'!$D$5:$D$230,G$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B15,'OPEX 상세'!$D$5:$D$254,G$5)</f>
         <v>0</v>
       </c>
       <c r="H15" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B15,'OPEX 상세'!$D$5:$D$230,H$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B15,'OPEX 상세'!$D$5:$D$254,H$5)</f>
         <v>0</v>
       </c>
       <c r="I15" s="9" t="n">
@@ -4760,15 +5067,15 @@
         <v>41276800</v>
       </c>
       <c r="K15" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$230,'OPEX 상세'!$C$5:$C$230,$B15)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$254,'OPEX 상세'!$C$5:$C$254,$B15)</f>
         <v>41276800</v>
       </c>
       <c r="L15" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$230,'OPEX 상세'!$C$5:$C$230,$B15)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$254,'OPEX 상세'!$C$5:$C$254,$B15)</f>
         <v>0</v>
       </c>
       <c r="M15" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$230,'OPEX 상세'!$C$5:$C$230,$B15)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$254,'OPEX 상세'!$C$5:$C$254,$B15)</f>
         <v>0</v>
       </c>
       <c r="N15" s="8" t="n">
@@ -4776,7 +5083,7 @@
         <v>41276800</v>
       </c>
       <c r="O15" s="10" t="str">
-        <f aca="false">IF(COUNTIF('OPEX 상세'!$C$5:$C$230,$B15)=0,"입력대기",IF(M15&gt;0,"VAT 추가 가능",""))</f>
+        <f aca="false">IF(COUNTIF('OPEX 상세'!$C$5:$C$254,$B15)=0,"입력대기",IF(M15&gt;0,"VAT 추가 가능",""))</f>
         <v/>
       </c>
     </row>
@@ -4788,27 +5095,27 @@
         <v>26</v>
       </c>
       <c r="C16" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B16,'OPEX 상세'!$D$5:$D$230,C$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B16,'OPEX 상세'!$D$5:$D$254,C$5)</f>
         <v>0</v>
       </c>
       <c r="D16" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B16,'OPEX 상세'!$D$5:$D$230,D$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B16,'OPEX 상세'!$D$5:$D$254,D$5)</f>
         <v>0</v>
       </c>
       <c r="E16" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B16,'OPEX 상세'!$D$5:$D$230,E$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B16,'OPEX 상세'!$D$5:$D$254,E$5)</f>
         <v>0</v>
       </c>
       <c r="F16" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B16,'OPEX 상세'!$D$5:$D$230,F$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B16,'OPEX 상세'!$D$5:$D$254,F$5)</f>
         <v>0</v>
       </c>
       <c r="G16" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B16,'OPEX 상세'!$D$5:$D$230,G$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B16,'OPEX 상세'!$D$5:$D$254,G$5)</f>
         <v>0</v>
       </c>
       <c r="H16" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$230,'OPEX 상세'!$C$5:$C$230,$B16,'OPEX 상세'!$D$5:$D$230,H$5)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$P$5:$P$254,'OPEX 상세'!$C$5:$C$254,$B16,'OPEX 상세'!$D$5:$D$254,H$5)</f>
         <v>12600000</v>
       </c>
       <c r="I16" s="9" t="n">
@@ -4816,15 +5123,15 @@
         <v>12600000</v>
       </c>
       <c r="K16" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$230,'OPEX 상세'!$C$5:$C$230,$B16)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$254,'OPEX 상세'!$C$5:$C$254,$B16)</f>
         <v>12600000</v>
       </c>
       <c r="L16" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$230,'OPEX 상세'!$C$5:$C$230,$B16)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$254,'OPEX 상세'!$C$5:$C$254,$B16)</f>
         <v>0</v>
       </c>
       <c r="M16" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$230,'OPEX 상세'!$C$5:$C$230,$B16)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$254,'OPEX 상세'!$C$5:$C$254,$B16)</f>
         <v>1260000</v>
       </c>
       <c r="N16" s="8" t="n">
@@ -4832,7 +5139,7 @@
         <v>13860000</v>
       </c>
       <c r="O16" s="10" t="str">
-        <f aca="false">IF(COUNTIF('OPEX 상세'!$C$5:$C$230,$B16)=0,"입력대기",IF(M16&gt;0,"VAT 추가 가능",""))</f>
+        <f aca="false">IF(COUNTIF('OPEX 상세'!$C$5:$C$254,$B16)=0,"입력대기",IF(M16&gt;0,"VAT 추가 가능",""))</f>
         <v>VAT 추가 가능</v>
       </c>
     </row>
@@ -4843,19 +5150,19 @@
       </c>
       <c r="C17" s="13" t="n">
         <f aca="false">SUM(C6:C16)</f>
-        <v>138391070</v>
+        <v>157903711</v>
       </c>
       <c r="D17" s="13" t="n">
         <f aca="false">SUM(D6:D16)</f>
-        <v>157411316</v>
+        <v>175906141</v>
       </c>
       <c r="E17" s="13" t="n">
         <f aca="false">SUM(E6:E16)</f>
-        <v>207540085</v>
+        <v>227033526</v>
       </c>
       <c r="F17" s="13" t="n">
         <f aca="false">SUM(F6:F16)</f>
-        <v>164609769</v>
+        <v>182957358</v>
       </c>
       <c r="G17" s="13" t="n">
         <f aca="false">SUM(G6:G16)</f>
@@ -4867,11 +5174,11 @@
       </c>
       <c r="I17" s="13" t="n">
         <f aca="false">SUM(I6:I16)</f>
-        <v>714327440</v>
+        <v>790175936</v>
       </c>
       <c r="K17" s="13" t="n">
         <f aca="false">SUM(K6:K16)</f>
-        <v>714172240</v>
+        <v>790020736</v>
       </c>
       <c r="L17" s="13" t="n">
         <f aca="false">SUM(L6:L16)</f>
@@ -4883,7 +5190,7 @@
       </c>
       <c r="N17" s="13" t="n">
         <f aca="false">SUM(N6:N16)</f>
-        <v>718317440</v>
+        <v>794165936</v>
       </c>
       <c r="O17" s="13"/>
     </row>
@@ -4892,7 +5199,7 @@
         <v>28</v>
       </c>
       <c r="I18" s="14" t="n">
-        <f aca="false">I17-'OPEX 상세'!P231</f>
+        <f aca="false">I17-'OPEX 상세'!P255</f>
         <v>0</v>
       </c>
     </row>
@@ -4926,24 +5233,24 @@
         <v>4</v>
       </c>
       <c r="C22" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$230,'OPEX 상세'!$D$5:$D$230,$B22)</f>
-        <v>138381870</v>
+        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$254,'OPEX 상세'!$D$5:$D$254,$B22)</f>
+        <v>157894511</v>
       </c>
       <c r="D22" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$230,'OPEX 상세'!$D$5:$D$230,$B22)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$254,'OPEX 상세'!$D$5:$D$254,$B22)</f>
         <v>9200</v>
       </c>
       <c r="E22" s="8" t="n">
         <f aca="false">C22+D22</f>
-        <v>138391070</v>
+        <v>157903711</v>
       </c>
       <c r="F22" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$230,'OPEX 상세'!$D$5:$D$230,$B22)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$254,'OPEX 상세'!$D$5:$D$254,$B22)</f>
         <v>0</v>
       </c>
       <c r="G22" s="16" t="n">
         <f aca="false">IF($E$28=0,0,E22/$E$28)</f>
-        <v>0.193736180707268</v>
+        <v>0.199833611485734</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4951,24 +5258,24 @@
         <v>5</v>
       </c>
       <c r="C23" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$230,'OPEX 상세'!$D$5:$D$230,$B23)</f>
-        <v>157402116</v>
+        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$254,'OPEX 상세'!$D$5:$D$254,$B23)</f>
+        <v>175896941</v>
       </c>
       <c r="D23" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$230,'OPEX 상세'!$D$5:$D$230,$B23)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$254,'OPEX 상세'!$D$5:$D$254,$B23)</f>
         <v>9200</v>
       </c>
       <c r="E23" s="8" t="n">
         <f aca="false">C23+D23</f>
-        <v>157411316</v>
+        <v>175906141</v>
       </c>
       <c r="F23" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$230,'OPEX 상세'!$D$5:$D$230,$B23)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$254,'OPEX 상세'!$D$5:$D$254,$B23)</f>
         <v>0</v>
       </c>
       <c r="G23" s="16" t="n">
         <f aca="false">IF($E$28=0,0,E23/$E$28)</f>
-        <v>0.220362969676763</v>
+        <v>0.222616423742876</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4976,24 +5283,24 @@
         <v>6</v>
       </c>
       <c r="C24" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$230,'OPEX 상세'!$D$5:$D$230,$B24)</f>
-        <v>207530885</v>
+        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$254,'OPEX 상세'!$D$5:$D$254,$B24)</f>
+        <v>227024326</v>
       </c>
       <c r="D24" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$230,'OPEX 상세'!$D$5:$D$230,$B24)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$254,'OPEX 상세'!$D$5:$D$254,$B24)</f>
         <v>9200</v>
       </c>
       <c r="E24" s="8" t="n">
         <f aca="false">C24+D24</f>
-        <v>207540085</v>
+        <v>227033526</v>
       </c>
       <c r="F24" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$230,'OPEX 상세'!$D$5:$D$230,$B24)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$254,'OPEX 상세'!$D$5:$D$254,$B24)</f>
         <v>0</v>
       </c>
       <c r="G24" s="16" t="n">
         <f aca="false">IF($E$28=0,0,E24/$E$28)</f>
-        <v>0.290539146865197</v>
+        <v>0.28732022282187</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5001,24 +5308,24 @@
         <v>7</v>
       </c>
       <c r="C25" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$230,'OPEX 상세'!$D$5:$D$230,$B25)</f>
-        <v>164600569</v>
+        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$254,'OPEX 상세'!$D$5:$D$254,$B25)</f>
+        <v>182948158</v>
       </c>
       <c r="D25" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$230,'OPEX 상세'!$D$5:$D$230,$B25)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$254,'OPEX 상세'!$D$5:$D$254,$B25)</f>
         <v>9200</v>
       </c>
       <c r="E25" s="8" t="n">
         <f aca="false">C25+D25</f>
-        <v>164609769</v>
+        <v>182957358</v>
       </c>
       <c r="F25" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$230,'OPEX 상세'!$D$5:$D$230,$B25)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$254,'OPEX 상세'!$D$5:$D$254,$B25)</f>
         <v>0</v>
       </c>
       <c r="G25" s="16" t="n">
         <f aca="false">IF($E$28=0,0,E25/$E$28)</f>
-        <v>0.230440215204389</v>
+        <v>0.231540027561659</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5026,11 +5333,11 @@
         <v>8</v>
       </c>
       <c r="C26" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$230,'OPEX 상세'!$D$5:$D$230,$B26)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$254,'OPEX 상세'!$D$5:$D$254,$B26)</f>
         <v>241500</v>
       </c>
       <c r="D26" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$230,'OPEX 상세'!$D$5:$D$230,$B26)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$254,'OPEX 상세'!$D$5:$D$254,$B26)</f>
         <v>0</v>
       </c>
       <c r="E26" s="8" t="n">
@@ -5038,12 +5345,12 @@
         <v>241500</v>
       </c>
       <c r="F26" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$230,'OPEX 상세'!$D$5:$D$230,$B26)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$254,'OPEX 상세'!$D$5:$D$254,$B26)</f>
         <v>0</v>
       </c>
       <c r="G26" s="16" t="n">
         <f aca="false">IF($E$28=0,0,E26/$E$28)</f>
-        <v>0.000338080250704075</v>
+        <v>0.000305628137984703</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5051,11 +5358,11 @@
         <v>32</v>
       </c>
       <c r="C27" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$230,'OPEX 상세'!$D$5:$D$230,$B27)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$N$5:$N$254,'OPEX 상세'!$D$5:$D$254,$B27)</f>
         <v>46015300</v>
       </c>
       <c r="D27" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$230,'OPEX 상세'!$D$5:$D$230,$B27)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$O$5:$O$254,'OPEX 상세'!$D$5:$D$254,$B27)</f>
         <v>118400</v>
       </c>
       <c r="E27" s="8" t="n">
@@ -5063,12 +5370,12 @@
         <v>46133700</v>
       </c>
       <c r="F27" s="8" t="n">
-        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$230,'OPEX 상세'!$D$5:$D$230,$B27)</f>
+        <f aca="false">SUMIFS('OPEX 상세'!$R$5:$R$254,'OPEX 상세'!$D$5:$D$254,$B27)</f>
         <v>3990000</v>
       </c>
       <c r="G27" s="16" t="n">
         <f aca="false">IF($E$28=0,0,E27/$E$28)</f>
-        <v>0.0645834072956794</v>
+        <v>0.0583840862498754</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5077,7 +5384,7 @@
       </c>
       <c r="C28" s="13" t="n">
         <f aca="false">SUM(C22:C27)</f>
-        <v>714172240</v>
+        <v>790020736</v>
       </c>
       <c r="D28" s="13" t="n">
         <f aca="false">SUM(D22:D27)</f>
@@ -5085,7 +5392,7 @@
       </c>
       <c r="E28" s="13" t="n">
         <f aca="false">SUM(E22:E27)</f>
-        <v>714327440</v>
+        <v>790175936</v>
       </c>
       <c r="F28" s="13" t="n">
         <f aca="false">SUM(F22:F27)</f>
@@ -5124,6 +5431,11 @@
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="20" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="20" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -5142,7 +5454,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:S231"/>
+  <dimension ref="A1:S255"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -5167,12 +5479,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5180,7 +5492,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>3</v>
@@ -5189,49 +5501,49 @@
         <v>30</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="R4" s="5" t="s">
         <v>13</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5244,7 +5556,7 @@
         <v>16</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E5" s="25"/>
       <c r="F5" s="7" t="str">
@@ -5253,19 +5565,19 @@
       </c>
       <c r="G5" s="25"/>
       <c r="H5" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J5" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K5" s="27" t="n">
         <v>1302400</v>
       </c>
       <c r="L5" s="26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M5" s="8" t="n">
         <f aca="false">IF(K5="","",IF(J5="USD",ROUND(K5*설정!$C$4,0),K5))</f>
@@ -5289,7 +5601,7 @@
         <v/>
       </c>
       <c r="S5" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5311,13 +5623,13 @@
       </c>
       <c r="G6" s="25"/>
       <c r="H6" s="25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J6" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K6" s="27" t="n">
         <v>3680000</v>
@@ -5365,13 +5677,13 @@
       </c>
       <c r="G7" s="25"/>
       <c r="H7" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="I7" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="I7" s="24" t="s">
-        <v>63</v>
-      </c>
       <c r="J7" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K7" s="27" t="n">
         <v>2800</v>
@@ -5399,7 +5711,7 @@
         <v/>
       </c>
       <c r="S7" s="25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5421,13 +5733,13 @@
       </c>
       <c r="G8" s="25"/>
       <c r="H8" s="25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J8" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K8" s="27" t="n">
         <v>160000</v>
@@ -5475,13 +5787,13 @@
       </c>
       <c r="G9" s="25"/>
       <c r="H9" s="25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I9" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J9" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K9" s="27" t="n">
         <v>3680000</v>
@@ -5529,13 +5841,13 @@
       </c>
       <c r="G10" s="25"/>
       <c r="H10" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="I10" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="I10" s="24" t="s">
-        <v>63</v>
-      </c>
       <c r="J10" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K10" s="27" t="n">
         <v>2800</v>
@@ -5563,7 +5875,7 @@
         <v/>
       </c>
       <c r="S10" s="25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5585,13 +5897,13 @@
       </c>
       <c r="G11" s="25"/>
       <c r="H11" s="25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I11" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J11" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K11" s="27" t="n">
         <v>160000</v>
@@ -5639,13 +5951,13 @@
       </c>
       <c r="G12" s="25"/>
       <c r="H12" s="25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I12" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J12" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K12" s="27" t="n">
         <v>26000</v>
@@ -5673,7 +5985,7 @@
         <v/>
       </c>
       <c r="S12" s="25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5695,13 +6007,13 @@
       </c>
       <c r="G13" s="25"/>
       <c r="H13" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="I13" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="I13" s="24" t="s">
-        <v>63</v>
-      </c>
       <c r="J13" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K13" s="27" t="n">
         <v>2800</v>
@@ -5729,7 +6041,7 @@
         <v/>
       </c>
       <c r="S13" s="25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5751,13 +6063,13 @@
       </c>
       <c r="G14" s="25"/>
       <c r="H14" s="25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J14" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K14" s="27" t="n">
         <v>26000</v>
@@ -5785,7 +6097,7 @@
         <v/>
       </c>
       <c r="S14" s="25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5807,13 +6119,13 @@
       </c>
       <c r="G15" s="25"/>
       <c r="H15" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="I15" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="I15" s="24" t="s">
-        <v>63</v>
-      </c>
       <c r="J15" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K15" s="27" t="n">
         <v>2800</v>
@@ -5841,7 +6153,7 @@
         <v/>
       </c>
       <c r="S15" s="25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5863,13 +6175,13 @@
       </c>
       <c r="G16" s="25"/>
       <c r="H16" s="25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J16" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K16" s="27" t="n">
         <v>33800000</v>
@@ -5897,7 +6209,7 @@
         <v/>
       </c>
       <c r="S16" s="23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5919,13 +6231,13 @@
       </c>
       <c r="G17" s="25"/>
       <c r="H17" s="23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J17" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K17" s="27" t="n">
         <v>7990000</v>
@@ -5973,13 +6285,13 @@
       </c>
       <c r="G18" s="25"/>
       <c r="H18" s="25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J18" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K18" s="27" t="n">
         <v>33800000</v>
@@ -6007,7 +6319,7 @@
         <v/>
       </c>
       <c r="S18" s="23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6029,13 +6341,13 @@
       </c>
       <c r="G19" s="25"/>
       <c r="H19" s="23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I19" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J19" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K19" s="27" t="n">
         <v>7290000</v>
@@ -6083,13 +6395,13 @@
       </c>
       <c r="G20" s="25"/>
       <c r="H20" s="25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I20" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J20" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>33800000</v>
@@ -6117,7 +6429,7 @@
         <v/>
       </c>
       <c r="S20" s="23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6139,13 +6451,13 @@
       </c>
       <c r="G21" s="25"/>
       <c r="H21" s="23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I21" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J21" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K21" s="27" t="n">
         <v>7040000</v>
@@ -6193,13 +6505,13 @@
       </c>
       <c r="G22" s="25"/>
       <c r="H22" s="25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J22" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K22" s="27" t="n">
         <v>33800000</v>
@@ -6227,7 +6539,7 @@
         <v/>
       </c>
       <c r="S22" s="23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6249,13 +6561,13 @@
       </c>
       <c r="G23" s="25"/>
       <c r="H23" s="23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I23" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J23" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K23" s="27" t="n">
         <v>8700000</v>
@@ -6294,7 +6606,7 @@
         <v>20</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E24" s="25"/>
       <c r="F24" s="7" t="str">
@@ -6303,13 +6615,13 @@
       </c>
       <c r="G24" s="25"/>
       <c r="H24" s="25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I24" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J24" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K24" s="27" t="n">
         <v>27300000</v>
@@ -6332,14 +6644,14 @@
         <v>27300000</v>
       </c>
       <c r="Q24" s="26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R24" s="8" t="n">
         <f aca="false">IF(OR(M24="",Q24&lt;&gt;"Y"),"",ROUND(N24*설정!$C$5,0))</f>
         <v>2730000</v>
       </c>
       <c r="S24" s="23" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6348,13 +6660,13 @@
         <v>21</v>
       </c>
       <c r="B25" s="22" t="n">
-        <v>46282</v>
+        <v>46268</v>
       </c>
       <c r="C25" s="23" t="s">
         <v>21</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E25" s="25"/>
       <c r="F25" s="7" t="str">
@@ -6363,25 +6675,25 @@
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I25" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J25" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K25" s="27" t="n">
-        <v>241500</v>
+        <v>9174000</v>
       </c>
       <c r="L25" s="26"/>
       <c r="M25" s="8" t="n">
         <f aca="false">IF(K25="","",IF(J25="USD",ROUND(K25*설정!$C$4,0),K25))</f>
-        <v>241500</v>
+        <v>9174000</v>
       </c>
       <c r="N25" s="8" t="n">
         <f aca="false">IF(M25="","",IF(AND(I25="과세",L25="VAT포함"),ROUND(M25/(1+설정!$C$5),0),M25))</f>
-        <v>241500</v>
+        <v>9174000</v>
       </c>
       <c r="O25" s="8" t="n">
         <f aca="false">IF(M25="","",IF(I25="과세",IF(L25="VAT포함",M25-N25,ROUND(N25*설정!$C$5,0)),0))</f>
@@ -6389,15 +6701,15 @@
       </c>
       <c r="P25" s="8" t="n">
         <f aca="false">IF(M25="","",N25+O25)</f>
-        <v>241500</v>
+        <v>9174000</v>
       </c>
       <c r="Q25" s="26"/>
       <c r="R25" s="8" t="str">
         <f aca="false">IF(OR(M25="",Q25&lt;&gt;"Y"),"",ROUND(N25*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S25" s="23" t="s">
-        <v>77</v>
+      <c r="S25" s="25" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6406,7 +6718,7 @@
         <v>22</v>
       </c>
       <c r="B26" s="22" t="n">
-        <v>46295</v>
+        <v>46268</v>
       </c>
       <c r="C26" s="23" t="s">
         <v>21</v>
@@ -6420,26 +6732,26 @@
         <v/>
       </c>
       <c r="G26" s="25"/>
-      <c r="H26" s="25" t="s">
-        <v>73</v>
+      <c r="H26" s="23" t="s">
+        <v>79</v>
       </c>
       <c r="I26" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J26" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K26" s="27" t="n">
-        <v>20700000</v>
+        <v>4400000</v>
       </c>
       <c r="L26" s="26"/>
       <c r="M26" s="8" t="n">
         <f aca="false">IF(K26="","",IF(J26="USD",ROUND(K26*설정!$C$4,0),K26))</f>
-        <v>20700000</v>
+        <v>4400000</v>
       </c>
       <c r="N26" s="8" t="n">
         <f aca="false">IF(M26="","",IF(AND(I26="과세",L26="VAT포함"),ROUND(M26/(1+설정!$C$5),0),M26))</f>
-        <v>20700000</v>
+        <v>4400000</v>
       </c>
       <c r="O26" s="8" t="n">
         <f aca="false">IF(M26="","",IF(I26="과세",IF(L26="VAT포함",M26-N26,ROUND(N26*설정!$C$5,0)),0))</f>
@@ -6447,7 +6759,7 @@
       </c>
       <c r="P26" s="8" t="n">
         <f aca="false">IF(M26="","",N26+O26)</f>
-        <v>20700000</v>
+        <v>4400000</v>
       </c>
       <c r="Q26" s="26"/>
       <c r="R26" s="8" t="str">
@@ -6464,13 +6776,13 @@
         <v>23</v>
       </c>
       <c r="B27" s="22" t="n">
-        <v>46295</v>
+        <v>46268</v>
       </c>
       <c r="C27" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="24" t="s">
-        <v>56</v>
+      <c r="D27" s="26" t="s">
+        <v>4</v>
       </c>
       <c r="E27" s="25"/>
       <c r="F27" s="7" t="str">
@@ -6478,26 +6790,26 @@
         <v/>
       </c>
       <c r="G27" s="25"/>
-      <c r="H27" s="23" t="s">
-        <v>79</v>
+      <c r="H27" s="25" t="s">
+        <v>80</v>
       </c>
       <c r="I27" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J27" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K27" s="27" t="n">
-        <v>531300</v>
+        <v>1600245</v>
       </c>
       <c r="L27" s="26"/>
       <c r="M27" s="8" t="n">
         <f aca="false">IF(K27="","",IF(J27="USD",ROUND(K27*설정!$C$4,0),K27))</f>
-        <v>531300</v>
+        <v>1600245</v>
       </c>
       <c r="N27" s="8" t="n">
         <f aca="false">IF(M27="","",IF(AND(I27="과세",L27="VAT포함"),ROUND(M27/(1+설정!$C$5),0),M27))</f>
-        <v>531300</v>
+        <v>1600245</v>
       </c>
       <c r="O27" s="8" t="n">
         <f aca="false">IF(M27="","",IF(I27="과세",IF(L27="VAT포함",M27-N27,ROUND(N27*설정!$C$5,0)),0))</f>
@@ -6505,7 +6817,7 @@
       </c>
       <c r="P27" s="8" t="n">
         <f aca="false">IF(M27="","",N27+O27)</f>
-        <v>531300</v>
+        <v>1600245</v>
       </c>
       <c r="Q27" s="26"/>
       <c r="R27" s="8" t="str">
@@ -6513,7 +6825,7 @@
         <v/>
       </c>
       <c r="S27" s="25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6521,12 +6833,14 @@
         <f aca="false">IF(C28="","",COUNTA($C$5:C28))</f>
         <v>24</v>
       </c>
-      <c r="B28" s="22"/>
+      <c r="B28" s="22" t="n">
+        <v>46268</v>
+      </c>
       <c r="C28" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="24" t="s">
-        <v>56</v>
+      <c r="D28" s="26" t="s">
+        <v>4</v>
       </c>
       <c r="E28" s="25"/>
       <c r="F28" s="7" t="str">
@@ -6538,22 +6852,22 @@
         <v>81</v>
       </c>
       <c r="I28" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J28" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K28" s="27" t="n">
-        <v>4400000</v>
+        <v>1100000</v>
       </c>
       <c r="L28" s="26"/>
       <c r="M28" s="8" t="n">
         <f aca="false">IF(K28="","",IF(J28="USD",ROUND(K28*설정!$C$4,0),K28))</f>
-        <v>4400000</v>
+        <v>1100000</v>
       </c>
       <c r="N28" s="8" t="n">
         <f aca="false">IF(M28="","",IF(AND(I28="과세",L28="VAT포함"),ROUND(M28/(1+설정!$C$5),0),M28))</f>
-        <v>4400000</v>
+        <v>1100000</v>
       </c>
       <c r="O28" s="8" t="n">
         <f aca="false">IF(M28="","",IF(I28="과세",IF(L28="VAT포함",M28-N28,ROUND(N28*설정!$C$5,0)),0))</f>
@@ -6561,15 +6875,15 @@
       </c>
       <c r="P28" s="8" t="n">
         <f aca="false">IF(M28="","",N28+O28)</f>
-        <v>4400000</v>
+        <v>1100000</v>
       </c>
       <c r="Q28" s="26"/>
       <c r="R28" s="8" t="str">
         <f aca="false">IF(OR(M28="",Q28&lt;&gt;"Y"),"",ROUND(N28*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S28" s="23" t="s">
-        <v>82</v>
+      <c r="S28" s="25" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6577,7 +6891,9 @@
         <f aca="false">IF(C29="","",COUNTA($C$5:C29))</f>
         <v>25</v>
       </c>
-      <c r="B29" s="22"/>
+      <c r="B29" s="22" t="n">
+        <v>46268</v>
+      </c>
       <c r="C29" s="23" t="s">
         <v>21</v>
       </c>
@@ -6591,25 +6907,25 @@
       </c>
       <c r="G29" s="25"/>
       <c r="H29" s="25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I29" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J29" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K29" s="27" t="n">
-        <v>20493000</v>
+        <v>981600</v>
       </c>
       <c r="L29" s="26"/>
       <c r="M29" s="8" t="n">
         <f aca="false">IF(K29="","",IF(J29="USD",ROUND(K29*설정!$C$4,0),K29))</f>
-        <v>20493000</v>
+        <v>981600</v>
       </c>
       <c r="N29" s="8" t="n">
         <f aca="false">IF(M29="","",IF(AND(I29="과세",L29="VAT포함"),ROUND(M29/(1+설정!$C$5),0),M29))</f>
-        <v>20493000</v>
+        <v>981600</v>
       </c>
       <c r="O29" s="8" t="n">
         <f aca="false">IF(M29="","",IF(I29="과세",IF(L29="VAT포함",M29-N29,ROUND(N29*설정!$C$5,0)),0))</f>
@@ -6617,7 +6933,7 @@
       </c>
       <c r="P29" s="8" t="n">
         <f aca="false">IF(M29="","",N29+O29)</f>
-        <v>20493000</v>
+        <v>981600</v>
       </c>
       <c r="Q29" s="26"/>
       <c r="R29" s="8" t="str">
@@ -6625,7 +6941,7 @@
         <v/>
       </c>
       <c r="S29" s="25" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6633,12 +6949,14 @@
         <f aca="false">IF(C30="","",COUNTA($C$5:C30))</f>
         <v>26</v>
       </c>
-      <c r="B30" s="22"/>
+      <c r="B30" s="22" t="n">
+        <v>46268</v>
+      </c>
       <c r="C30" s="23" t="s">
         <v>21</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E30" s="25"/>
       <c r="F30" s="7" t="str">
@@ -6647,25 +6965,25 @@
       </c>
       <c r="G30" s="25"/>
       <c r="H30" s="25" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I30" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J30" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K30" s="27" t="n">
-        <v>2530000</v>
+        <v>2256796</v>
       </c>
       <c r="L30" s="26"/>
       <c r="M30" s="8" t="n">
         <f aca="false">IF(K30="","",IF(J30="USD",ROUND(K30*설정!$C$4,0),K30))</f>
-        <v>2530000</v>
+        <v>2256796</v>
       </c>
       <c r="N30" s="8" t="n">
         <f aca="false">IF(M30="","",IF(AND(I30="과세",L30="VAT포함"),ROUND(M30/(1+설정!$C$5),0),M30))</f>
-        <v>2530000</v>
+        <v>2256796</v>
       </c>
       <c r="O30" s="8" t="n">
         <f aca="false">IF(M30="","",IF(I30="과세",IF(L30="VAT포함",M30-N30,ROUND(N30*설정!$C$5,0)),0))</f>
@@ -6673,7 +6991,7 @@
       </c>
       <c r="P30" s="8" t="n">
         <f aca="false">IF(M30="","",N30+O30)</f>
-        <v>2530000</v>
+        <v>2256796</v>
       </c>
       <c r="Q30" s="26"/>
       <c r="R30" s="8" t="str">
@@ -6681,7 +6999,7 @@
         <v/>
       </c>
       <c r="S30" s="25" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6690,7 +7008,7 @@
         <v>27</v>
       </c>
       <c r="B31" s="22" t="n">
-        <v>46288</v>
+        <v>46268</v>
       </c>
       <c r="C31" s="23" t="s">
         <v>21</v>
@@ -6704,26 +7022,26 @@
         <v/>
       </c>
       <c r="G31" s="25"/>
-      <c r="H31" s="25" t="s">
-        <v>87</v>
+      <c r="H31" s="23" t="s">
+        <v>77</v>
       </c>
       <c r="I31" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J31" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K31" s="27" t="n">
-        <v>16651957</v>
+        <v>9174000</v>
       </c>
       <c r="L31" s="26"/>
       <c r="M31" s="8" t="n">
         <f aca="false">IF(K31="","",IF(J31="USD",ROUND(K31*설정!$C$4,0),K31))</f>
-        <v>16651957</v>
+        <v>9174000</v>
       </c>
       <c r="N31" s="8" t="n">
         <f aca="false">IF(M31="","",IF(AND(I31="과세",L31="VAT포함"),ROUND(M31/(1+설정!$C$5),0),M31))</f>
-        <v>16651957</v>
+        <v>9174000</v>
       </c>
       <c r="O31" s="8" t="n">
         <f aca="false">IF(M31="","",IF(I31="과세",IF(L31="VAT포함",M31-N31,ROUND(N31*설정!$C$5,0)),0))</f>
@@ -6731,7 +7049,7 @@
       </c>
       <c r="P31" s="8" t="n">
         <f aca="false">IF(M31="","",N31+O31)</f>
-        <v>16651957</v>
+        <v>9174000</v>
       </c>
       <c r="Q31" s="26"/>
       <c r="R31" s="8" t="str">
@@ -6739,7 +7057,7 @@
         <v/>
       </c>
       <c r="S31" s="25" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6748,7 +7066,7 @@
         <v>28</v>
       </c>
       <c r="B32" s="22" t="n">
-        <v>46288</v>
+        <v>46268</v>
       </c>
       <c r="C32" s="23" t="s">
         <v>21</v>
@@ -6762,26 +7080,26 @@
         <v/>
       </c>
       <c r="G32" s="25"/>
-      <c r="H32" s="25" t="s">
-        <v>89</v>
+      <c r="H32" s="23" t="s">
+        <v>79</v>
       </c>
       <c r="I32" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J32" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K32" s="27" t="n">
-        <v>5290660</v>
+        <v>4400000</v>
       </c>
       <c r="L32" s="26"/>
       <c r="M32" s="8" t="n">
         <f aca="false">IF(K32="","",IF(J32="USD",ROUND(K32*설정!$C$4,0),K32))</f>
-        <v>5290660</v>
+        <v>4400000</v>
       </c>
       <c r="N32" s="8" t="n">
         <f aca="false">IF(M32="","",IF(AND(I32="과세",L32="VAT포함"),ROUND(M32/(1+설정!$C$5),0),M32))</f>
-        <v>5290660</v>
+        <v>4400000</v>
       </c>
       <c r="O32" s="8" t="n">
         <f aca="false">IF(M32="","",IF(I32="과세",IF(L32="VAT포함",M32-N32,ROUND(N32*설정!$C$5,0)),0))</f>
@@ -6789,7 +7107,7 @@
       </c>
       <c r="P32" s="8" t="n">
         <f aca="false">IF(M32="","",N32+O32)</f>
-        <v>5290660</v>
+        <v>4400000</v>
       </c>
       <c r="Q32" s="26"/>
       <c r="R32" s="8" t="str">
@@ -6797,7 +7115,7 @@
         <v/>
       </c>
       <c r="S32" s="25" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6806,7 +7124,7 @@
         <v>29</v>
       </c>
       <c r="B33" s="22" t="n">
-        <v>46288</v>
+        <v>46268</v>
       </c>
       <c r="C33" s="23" t="s">
         <v>21</v>
@@ -6821,25 +7139,25 @@
       </c>
       <c r="G33" s="25"/>
       <c r="H33" s="25" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I33" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J33" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K33" s="27" t="n">
-        <v>4002720</v>
+        <v>1581045</v>
       </c>
       <c r="L33" s="26"/>
       <c r="M33" s="8" t="n">
         <f aca="false">IF(K33="","",IF(J33="USD",ROUND(K33*설정!$C$4,0),K33))</f>
-        <v>4002720</v>
+        <v>1581045</v>
       </c>
       <c r="N33" s="8" t="n">
         <f aca="false">IF(M33="","",IF(AND(I33="과세",L33="VAT포함"),ROUND(M33/(1+설정!$C$5),0),M33))</f>
-        <v>4002720</v>
+        <v>1581045</v>
       </c>
       <c r="O33" s="8" t="n">
         <f aca="false">IF(M33="","",IF(I33="과세",IF(L33="VAT포함",M33-N33,ROUND(N33*설정!$C$5,0)),0))</f>
@@ -6847,7 +7165,7 @@
       </c>
       <c r="P33" s="8" t="n">
         <f aca="false">IF(M33="","",N33+O33)</f>
-        <v>4002720</v>
+        <v>1581045</v>
       </c>
       <c r="Q33" s="26"/>
       <c r="R33" s="8" t="str">
@@ -6855,7 +7173,7 @@
         <v/>
       </c>
       <c r="S33" s="25" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6864,7 +7182,7 @@
         <v>30</v>
       </c>
       <c r="B34" s="22" t="n">
-        <v>46288</v>
+        <v>46268</v>
       </c>
       <c r="C34" s="23" t="s">
         <v>21</v>
@@ -6879,25 +7197,25 @@
       </c>
       <c r="G34" s="25"/>
       <c r="H34" s="25" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I34" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J34" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K34" s="27" t="n">
-        <v>5168440</v>
+        <v>1100000</v>
       </c>
       <c r="L34" s="26"/>
       <c r="M34" s="8" t="n">
         <f aca="false">IF(K34="","",IF(J34="USD",ROUND(K34*설정!$C$4,0),K34))</f>
-        <v>5168440</v>
+        <v>1100000</v>
       </c>
       <c r="N34" s="8" t="n">
         <f aca="false">IF(M34="","",IF(AND(I34="과세",L34="VAT포함"),ROUND(M34/(1+설정!$C$5),0),M34))</f>
-        <v>5168440</v>
+        <v>1100000</v>
       </c>
       <c r="O34" s="8" t="n">
         <f aca="false">IF(M34="","",IF(I34="과세",IF(L34="VAT포함",M34-N34,ROUND(N34*설정!$C$5,0)),0))</f>
@@ -6905,7 +7223,7 @@
       </c>
       <c r="P34" s="8" t="n">
         <f aca="false">IF(M34="","",N34+O34)</f>
-        <v>5168440</v>
+        <v>1100000</v>
       </c>
       <c r="Q34" s="26"/>
       <c r="R34" s="8" t="str">
@@ -6913,7 +7231,7 @@
         <v/>
       </c>
       <c r="S34" s="25" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6922,7 +7240,7 @@
         <v>31</v>
       </c>
       <c r="B35" s="22" t="n">
-        <v>46288</v>
+        <v>46268</v>
       </c>
       <c r="C35" s="23" t="s">
         <v>21</v>
@@ -6937,25 +7255,25 @@
       </c>
       <c r="G35" s="25"/>
       <c r="H35" s="25" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I35" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J35" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K35" s="27" t="n">
-        <v>27402775</v>
+        <v>981600</v>
       </c>
       <c r="L35" s="26"/>
       <c r="M35" s="8" t="n">
         <f aca="false">IF(K35="","",IF(J35="USD",ROUND(K35*설정!$C$4,0),K35))</f>
-        <v>27402775</v>
+        <v>981600</v>
       </c>
       <c r="N35" s="8" t="n">
         <f aca="false">IF(M35="","",IF(AND(I35="과세",L35="VAT포함"),ROUND(M35/(1+설정!$C$5),0),M35))</f>
-        <v>27402775</v>
+        <v>981600</v>
       </c>
       <c r="O35" s="8" t="n">
         <f aca="false">IF(M35="","",IF(I35="과세",IF(L35="VAT포함",M35-N35,ROUND(N35*설정!$C$5,0)),0))</f>
@@ -6963,7 +7281,7 @@
       </c>
       <c r="P35" s="8" t="n">
         <f aca="false">IF(M35="","",N35+O35)</f>
-        <v>27402775</v>
+        <v>981600</v>
       </c>
       <c r="Q35" s="26"/>
       <c r="R35" s="8" t="str">
@@ -6971,7 +7289,7 @@
         <v/>
       </c>
       <c r="S35" s="25" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6979,12 +7297,14 @@
         <f aca="false">IF(C36="","",COUNTA($C$5:C36))</f>
         <v>32</v>
       </c>
-      <c r="B36" s="22"/>
+      <c r="B36" s="22" t="n">
+        <v>46268</v>
+      </c>
       <c r="C36" s="23" t="s">
         <v>21</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E36" s="25"/>
       <c r="F36" s="7" t="str">
@@ -6993,25 +7313,25 @@
       </c>
       <c r="G36" s="25"/>
       <c r="H36" s="25" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="I36" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J36" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K36" s="27" t="n">
-        <v>1789400</v>
+        <v>1258180</v>
       </c>
       <c r="L36" s="26"/>
       <c r="M36" s="8" t="n">
         <f aca="false">IF(K36="","",IF(J36="USD",ROUND(K36*설정!$C$4,0),K36))</f>
-        <v>1789400</v>
+        <v>1258180</v>
       </c>
       <c r="N36" s="8" t="n">
         <f aca="false">IF(M36="","",IF(AND(I36="과세",L36="VAT포함"),ROUND(M36/(1+설정!$C$5),0),M36))</f>
-        <v>1789400</v>
+        <v>1258180</v>
       </c>
       <c r="O36" s="8" t="n">
         <f aca="false">IF(M36="","",IF(I36="과세",IF(L36="VAT포함",M36-N36,ROUND(N36*설정!$C$5,0)),0))</f>
@@ -7019,21 +7339,25 @@
       </c>
       <c r="P36" s="8" t="n">
         <f aca="false">IF(M36="","",N36+O36)</f>
-        <v>1789400</v>
+        <v>1258180</v>
       </c>
       <c r="Q36" s="26"/>
       <c r="R36" s="8" t="str">
         <f aca="false">IF(OR(M36="",Q36&lt;&gt;"Y"),"",ROUND(N36*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S36" s="25"/>
+      <c r="S36" s="25" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="n">
         <f aca="false">IF(C37="","",COUNTA($C$5:C37))</f>
         <v>33</v>
       </c>
-      <c r="B37" s="22"/>
+      <c r="B37" s="22" t="n">
+        <v>46268</v>
+      </c>
       <c r="C37" s="23" t="s">
         <v>21</v>
       </c>
@@ -7046,26 +7370,26 @@
         <v/>
       </c>
       <c r="G37" s="25"/>
-      <c r="H37" s="25" t="s">
-        <v>94</v>
+      <c r="H37" s="23" t="s">
+        <v>77</v>
       </c>
       <c r="I37" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J37" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K37" s="27" t="n">
-        <v>5381313</v>
+        <v>9174000</v>
       </c>
       <c r="L37" s="26"/>
       <c r="M37" s="8" t="n">
         <f aca="false">IF(K37="","",IF(J37="USD",ROUND(K37*설정!$C$4,0),K37))</f>
-        <v>5381313</v>
+        <v>9174000</v>
       </c>
       <c r="N37" s="8" t="n">
         <f aca="false">IF(M37="","",IF(AND(I37="과세",L37="VAT포함"),ROUND(M37/(1+설정!$C$5),0),M37))</f>
-        <v>5381313</v>
+        <v>9174000</v>
       </c>
       <c r="O37" s="8" t="n">
         <f aca="false">IF(M37="","",IF(I37="과세",IF(L37="VAT포함",M37-N37,ROUND(N37*설정!$C$5,0)),0))</f>
@@ -7073,21 +7397,25 @@
       </c>
       <c r="P37" s="8" t="n">
         <f aca="false">IF(M37="","",N37+O37)</f>
-        <v>5381313</v>
+        <v>9174000</v>
       </c>
       <c r="Q37" s="26"/>
       <c r="R37" s="8" t="str">
         <f aca="false">IF(OR(M37="",Q37&lt;&gt;"Y"),"",ROUND(N37*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S37" s="25"/>
+      <c r="S37" s="25" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="21" t="n">
         <f aca="false">IF(C38="","",COUNTA($C$5:C38))</f>
         <v>34</v>
       </c>
-      <c r="B38" s="22"/>
+      <c r="B38" s="22" t="n">
+        <v>46268</v>
+      </c>
       <c r="C38" s="23" t="s">
         <v>21</v>
       </c>
@@ -7100,26 +7428,26 @@
         <v/>
       </c>
       <c r="G38" s="25"/>
-      <c r="H38" s="25" t="s">
-        <v>95</v>
+      <c r="H38" s="23" t="s">
+        <v>79</v>
       </c>
       <c r="I38" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J38" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K38" s="27" t="n">
-        <v>17207955</v>
+        <v>4400000</v>
       </c>
       <c r="L38" s="26"/>
       <c r="M38" s="8" t="n">
         <f aca="false">IF(K38="","",IF(J38="USD",ROUND(K38*설정!$C$4,0),K38))</f>
-        <v>17207955</v>
+        <v>4400000</v>
       </c>
       <c r="N38" s="8" t="n">
         <f aca="false">IF(M38="","",IF(AND(I38="과세",L38="VAT포함"),ROUND(M38/(1+설정!$C$5),0),M38))</f>
-        <v>17207955</v>
+        <v>4400000</v>
       </c>
       <c r="O38" s="8" t="n">
         <f aca="false">IF(M38="","",IF(I38="과세",IF(L38="VAT포함",M38-N38,ROUND(N38*설정!$C$5,0)),0))</f>
@@ -7127,21 +7455,25 @@
       </c>
       <c r="P38" s="8" t="n">
         <f aca="false">IF(M38="","",N38+O38)</f>
-        <v>17207955</v>
+        <v>4400000</v>
       </c>
       <c r="Q38" s="26"/>
       <c r="R38" s="8" t="str">
         <f aca="false">IF(OR(M38="",Q38&lt;&gt;"Y"),"",ROUND(N38*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S38" s="25"/>
+      <c r="S38" s="25" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="21" t="n">
         <f aca="false">IF(C39="","",COUNTA($C$5:C39))</f>
         <v>35</v>
       </c>
-      <c r="B39" s="22"/>
+      <c r="B39" s="22" t="n">
+        <v>46268</v>
+      </c>
       <c r="C39" s="23" t="s">
         <v>21</v>
       </c>
@@ -7155,25 +7487,25 @@
       </c>
       <c r="G39" s="25"/>
       <c r="H39" s="25" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I39" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J39" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K39" s="27" t="n">
-        <v>14285290</v>
+        <v>1581045</v>
       </c>
       <c r="L39" s="26"/>
       <c r="M39" s="8" t="n">
         <f aca="false">IF(K39="","",IF(J39="USD",ROUND(K39*설정!$C$4,0),K39))</f>
-        <v>14285290</v>
+        <v>1581045</v>
       </c>
       <c r="N39" s="8" t="n">
         <f aca="false">IF(M39="","",IF(AND(I39="과세",L39="VAT포함"),ROUND(M39/(1+설정!$C$5),0),M39))</f>
-        <v>14285290</v>
+        <v>1581045</v>
       </c>
       <c r="O39" s="8" t="n">
         <f aca="false">IF(M39="","",IF(I39="과세",IF(L39="VAT포함",M39-N39,ROUND(N39*설정!$C$5,0)),0))</f>
@@ -7181,21 +7513,25 @@
       </c>
       <c r="P39" s="8" t="n">
         <f aca="false">IF(M39="","",N39+O39)</f>
-        <v>14285290</v>
+        <v>1581045</v>
       </c>
       <c r="Q39" s="26"/>
       <c r="R39" s="8" t="str">
         <f aca="false">IF(OR(M39="",Q39&lt;&gt;"Y"),"",ROUND(N39*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S39" s="25"/>
+      <c r="S39" s="25" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="21" t="n">
         <f aca="false">IF(C40="","",COUNTA($C$5:C40))</f>
         <v>36</v>
       </c>
-      <c r="B40" s="22"/>
+      <c r="B40" s="22" t="n">
+        <v>46268</v>
+      </c>
       <c r="C40" s="23" t="s">
         <v>21</v>
       </c>
@@ -7209,25 +7545,25 @@
       </c>
       <c r="G40" s="25"/>
       <c r="H40" s="25" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="I40" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J40" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K40" s="27" t="n">
-        <v>1391500</v>
+        <v>1100000</v>
       </c>
       <c r="L40" s="26"/>
       <c r="M40" s="8" t="n">
         <f aca="false">IF(K40="","",IF(J40="USD",ROUND(K40*설정!$C$4,0),K40))</f>
-        <v>1391500</v>
+        <v>1100000</v>
       </c>
       <c r="N40" s="8" t="n">
         <f aca="false">IF(M40="","",IF(AND(I40="과세",L40="VAT포함"),ROUND(M40/(1+설정!$C$5),0),M40))</f>
-        <v>1391500</v>
+        <v>1100000</v>
       </c>
       <c r="O40" s="8" t="n">
         <f aca="false">IF(M40="","",IF(I40="과세",IF(L40="VAT포함",M40-N40,ROUND(N40*설정!$C$5,0)),0))</f>
@@ -7235,21 +7571,25 @@
       </c>
       <c r="P40" s="8" t="n">
         <f aca="false">IF(M40="","",N40+O40)</f>
-        <v>1391500</v>
+        <v>1100000</v>
       </c>
       <c r="Q40" s="26"/>
       <c r="R40" s="8" t="str">
         <f aca="false">IF(OR(M40="",Q40&lt;&gt;"Y"),"",ROUND(N40*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S40" s="25"/>
+      <c r="S40" s="25" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="21" t="n">
         <f aca="false">IF(C41="","",COUNTA($C$5:C41))</f>
         <v>37</v>
       </c>
-      <c r="B41" s="22"/>
+      <c r="B41" s="22" t="n">
+        <v>46268</v>
+      </c>
       <c r="C41" s="23" t="s">
         <v>21</v>
       </c>
@@ -7263,25 +7603,25 @@
       </c>
       <c r="G41" s="25"/>
       <c r="H41" s="25" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="I41" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J41" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K41" s="27" t="n">
-        <v>5001335</v>
+        <v>981600</v>
       </c>
       <c r="L41" s="26"/>
       <c r="M41" s="8" t="n">
         <f aca="false">IF(K41="","",IF(J41="USD",ROUND(K41*설정!$C$4,0),K41))</f>
-        <v>5001335</v>
+        <v>981600</v>
       </c>
       <c r="N41" s="8" t="n">
         <f aca="false">IF(M41="","",IF(AND(I41="과세",L41="VAT포함"),ROUND(M41/(1+설정!$C$5),0),M41))</f>
-        <v>5001335</v>
+        <v>981600</v>
       </c>
       <c r="O41" s="8" t="n">
         <f aca="false">IF(M41="","",IF(I41="과세",IF(L41="VAT포함",M41-N41,ROUND(N41*설정!$C$5,0)),0))</f>
@@ -7289,21 +7629,25 @@
       </c>
       <c r="P41" s="8" t="n">
         <f aca="false">IF(M41="","",N41+O41)</f>
-        <v>5001335</v>
+        <v>981600</v>
       </c>
       <c r="Q41" s="26"/>
       <c r="R41" s="8" t="str">
         <f aca="false">IF(OR(M41="",Q41&lt;&gt;"Y"),"",ROUND(N41*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S41" s="25"/>
+      <c r="S41" s="25" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="21" t="n">
         <f aca="false">IF(C42="","",COUNTA($C$5:C42))</f>
         <v>38</v>
       </c>
-      <c r="B42" s="22"/>
+      <c r="B42" s="22" t="n">
+        <v>46268</v>
+      </c>
       <c r="C42" s="23" t="s">
         <v>21</v>
       </c>
@@ -7317,25 +7661,25 @@
       </c>
       <c r="G42" s="25"/>
       <c r="H42" s="25" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="I42" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J42" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K42" s="27" t="n">
-        <v>3380000</v>
+        <v>2256796</v>
       </c>
       <c r="L42" s="26"/>
       <c r="M42" s="8" t="n">
         <f aca="false">IF(K42="","",IF(J42="USD",ROUND(K42*설정!$C$4,0),K42))</f>
-        <v>3380000</v>
+        <v>2256796</v>
       </c>
       <c r="N42" s="8" t="n">
         <f aca="false">IF(M42="","",IF(AND(I42="과세",L42="VAT포함"),ROUND(M42/(1+설정!$C$5),0),M42))</f>
-        <v>3380000</v>
+        <v>2256796</v>
       </c>
       <c r="O42" s="8" t="n">
         <f aca="false">IF(M42="","",IF(I42="과세",IF(L42="VAT포함",M42-N42,ROUND(N42*설정!$C$5,0)),0))</f>
@@ -7343,21 +7687,25 @@
       </c>
       <c r="P42" s="8" t="n">
         <f aca="false">IF(M42="","",N42+O42)</f>
-        <v>3380000</v>
+        <v>2256796</v>
       </c>
       <c r="Q42" s="26"/>
       <c r="R42" s="8" t="str">
         <f aca="false">IF(OR(M42="",Q42&lt;&gt;"Y"),"",ROUND(N42*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S42" s="25"/>
+      <c r="S42" s="25" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="21" t="n">
         <f aca="false">IF(C43="","",COUNTA($C$5:C43))</f>
         <v>39</v>
       </c>
-      <c r="B43" s="22"/>
+      <c r="B43" s="22" t="n">
+        <v>46268</v>
+      </c>
       <c r="C43" s="23" t="s">
         <v>21</v>
       </c>
@@ -7370,26 +7718,26 @@
         <v/>
       </c>
       <c r="G43" s="25"/>
-      <c r="H43" s="25" t="s">
-        <v>99</v>
+      <c r="H43" s="23" t="s">
+        <v>77</v>
       </c>
       <c r="I43" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J43" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K43" s="27" t="n">
-        <v>6129745</v>
+        <v>9174000</v>
       </c>
       <c r="L43" s="26"/>
       <c r="M43" s="8" t="n">
         <f aca="false">IF(K43="","",IF(J43="USD",ROUND(K43*설정!$C$4,0),K43))</f>
-        <v>6129745</v>
+        <v>9174000</v>
       </c>
       <c r="N43" s="8" t="n">
         <f aca="false">IF(M43="","",IF(AND(I43="과세",L43="VAT포함"),ROUND(M43/(1+설정!$C$5),0),M43))</f>
-        <v>6129745</v>
+        <v>9174000</v>
       </c>
       <c r="O43" s="8" t="n">
         <f aca="false">IF(M43="","",IF(I43="과세",IF(L43="VAT포함",M43-N43,ROUND(N43*설정!$C$5,0)),0))</f>
@@ -7397,21 +7745,25 @@
       </c>
       <c r="P43" s="8" t="n">
         <f aca="false">IF(M43="","",N43+O43)</f>
-        <v>6129745</v>
+        <v>9174000</v>
       </c>
       <c r="Q43" s="26"/>
       <c r="R43" s="8" t="str">
         <f aca="false">IF(OR(M43="",Q43&lt;&gt;"Y"),"",ROUND(N43*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S43" s="25"/>
+      <c r="S43" s="25" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="21" t="n">
         <f aca="false">IF(C44="","",COUNTA($C$5:C44))</f>
         <v>40</v>
       </c>
-      <c r="B44" s="22"/>
+      <c r="B44" s="22" t="n">
+        <v>46268</v>
+      </c>
       <c r="C44" s="23" t="s">
         <v>21</v>
       </c>
@@ -7424,26 +7776,26 @@
         <v/>
       </c>
       <c r="G44" s="25"/>
-      <c r="H44" s="25" t="s">
-        <v>100</v>
+      <c r="H44" s="23" t="s">
+        <v>79</v>
       </c>
       <c r="I44" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J44" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K44" s="27" t="n">
-        <v>3762800</v>
+        <v>4400000</v>
       </c>
       <c r="L44" s="26"/>
       <c r="M44" s="8" t="n">
         <f aca="false">IF(K44="","",IF(J44="USD",ROUND(K44*설정!$C$4,0),K44))</f>
-        <v>3762800</v>
+        <v>4400000</v>
       </c>
       <c r="N44" s="8" t="n">
         <f aca="false">IF(M44="","",IF(AND(I44="과세",L44="VAT포함"),ROUND(M44/(1+설정!$C$5),0),M44))</f>
-        <v>3762800</v>
+        <v>4400000</v>
       </c>
       <c r="O44" s="8" t="n">
         <f aca="false">IF(M44="","",IF(I44="과세",IF(L44="VAT포함",M44-N44,ROUND(N44*설정!$C$5,0)),0))</f>
@@ -7451,21 +7803,25 @@
       </c>
       <c r="P44" s="8" t="n">
         <f aca="false">IF(M44="","",N44+O44)</f>
-        <v>3762800</v>
+        <v>4400000</v>
       </c>
       <c r="Q44" s="26"/>
       <c r="R44" s="8" t="str">
         <f aca="false">IF(OR(M44="",Q44&lt;&gt;"Y"),"",ROUND(N44*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S44" s="25"/>
+      <c r="S44" s="25" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="21" t="n">
         <f aca="false">IF(C45="","",COUNTA($C$5:C45))</f>
         <v>41</v>
       </c>
-      <c r="B45" s="22"/>
+      <c r="B45" s="22" t="n">
+        <v>46268</v>
+      </c>
       <c r="C45" s="23" t="s">
         <v>21</v>
       </c>
@@ -7479,25 +7835,25 @@
       </c>
       <c r="G45" s="25"/>
       <c r="H45" s="25" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="I45" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J45" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K45" s="27" t="n">
-        <v>1997232</v>
+        <v>1600245</v>
       </c>
       <c r="L45" s="26"/>
       <c r="M45" s="8" t="n">
         <f aca="false">IF(K45="","",IF(J45="USD",ROUND(K45*설정!$C$4,0),K45))</f>
-        <v>1997232</v>
+        <v>1600245</v>
       </c>
       <c r="N45" s="8" t="n">
         <f aca="false">IF(M45="","",IF(AND(I45="과세",L45="VAT포함"),ROUND(M45/(1+설정!$C$5),0),M45))</f>
-        <v>1997232</v>
+        <v>1600245</v>
       </c>
       <c r="O45" s="8" t="n">
         <f aca="false">IF(M45="","",IF(I45="과세",IF(L45="VAT포함",M45-N45,ROUND(N45*설정!$C$5,0)),0))</f>
@@ -7505,21 +7861,25 @@
       </c>
       <c r="P45" s="8" t="n">
         <f aca="false">IF(M45="","",N45+O45)</f>
-        <v>1997232</v>
+        <v>1600245</v>
       </c>
       <c r="Q45" s="26"/>
       <c r="R45" s="8" t="str">
         <f aca="false">IF(OR(M45="",Q45&lt;&gt;"Y"),"",ROUND(N45*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S45" s="25"/>
+      <c r="S45" s="25" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="21" t="n">
         <f aca="false">IF(C46="","",COUNTA($C$5:C46))</f>
         <v>42</v>
       </c>
-      <c r="B46" s="22"/>
+      <c r="B46" s="22" t="n">
+        <v>46268</v>
+      </c>
       <c r="C46" s="23" t="s">
         <v>21</v>
       </c>
@@ -7533,25 +7893,25 @@
       </c>
       <c r="G46" s="25"/>
       <c r="H46" s="25" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="I46" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J46" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K46" s="27" t="n">
-        <v>30800</v>
+        <v>1100000</v>
       </c>
       <c r="L46" s="26"/>
       <c r="M46" s="8" t="n">
         <f aca="false">IF(K46="","",IF(J46="USD",ROUND(K46*설정!$C$4,0),K46))</f>
-        <v>30800</v>
+        <v>1100000</v>
       </c>
       <c r="N46" s="8" t="n">
         <f aca="false">IF(M46="","",IF(AND(I46="과세",L46="VAT포함"),ROUND(M46/(1+설정!$C$5),0),M46))</f>
-        <v>30800</v>
+        <v>1100000</v>
       </c>
       <c r="O46" s="8" t="n">
         <f aca="false">IF(M46="","",IF(I46="과세",IF(L46="VAT포함",M46-N46,ROUND(N46*설정!$C$5,0)),0))</f>
@@ -7559,21 +7919,25 @@
       </c>
       <c r="P46" s="8" t="n">
         <f aca="false">IF(M46="","",N46+O46)</f>
-        <v>30800</v>
+        <v>1100000</v>
       </c>
       <c r="Q46" s="26"/>
       <c r="R46" s="8" t="str">
         <f aca="false">IF(OR(M46="",Q46&lt;&gt;"Y"),"",ROUND(N46*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S46" s="25"/>
+      <c r="S46" s="25" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="21" t="n">
         <f aca="false">IF(C47="","",COUNTA($C$5:C47))</f>
         <v>43</v>
       </c>
-      <c r="B47" s="22"/>
+      <c r="B47" s="22" t="n">
+        <v>46268</v>
+      </c>
       <c r="C47" s="23" t="s">
         <v>21</v>
       </c>
@@ -7587,25 +7951,25 @@
       </c>
       <c r="G47" s="25"/>
       <c r="H47" s="25" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I47" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J47" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K47" s="27" t="n">
-        <v>2029300</v>
+        <v>981600</v>
       </c>
       <c r="L47" s="26"/>
       <c r="M47" s="8" t="n">
         <f aca="false">IF(K47="","",IF(J47="USD",ROUND(K47*설정!$C$4,0),K47))</f>
-        <v>2029300</v>
+        <v>981600</v>
       </c>
       <c r="N47" s="8" t="n">
         <f aca="false">IF(M47="","",IF(AND(I47="과세",L47="VAT포함"),ROUND(M47/(1+설정!$C$5),0),M47))</f>
-        <v>2029300</v>
+        <v>981600</v>
       </c>
       <c r="O47" s="8" t="n">
         <f aca="false">IF(M47="","",IF(I47="과세",IF(L47="VAT포함",M47-N47,ROUND(N47*설정!$C$5,0)),0))</f>
@@ -7613,21 +7977,25 @@
       </c>
       <c r="P47" s="8" t="n">
         <f aca="false">IF(M47="","",N47+O47)</f>
-        <v>2029300</v>
+        <v>981600</v>
       </c>
       <c r="Q47" s="26"/>
       <c r="R47" s="8" t="str">
         <f aca="false">IF(OR(M47="",Q47&lt;&gt;"Y"),"",ROUND(N47*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S47" s="25"/>
+      <c r="S47" s="25" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="21" t="n">
         <f aca="false">IF(C48="","",COUNTA($C$5:C48))</f>
         <v>44</v>
       </c>
-      <c r="B48" s="22"/>
+      <c r="B48" s="22" t="n">
+        <v>46268</v>
+      </c>
       <c r="C48" s="23" t="s">
         <v>21</v>
       </c>
@@ -7641,25 +8009,25 @@
       </c>
       <c r="G48" s="25"/>
       <c r="H48" s="25" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="I48" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J48" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K48" s="27" t="n">
-        <v>41976</v>
+        <v>1091744</v>
       </c>
       <c r="L48" s="26"/>
       <c r="M48" s="8" t="n">
         <f aca="false">IF(K48="","",IF(J48="USD",ROUND(K48*설정!$C$4,0),K48))</f>
-        <v>41976</v>
+        <v>1091744</v>
       </c>
       <c r="N48" s="8" t="n">
         <f aca="false">IF(M48="","",IF(AND(I48="과세",L48="VAT포함"),ROUND(M48/(1+설정!$C$5),0),M48))</f>
-        <v>41976</v>
+        <v>1091744</v>
       </c>
       <c r="O48" s="8" t="n">
         <f aca="false">IF(M48="","",IF(I48="과세",IF(L48="VAT포함",M48-N48,ROUND(N48*설정!$C$5,0)),0))</f>
@@ -7667,26 +8035,30 @@
       </c>
       <c r="P48" s="8" t="n">
         <f aca="false">IF(M48="","",N48+O48)</f>
-        <v>41976</v>
+        <v>1091744</v>
       </c>
       <c r="Q48" s="26"/>
       <c r="R48" s="8" t="str">
         <f aca="false">IF(OR(M48="",Q48&lt;&gt;"Y"),"",ROUND(N48*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S48" s="25"/>
+      <c r="S48" s="25" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="21" t="n">
         <f aca="false">IF(C49="","",COUNTA($C$5:C49))</f>
         <v>45</v>
       </c>
-      <c r="B49" s="22"/>
+      <c r="B49" s="22" t="n">
+        <v>46282</v>
+      </c>
       <c r="C49" s="23" t="s">
         <v>21</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E49" s="25"/>
       <c r="F49" s="7" t="str">
@@ -7694,26 +8066,26 @@
         <v/>
       </c>
       <c r="G49" s="25"/>
-      <c r="H49" s="25" t="s">
-        <v>103</v>
+      <c r="H49" s="23" t="s">
+        <v>84</v>
       </c>
       <c r="I49" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J49" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K49" s="27" t="n">
-        <v>1050000</v>
+        <v>241500</v>
       </c>
       <c r="L49" s="26"/>
       <c r="M49" s="8" t="n">
         <f aca="false">IF(K49="","",IF(J49="USD",ROUND(K49*설정!$C$4,0),K49))</f>
-        <v>1050000</v>
+        <v>241500</v>
       </c>
       <c r="N49" s="8" t="n">
         <f aca="false">IF(M49="","",IF(AND(I49="과세",L49="VAT포함"),ROUND(M49/(1+설정!$C$5),0),M49))</f>
-        <v>1050000</v>
+        <v>241500</v>
       </c>
       <c r="O49" s="8" t="n">
         <f aca="false">IF(M49="","",IF(I49="과세",IF(L49="VAT포함",M49-N49,ROUND(N49*설정!$C$5,0)),0))</f>
@@ -7721,23 +8093,27 @@
       </c>
       <c r="P49" s="8" t="n">
         <f aca="false">IF(M49="","",N49+O49)</f>
-        <v>1050000</v>
+        <v>241500</v>
       </c>
       <c r="Q49" s="26"/>
       <c r="R49" s="8" t="str">
         <f aca="false">IF(OR(M49="",Q49&lt;&gt;"Y"),"",ROUND(N49*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S49" s="25"/>
+      <c r="S49" s="23" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="21" t="n">
         <f aca="false">IF(C50="","",COUNTA($C$5:C50))</f>
         <v>46</v>
       </c>
-      <c r="B50" s="22"/>
+      <c r="B50" s="22" t="n">
+        <v>46295</v>
+      </c>
       <c r="C50" s="23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D50" s="26" t="s">
         <v>4</v>
@@ -7748,26 +8124,26 @@
         <v/>
       </c>
       <c r="G50" s="25"/>
-      <c r="H50" s="23" t="s">
-        <v>104</v>
+      <c r="H50" s="25" t="s">
+        <v>74</v>
       </c>
       <c r="I50" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J50" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K50" s="27" t="n">
-        <v>28656495</v>
+        <v>20700000</v>
       </c>
       <c r="L50" s="26"/>
       <c r="M50" s="8" t="n">
         <f aca="false">IF(K50="","",IF(J50="USD",ROUND(K50*설정!$C$4,0),K50))</f>
-        <v>28656495</v>
+        <v>20700000</v>
       </c>
       <c r="N50" s="8" t="n">
         <f aca="false">IF(M50="","",IF(AND(I50="과세",L50="VAT포함"),ROUND(M50/(1+설정!$C$5),0),M50))</f>
-        <v>28656495</v>
+        <v>20700000</v>
       </c>
       <c r="O50" s="8" t="n">
         <f aca="false">IF(M50="","",IF(I50="과세",IF(L50="VAT포함",M50-N50,ROUND(N50*설정!$C$5,0)),0))</f>
@@ -7775,15 +8151,15 @@
       </c>
       <c r="P50" s="8" t="n">
         <f aca="false">IF(M50="","",N50+O50)</f>
-        <v>28656495</v>
+        <v>20700000</v>
       </c>
       <c r="Q50" s="26"/>
       <c r="R50" s="8" t="str">
         <f aca="false">IF(OR(M50="",Q50&lt;&gt;"Y"),"",ROUND(N50*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S50" s="23" t="s">
-        <v>105</v>
+      <c r="S50" s="25" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7791,12 +8167,14 @@
         <f aca="false">IF(C51="","",COUNTA($C$5:C51))</f>
         <v>47</v>
       </c>
-      <c r="B51" s="22"/>
+      <c r="B51" s="22" t="n">
+        <v>46295</v>
+      </c>
       <c r="C51" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D51" s="26" t="s">
-        <v>4</v>
+        <v>21</v>
+      </c>
+      <c r="D51" s="24" t="s">
+        <v>57</v>
       </c>
       <c r="E51" s="25"/>
       <c r="F51" s="7" t="str">
@@ -7805,25 +8183,25 @@
       </c>
       <c r="G51" s="25"/>
       <c r="H51" s="23" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="I51" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J51" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K51" s="27" t="n">
-        <v>5146892</v>
+        <v>531300</v>
       </c>
       <c r="L51" s="26"/>
       <c r="M51" s="8" t="n">
         <f aca="false">IF(K51="","",IF(J51="USD",ROUND(K51*설정!$C$4,0),K51))</f>
-        <v>5146892</v>
+        <v>531300</v>
       </c>
       <c r="N51" s="8" t="n">
         <f aca="false">IF(M51="","",IF(AND(I51="과세",L51="VAT포함"),ROUND(M51/(1+설정!$C$5),0),M51))</f>
-        <v>5146892</v>
+        <v>531300</v>
       </c>
       <c r="O51" s="8" t="n">
         <f aca="false">IF(M51="","",IF(I51="과세",IF(L51="VAT포함",M51-N51,ROUND(N51*설정!$C$5,0)),0))</f>
@@ -7831,15 +8209,15 @@
       </c>
       <c r="P51" s="8" t="n">
         <f aca="false">IF(M51="","",N51+O51)</f>
-        <v>5146892</v>
+        <v>531300</v>
       </c>
       <c r="Q51" s="26"/>
       <c r="R51" s="8" t="str">
         <f aca="false">IF(OR(M51="",Q51&lt;&gt;"Y"),"",ROUND(N51*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S51" s="23" t="s">
-        <v>107</v>
+      <c r="S51" s="25" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7849,10 +8227,10 @@
       </c>
       <c r="B52" s="22"/>
       <c r="C52" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D52" s="26" t="s">
-        <v>4</v>
+        <v>21</v>
+      </c>
+      <c r="D52" s="24" t="s">
+        <v>57</v>
       </c>
       <c r="E52" s="25"/>
       <c r="F52" s="7" t="str">
@@ -7860,26 +8238,26 @@
         <v/>
       </c>
       <c r="G52" s="25"/>
-      <c r="H52" s="23" t="s">
-        <v>108</v>
+      <c r="H52" s="25" t="s">
+        <v>89</v>
       </c>
       <c r="I52" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J52" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K52" s="27" t="n">
-        <v>878683</v>
+        <v>4400000</v>
       </c>
       <c r="L52" s="26"/>
       <c r="M52" s="8" t="n">
         <f aca="false">IF(K52="","",IF(J52="USD",ROUND(K52*설정!$C$4,0),K52))</f>
-        <v>878683</v>
+        <v>4400000</v>
       </c>
       <c r="N52" s="8" t="n">
         <f aca="false">IF(M52="","",IF(AND(I52="과세",L52="VAT포함"),ROUND(M52/(1+설정!$C$5),0),M52))</f>
-        <v>878683</v>
+        <v>4400000</v>
       </c>
       <c r="O52" s="8" t="n">
         <f aca="false">IF(M52="","",IF(I52="과세",IF(L52="VAT포함",M52-N52,ROUND(N52*설정!$C$5,0)),0))</f>
@@ -7887,7 +8265,7 @@
       </c>
       <c r="P52" s="8" t="n">
         <f aca="false">IF(M52="","",N52+O52)</f>
-        <v>878683</v>
+        <v>4400000</v>
       </c>
       <c r="Q52" s="26"/>
       <c r="R52" s="8" t="str">
@@ -7895,7 +8273,7 @@
         <v/>
       </c>
       <c r="S52" s="23" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7905,7 +8283,7 @@
       </c>
       <c r="B53" s="22"/>
       <c r="C53" s="23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D53" s="26" t="s">
         <v>4</v>
@@ -7916,26 +8294,26 @@
         <v/>
       </c>
       <c r="G53" s="25"/>
-      <c r="H53" s="23" t="s">
-        <v>109</v>
+      <c r="H53" s="25" t="s">
+        <v>91</v>
       </c>
       <c r="I53" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J53" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K53" s="27" t="n">
-        <v>1869000</v>
+        <v>20493000</v>
       </c>
       <c r="L53" s="26"/>
       <c r="M53" s="8" t="n">
         <f aca="false">IF(K53="","",IF(J53="USD",ROUND(K53*설정!$C$4,0),K53))</f>
-        <v>1869000</v>
+        <v>20493000</v>
       </c>
       <c r="N53" s="8" t="n">
         <f aca="false">IF(M53="","",IF(AND(I53="과세",L53="VAT포함"),ROUND(M53/(1+설정!$C$5),0),M53))</f>
-        <v>1869000</v>
+        <v>20493000</v>
       </c>
       <c r="O53" s="8" t="n">
         <f aca="false">IF(M53="","",IF(I53="과세",IF(L53="VAT포함",M53-N53,ROUND(N53*설정!$C$5,0)),0))</f>
@@ -7943,15 +8321,15 @@
       </c>
       <c r="P53" s="8" t="n">
         <f aca="false">IF(M53="","",N53+O53)</f>
-        <v>1869000</v>
+        <v>20493000</v>
       </c>
       <c r="Q53" s="26"/>
       <c r="R53" s="8" t="str">
         <f aca="false">IF(OR(M53="",Q53&lt;&gt;"Y"),"",ROUND(N53*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S53" s="23" t="s">
-        <v>107</v>
+      <c r="S53" s="25" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7961,10 +8339,10 @@
       </c>
       <c r="B54" s="22"/>
       <c r="C54" s="23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D54" s="26" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E54" s="25"/>
       <c r="F54" s="7" t="str">
@@ -7972,26 +8350,26 @@
         <v/>
       </c>
       <c r="G54" s="25"/>
-      <c r="H54" s="23" t="s">
-        <v>104</v>
+      <c r="H54" s="25" t="s">
+        <v>93</v>
       </c>
       <c r="I54" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J54" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K54" s="27" t="n">
-        <v>39515305</v>
+        <v>2530000</v>
       </c>
       <c r="L54" s="26"/>
       <c r="M54" s="8" t="n">
         <f aca="false">IF(K54="","",IF(J54="USD",ROUND(K54*설정!$C$4,0),K54))</f>
-        <v>39515305</v>
+        <v>2530000</v>
       </c>
       <c r="N54" s="8" t="n">
         <f aca="false">IF(M54="","",IF(AND(I54="과세",L54="VAT포함"),ROUND(M54/(1+설정!$C$5),0),M54))</f>
-        <v>39515305</v>
+        <v>2530000</v>
       </c>
       <c r="O54" s="8" t="n">
         <f aca="false">IF(M54="","",IF(I54="과세",IF(L54="VAT포함",M54-N54,ROUND(N54*설정!$C$5,0)),0))</f>
@@ -7999,15 +8377,15 @@
       </c>
       <c r="P54" s="8" t="n">
         <f aca="false">IF(M54="","",N54+O54)</f>
-        <v>39515305</v>
+        <v>2530000</v>
       </c>
       <c r="Q54" s="26"/>
       <c r="R54" s="8" t="str">
         <f aca="false">IF(OR(M54="",Q54&lt;&gt;"Y"),"",ROUND(N54*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S54" s="23" t="s">
-        <v>110</v>
+      <c r="S54" s="25" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8015,9 +8393,11 @@
         <f aca="false">IF(C55="","",COUNTA($C$5:C55))</f>
         <v>51</v>
       </c>
-      <c r="B55" s="22"/>
+      <c r="B55" s="22" t="n">
+        <v>46288</v>
+      </c>
       <c r="C55" s="23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D55" s="26" t="s">
         <v>5</v>
@@ -8028,26 +8408,26 @@
         <v/>
       </c>
       <c r="G55" s="25"/>
-      <c r="H55" s="23" t="s">
-        <v>106</v>
+      <c r="H55" s="25" t="s">
+        <v>95</v>
       </c>
       <c r="I55" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J55" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K55" s="27" t="n">
-        <v>5740259</v>
+        <v>16651957</v>
       </c>
       <c r="L55" s="26"/>
       <c r="M55" s="8" t="n">
         <f aca="false">IF(K55="","",IF(J55="USD",ROUND(K55*설정!$C$4,0),K55))</f>
-        <v>5740259</v>
+        <v>16651957</v>
       </c>
       <c r="N55" s="8" t="n">
         <f aca="false">IF(M55="","",IF(AND(I55="과세",L55="VAT포함"),ROUND(M55/(1+설정!$C$5),0),M55))</f>
-        <v>5740259</v>
+        <v>16651957</v>
       </c>
       <c r="O55" s="8" t="n">
         <f aca="false">IF(M55="","",IF(I55="과세",IF(L55="VAT포함",M55-N55,ROUND(N55*설정!$C$5,0)),0))</f>
@@ -8055,15 +8435,15 @@
       </c>
       <c r="P55" s="8" t="n">
         <f aca="false">IF(M55="","",N55+O55)</f>
-        <v>5740259</v>
+        <v>16651957</v>
       </c>
       <c r="Q55" s="26"/>
       <c r="R55" s="8" t="str">
         <f aca="false">IF(OR(M55="",Q55&lt;&gt;"Y"),"",ROUND(N55*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S55" s="23" t="s">
-        <v>107</v>
+      <c r="S55" s="25" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8071,12 +8451,14 @@
         <f aca="false">IF(C56="","",COUNTA($C$5:C56))</f>
         <v>52</v>
       </c>
-      <c r="B56" s="22"/>
+      <c r="B56" s="22" t="n">
+        <v>46288</v>
+      </c>
       <c r="C56" s="23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D56" s="26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E56" s="25"/>
       <c r="F56" s="7" t="str">
@@ -8084,26 +8466,26 @@
         <v/>
       </c>
       <c r="G56" s="25"/>
-      <c r="H56" s="23" t="s">
-        <v>104</v>
+      <c r="H56" s="25" t="s">
+        <v>97</v>
       </c>
       <c r="I56" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J56" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K56" s="27" t="n">
-        <v>48315826</v>
+        <v>5290660</v>
       </c>
       <c r="L56" s="26"/>
       <c r="M56" s="8" t="n">
         <f aca="false">IF(K56="","",IF(J56="USD",ROUND(K56*설정!$C$4,0),K56))</f>
-        <v>48315826</v>
+        <v>5290660</v>
       </c>
       <c r="N56" s="8" t="n">
         <f aca="false">IF(M56="","",IF(AND(I56="과세",L56="VAT포함"),ROUND(M56/(1+설정!$C$5),0),M56))</f>
-        <v>48315826</v>
+        <v>5290660</v>
       </c>
       <c r="O56" s="8" t="n">
         <f aca="false">IF(M56="","",IF(I56="과세",IF(L56="VAT포함",M56-N56,ROUND(N56*설정!$C$5,0)),0))</f>
@@ -8111,15 +8493,15 @@
       </c>
       <c r="P56" s="8" t="n">
         <f aca="false">IF(M56="","",N56+O56)</f>
-        <v>48315826</v>
+        <v>5290660</v>
       </c>
       <c r="Q56" s="26"/>
       <c r="R56" s="8" t="str">
         <f aca="false">IF(OR(M56="",Q56&lt;&gt;"Y"),"",ROUND(N56*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S56" s="23" t="s">
-        <v>111</v>
+      <c r="S56" s="25" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8127,12 +8509,14 @@
         <f aca="false">IF(C57="","",COUNTA($C$5:C57))</f>
         <v>53</v>
       </c>
-      <c r="B57" s="22"/>
+      <c r="B57" s="22" t="n">
+        <v>46288</v>
+      </c>
       <c r="C57" s="23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D57" s="26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E57" s="25"/>
       <c r="F57" s="7" t="str">
@@ -8140,26 +8524,26 @@
         <v/>
       </c>
       <c r="G57" s="25"/>
-      <c r="H57" s="23" t="s">
-        <v>106</v>
+      <c r="H57" s="25" t="s">
+        <v>98</v>
       </c>
       <c r="I57" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J57" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K57" s="27" t="n">
-        <v>9371766</v>
+        <v>4002720</v>
       </c>
       <c r="L57" s="26"/>
       <c r="M57" s="8" t="n">
         <f aca="false">IF(K57="","",IF(J57="USD",ROUND(K57*설정!$C$4,0),K57))</f>
-        <v>9371766</v>
+        <v>4002720</v>
       </c>
       <c r="N57" s="8" t="n">
         <f aca="false">IF(M57="","",IF(AND(I57="과세",L57="VAT포함"),ROUND(M57/(1+설정!$C$5),0),M57))</f>
-        <v>9371766</v>
+        <v>4002720</v>
       </c>
       <c r="O57" s="8" t="n">
         <f aca="false">IF(M57="","",IF(I57="과세",IF(L57="VAT포함",M57-N57,ROUND(N57*설정!$C$5,0)),0))</f>
@@ -8167,15 +8551,15 @@
       </c>
       <c r="P57" s="8" t="n">
         <f aca="false">IF(M57="","",N57+O57)</f>
-        <v>9371766</v>
+        <v>4002720</v>
       </c>
       <c r="Q57" s="26"/>
       <c r="R57" s="8" t="str">
         <f aca="false">IF(OR(M57="",Q57&lt;&gt;"Y"),"",ROUND(N57*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S57" s="23" t="s">
-        <v>107</v>
+      <c r="S57" s="25" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8183,12 +8567,14 @@
         <f aca="false">IF(C58="","",COUNTA($C$5:C58))</f>
         <v>54</v>
       </c>
-      <c r="B58" s="22"/>
+      <c r="B58" s="22" t="n">
+        <v>46288</v>
+      </c>
       <c r="C58" s="23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D58" s="26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E58" s="25"/>
       <c r="F58" s="7" t="str">
@@ -8196,26 +8582,26 @@
         <v/>
       </c>
       <c r="G58" s="25"/>
-      <c r="H58" s="23" t="s">
-        <v>109</v>
+      <c r="H58" s="25" t="s">
+        <v>99</v>
       </c>
       <c r="I58" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J58" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K58" s="27" t="n">
-        <v>1869000</v>
+        <v>5168440</v>
       </c>
       <c r="L58" s="26"/>
       <c r="M58" s="8" t="n">
         <f aca="false">IF(K58="","",IF(J58="USD",ROUND(K58*설정!$C$4,0),K58))</f>
-        <v>1869000</v>
+        <v>5168440</v>
       </c>
       <c r="N58" s="8" t="n">
         <f aca="false">IF(M58="","",IF(AND(I58="과세",L58="VAT포함"),ROUND(M58/(1+설정!$C$5),0),M58))</f>
-        <v>1869000</v>
+        <v>5168440</v>
       </c>
       <c r="O58" s="8" t="n">
         <f aca="false">IF(M58="","",IF(I58="과세",IF(L58="VAT포함",M58-N58,ROUND(N58*설정!$C$5,0)),0))</f>
@@ -8223,15 +8609,15 @@
       </c>
       <c r="P58" s="8" t="n">
         <f aca="false">IF(M58="","",N58+O58)</f>
-        <v>1869000</v>
+        <v>5168440</v>
       </c>
       <c r="Q58" s="26"/>
       <c r="R58" s="8" t="str">
         <f aca="false">IF(OR(M58="",Q58&lt;&gt;"Y"),"",ROUND(N58*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S58" s="23" t="s">
-        <v>107</v>
+      <c r="S58" s="25" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8239,12 +8625,14 @@
         <f aca="false">IF(C59="","",COUNTA($C$5:C59))</f>
         <v>55</v>
       </c>
-      <c r="B59" s="22"/>
+      <c r="B59" s="22" t="n">
+        <v>46288</v>
+      </c>
       <c r="C59" s="23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D59" s="26" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E59" s="25"/>
       <c r="F59" s="7" t="str">
@@ -8252,26 +8640,26 @@
         <v/>
       </c>
       <c r="G59" s="25"/>
-      <c r="H59" s="23" t="s">
-        <v>104</v>
+      <c r="H59" s="25" t="s">
+        <v>100</v>
       </c>
       <c r="I59" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J59" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K59" s="27" t="n">
-        <v>36479048</v>
+        <v>27402775</v>
       </c>
       <c r="L59" s="26"/>
       <c r="M59" s="8" t="n">
         <f aca="false">IF(K59="","",IF(J59="USD",ROUND(K59*설정!$C$4,0),K59))</f>
-        <v>36479048</v>
+        <v>27402775</v>
       </c>
       <c r="N59" s="8" t="n">
         <f aca="false">IF(M59="","",IF(AND(I59="과세",L59="VAT포함"),ROUND(M59/(1+설정!$C$5),0),M59))</f>
-        <v>36479048</v>
+        <v>27402775</v>
       </c>
       <c r="O59" s="8" t="n">
         <f aca="false">IF(M59="","",IF(I59="과세",IF(L59="VAT포함",M59-N59,ROUND(N59*설정!$C$5,0)),0))</f>
@@ -8279,15 +8667,15 @@
       </c>
       <c r="P59" s="8" t="n">
         <f aca="false">IF(M59="","",N59+O59)</f>
-        <v>36479048</v>
+        <v>27402775</v>
       </c>
       <c r="Q59" s="26"/>
       <c r="R59" s="8" t="str">
         <f aca="false">IF(OR(M59="",Q59&lt;&gt;"Y"),"",ROUND(N59*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S59" s="23" t="s">
-        <v>112</v>
+      <c r="S59" s="25" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8297,10 +8685,10 @@
       </c>
       <c r="B60" s="22"/>
       <c r="C60" s="23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D60" s="26" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E60" s="25"/>
       <c r="F60" s="7" t="str">
@@ -8308,26 +8696,26 @@
         <v/>
       </c>
       <c r="G60" s="25"/>
-      <c r="H60" s="23" t="s">
-        <v>106</v>
+      <c r="H60" s="25" t="s">
+        <v>101</v>
       </c>
       <c r="I60" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J60" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K60" s="27" t="n">
-        <v>14223063</v>
+        <v>1789400</v>
       </c>
       <c r="L60" s="26"/>
       <c r="M60" s="8" t="n">
         <f aca="false">IF(K60="","",IF(J60="USD",ROUND(K60*설정!$C$4,0),K60))</f>
-        <v>14223063</v>
+        <v>1789400</v>
       </c>
       <c r="N60" s="8" t="n">
         <f aca="false">IF(M60="","",IF(AND(I60="과세",L60="VAT포함"),ROUND(M60/(1+설정!$C$5),0),M60))</f>
-        <v>14223063</v>
+        <v>1789400</v>
       </c>
       <c r="O60" s="8" t="n">
         <f aca="false">IF(M60="","",IF(I60="과세",IF(L60="VAT포함",M60-N60,ROUND(N60*설정!$C$5,0)),0))</f>
@@ -8335,16 +8723,14 @@
       </c>
       <c r="P60" s="8" t="n">
         <f aca="false">IF(M60="","",N60+O60)</f>
-        <v>14223063</v>
+        <v>1789400</v>
       </c>
       <c r="Q60" s="26"/>
       <c r="R60" s="8" t="str">
         <f aca="false">IF(OR(M60="",Q60&lt;&gt;"Y"),"",ROUND(N60*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S60" s="23" t="s">
-        <v>107</v>
-      </c>
+      <c r="S60" s="25"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="21" t="n">
@@ -8353,10 +8739,10 @@
       </c>
       <c r="B61" s="22"/>
       <c r="C61" s="23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D61" s="26" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E61" s="25"/>
       <c r="F61" s="7" t="str">
@@ -8364,26 +8750,26 @@
         <v/>
       </c>
       <c r="G61" s="25"/>
-      <c r="H61" s="23" t="s">
-        <v>108</v>
+      <c r="H61" s="25" t="s">
+        <v>102</v>
       </c>
       <c r="I61" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J61" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K61" s="27" t="n">
-        <v>1345105</v>
+        <v>5381313</v>
       </c>
       <c r="L61" s="26"/>
       <c r="M61" s="8" t="n">
         <f aca="false">IF(K61="","",IF(J61="USD",ROUND(K61*설정!$C$4,0),K61))</f>
-        <v>1345105</v>
+        <v>5381313</v>
       </c>
       <c r="N61" s="8" t="n">
         <f aca="false">IF(M61="","",IF(AND(I61="과세",L61="VAT포함"),ROUND(M61/(1+설정!$C$5),0),M61))</f>
-        <v>1345105</v>
+        <v>5381313</v>
       </c>
       <c r="O61" s="8" t="n">
         <f aca="false">IF(M61="","",IF(I61="과세",IF(L61="VAT포함",M61-N61,ROUND(N61*설정!$C$5,0)),0))</f>
@@ -8391,16 +8777,14 @@
       </c>
       <c r="P61" s="8" t="n">
         <f aca="false">IF(M61="","",N61+O61)</f>
-        <v>1345105</v>
+        <v>5381313</v>
       </c>
       <c r="Q61" s="26"/>
       <c r="R61" s="8" t="str">
         <f aca="false">IF(OR(M61="",Q61&lt;&gt;"Y"),"",ROUND(N61*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S61" s="23" t="s">
-        <v>107</v>
-      </c>
+      <c r="S61" s="25"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="21" t="n">
@@ -8409,10 +8793,10 @@
       </c>
       <c r="B62" s="22"/>
       <c r="C62" s="23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D62" s="26" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E62" s="25"/>
       <c r="F62" s="7" t="str">
@@ -8420,26 +8804,26 @@
         <v/>
       </c>
       <c r="G62" s="25"/>
-      <c r="H62" s="23" t="s">
-        <v>109</v>
+      <c r="H62" s="25" t="s">
+        <v>103</v>
       </c>
       <c r="I62" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J62" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K62" s="27" t="n">
-        <v>1869000</v>
+        <v>17207955</v>
       </c>
       <c r="L62" s="26"/>
       <c r="M62" s="8" t="n">
         <f aca="false">IF(K62="","",IF(J62="USD",ROUND(K62*설정!$C$4,0),K62))</f>
-        <v>1869000</v>
+        <v>17207955</v>
       </c>
       <c r="N62" s="8" t="n">
         <f aca="false">IF(M62="","",IF(AND(I62="과세",L62="VAT포함"),ROUND(M62/(1+설정!$C$5),0),M62))</f>
-        <v>1869000</v>
+        <v>17207955</v>
       </c>
       <c r="O62" s="8" t="n">
         <f aca="false">IF(M62="","",IF(I62="과세",IF(L62="VAT포함",M62-N62,ROUND(N62*설정!$C$5,0)),0))</f>
@@ -8447,16 +8831,14 @@
       </c>
       <c r="P62" s="8" t="n">
         <f aca="false">IF(M62="","",N62+O62)</f>
-        <v>1869000</v>
+        <v>17207955</v>
       </c>
       <c r="Q62" s="26"/>
       <c r="R62" s="8" t="str">
         <f aca="false">IF(OR(M62="",Q62&lt;&gt;"Y"),"",ROUND(N62*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S62" s="23" t="s">
-        <v>107</v>
-      </c>
+      <c r="S62" s="25"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="21" t="n">
@@ -8465,10 +8847,10 @@
       </c>
       <c r="B63" s="22"/>
       <c r="C63" s="23" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D63" s="26" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E63" s="25"/>
       <c r="F63" s="7" t="str">
@@ -8476,26 +8858,26 @@
         <v/>
       </c>
       <c r="G63" s="25"/>
-      <c r="H63" s="23" t="s">
-        <v>113</v>
+      <c r="H63" s="25" t="s">
+        <v>97</v>
       </c>
       <c r="I63" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J63" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K63" s="27" t="n">
-        <v>366000</v>
+        <v>14285290</v>
       </c>
       <c r="L63" s="26"/>
       <c r="M63" s="8" t="n">
         <f aca="false">IF(K63="","",IF(J63="USD",ROUND(K63*설정!$C$4,0),K63))</f>
-        <v>366000</v>
+        <v>14285290</v>
       </c>
       <c r="N63" s="8" t="n">
         <f aca="false">IF(M63="","",IF(AND(I63="과세",L63="VAT포함"),ROUND(M63/(1+설정!$C$5),0),M63))</f>
-        <v>366000</v>
+        <v>14285290</v>
       </c>
       <c r="O63" s="8" t="n">
         <f aca="false">IF(M63="","",IF(I63="과세",IF(L63="VAT포함",M63-N63,ROUND(N63*설정!$C$5,0)),0))</f>
@@ -8503,7 +8885,7 @@
       </c>
       <c r="P63" s="8" t="n">
         <f aca="false">IF(M63="","",N63+O63)</f>
-        <v>366000</v>
+        <v>14285290</v>
       </c>
       <c r="Q63" s="26"/>
       <c r="R63" s="8" t="str">
@@ -8519,10 +8901,10 @@
       </c>
       <c r="B64" s="22"/>
       <c r="C64" s="23" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D64" s="26" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E64" s="25"/>
       <c r="F64" s="7" t="str">
@@ -8530,45 +8912,41 @@
         <v/>
       </c>
       <c r="G64" s="25"/>
-      <c r="H64" s="23" t="s">
-        <v>114</v>
+      <c r="H64" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="I64" s="24" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="J64" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K64" s="27" t="n">
-        <v>101200</v>
-      </c>
-      <c r="L64" s="26" t="s">
-        <v>60</v>
-      </c>
+        <v>1391500</v>
+      </c>
+      <c r="L64" s="26"/>
       <c r="M64" s="8" t="n">
         <f aca="false">IF(K64="","",IF(J64="USD",ROUND(K64*설정!$C$4,0),K64))</f>
-        <v>101200</v>
+        <v>1391500</v>
       </c>
       <c r="N64" s="8" t="n">
         <f aca="false">IF(M64="","",IF(AND(I64="과세",L64="VAT포함"),ROUND(M64/(1+설정!$C$5),0),M64))</f>
-        <v>92000</v>
+        <v>1391500</v>
       </c>
       <c r="O64" s="8" t="n">
         <f aca="false">IF(M64="","",IF(I64="과세",IF(L64="VAT포함",M64-N64,ROUND(N64*설정!$C$5,0)),0))</f>
-        <v>9200</v>
+        <v>0</v>
       </c>
       <c r="P64" s="8" t="n">
         <f aca="false">IF(M64="","",N64+O64)</f>
-        <v>101200</v>
+        <v>1391500</v>
       </c>
       <c r="Q64" s="26"/>
       <c r="R64" s="8" t="str">
         <f aca="false">IF(OR(M64="",Q64&lt;&gt;"Y"),"",ROUND(N64*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S64" s="23" t="s">
-        <v>115</v>
-      </c>
+      <c r="S64" s="25"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="21" t="n">
@@ -8577,10 +8955,10 @@
       </c>
       <c r="B65" s="22"/>
       <c r="C65" s="23" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D65" s="26" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E65" s="25"/>
       <c r="F65" s="7" t="str">
@@ -8588,26 +8966,26 @@
         <v/>
       </c>
       <c r="G65" s="25"/>
-      <c r="H65" s="23" t="s">
-        <v>113</v>
+      <c r="H65" s="25" t="s">
+        <v>105</v>
       </c>
       <c r="I65" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J65" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K65" s="27" t="n">
-        <v>1342000</v>
+        <v>5001335</v>
       </c>
       <c r="L65" s="26"/>
       <c r="M65" s="8" t="n">
         <f aca="false">IF(K65="","",IF(J65="USD",ROUND(K65*설정!$C$4,0),K65))</f>
-        <v>1342000</v>
+        <v>5001335</v>
       </c>
       <c r="N65" s="8" t="n">
         <f aca="false">IF(M65="","",IF(AND(I65="과세",L65="VAT포함"),ROUND(M65/(1+설정!$C$5),0),M65))</f>
-        <v>1342000</v>
+        <v>5001335</v>
       </c>
       <c r="O65" s="8" t="n">
         <f aca="false">IF(M65="","",IF(I65="과세",IF(L65="VAT포함",M65-N65,ROUND(N65*설정!$C$5,0)),0))</f>
@@ -8615,7 +8993,7 @@
       </c>
       <c r="P65" s="8" t="n">
         <f aca="false">IF(M65="","",N65+O65)</f>
-        <v>1342000</v>
+        <v>5001335</v>
       </c>
       <c r="Q65" s="26"/>
       <c r="R65" s="8" t="str">
@@ -8631,7 +9009,7 @@
       </c>
       <c r="B66" s="22"/>
       <c r="C66" s="23" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D66" s="26" t="s">
         <v>6</v>
@@ -8642,26 +9020,26 @@
         <v/>
       </c>
       <c r="G66" s="25"/>
-      <c r="H66" s="23" t="s">
-        <v>113</v>
+      <c r="H66" s="25" t="s">
+        <v>106</v>
       </c>
       <c r="I66" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J66" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K66" s="27" t="n">
-        <v>366000</v>
+        <v>3380000</v>
       </c>
       <c r="L66" s="26"/>
       <c r="M66" s="8" t="n">
         <f aca="false">IF(K66="","",IF(J66="USD",ROUND(K66*설정!$C$4,0),K66))</f>
-        <v>366000</v>
+        <v>3380000</v>
       </c>
       <c r="N66" s="8" t="n">
         <f aca="false">IF(M66="","",IF(AND(I66="과세",L66="VAT포함"),ROUND(M66/(1+설정!$C$5),0),M66))</f>
-        <v>366000</v>
+        <v>3380000</v>
       </c>
       <c r="O66" s="8" t="n">
         <f aca="false">IF(M66="","",IF(I66="과세",IF(L66="VAT포함",M66-N66,ROUND(N66*설정!$C$5,0)),0))</f>
@@ -8669,7 +9047,7 @@
       </c>
       <c r="P66" s="8" t="n">
         <f aca="false">IF(M66="","",N66+O66)</f>
-        <v>366000</v>
+        <v>3380000</v>
       </c>
       <c r="Q66" s="26"/>
       <c r="R66" s="8" t="str">
@@ -8685,10 +9063,10 @@
       </c>
       <c r="B67" s="22"/>
       <c r="C67" s="23" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D67" s="26" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E67" s="25"/>
       <c r="F67" s="7" t="str">
@@ -8696,45 +9074,41 @@
         <v/>
       </c>
       <c r="G67" s="25"/>
-      <c r="H67" s="23" t="s">
-        <v>114</v>
+      <c r="H67" s="25" t="s">
+        <v>107</v>
       </c>
       <c r="I67" s="24" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="J67" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K67" s="27" t="n">
-        <v>101200</v>
-      </c>
-      <c r="L67" s="26" t="s">
-        <v>60</v>
-      </c>
+        <v>6129745</v>
+      </c>
+      <c r="L67" s="26"/>
       <c r="M67" s="8" t="n">
         <f aca="false">IF(K67="","",IF(J67="USD",ROUND(K67*설정!$C$4,0),K67))</f>
-        <v>101200</v>
+        <v>6129745</v>
       </c>
       <c r="N67" s="8" t="n">
         <f aca="false">IF(M67="","",IF(AND(I67="과세",L67="VAT포함"),ROUND(M67/(1+설정!$C$5),0),M67))</f>
-        <v>92000</v>
+        <v>6129745</v>
       </c>
       <c r="O67" s="8" t="n">
         <f aca="false">IF(M67="","",IF(I67="과세",IF(L67="VAT포함",M67-N67,ROUND(N67*설정!$C$5,0)),0))</f>
-        <v>9200</v>
+        <v>0</v>
       </c>
       <c r="P67" s="8" t="n">
         <f aca="false">IF(M67="","",N67+O67)</f>
-        <v>101200</v>
+        <v>6129745</v>
       </c>
       <c r="Q67" s="26"/>
       <c r="R67" s="8" t="str">
         <f aca="false">IF(OR(M67="",Q67&lt;&gt;"Y"),"",ROUND(N67*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S67" s="23" t="s">
-        <v>115</v>
-      </c>
+      <c r="S67" s="25"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="21" t="n">
@@ -8743,10 +9117,10 @@
       </c>
       <c r="B68" s="22"/>
       <c r="C68" s="23" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D68" s="26" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E68" s="25"/>
       <c r="F68" s="7" t="str">
@@ -8754,26 +9128,26 @@
         <v/>
       </c>
       <c r="G68" s="25"/>
-      <c r="H68" s="23" t="s">
-        <v>113</v>
+      <c r="H68" s="25" t="s">
+        <v>108</v>
       </c>
       <c r="I68" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J68" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K68" s="27" t="n">
-        <v>1342000</v>
+        <v>3762800</v>
       </c>
       <c r="L68" s="26"/>
       <c r="M68" s="8" t="n">
         <f aca="false">IF(K68="","",IF(J68="USD",ROUND(K68*설정!$C$4,0),K68))</f>
-        <v>1342000</v>
+        <v>3762800</v>
       </c>
       <c r="N68" s="8" t="n">
         <f aca="false">IF(M68="","",IF(AND(I68="과세",L68="VAT포함"),ROUND(M68/(1+설정!$C$5),0),M68))</f>
-        <v>1342000</v>
+        <v>3762800</v>
       </c>
       <c r="O68" s="8" t="n">
         <f aca="false">IF(M68="","",IF(I68="과세",IF(L68="VAT포함",M68-N68,ROUND(N68*설정!$C$5,0)),0))</f>
@@ -8781,7 +9155,7 @@
       </c>
       <c r="P68" s="8" t="n">
         <f aca="false">IF(M68="","",N68+O68)</f>
-        <v>1342000</v>
+        <v>3762800</v>
       </c>
       <c r="Q68" s="26"/>
       <c r="R68" s="8" t="str">
@@ -8797,7 +9171,7 @@
       </c>
       <c r="B69" s="22"/>
       <c r="C69" s="23" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D69" s="26" t="s">
         <v>7</v>
@@ -8808,26 +9182,26 @@
         <v/>
       </c>
       <c r="G69" s="25"/>
-      <c r="H69" s="23" t="s">
-        <v>113</v>
+      <c r="H69" s="25" t="s">
+        <v>109</v>
       </c>
       <c r="I69" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J69" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K69" s="27" t="n">
-        <v>366000</v>
+        <v>1997232</v>
       </c>
       <c r="L69" s="26"/>
       <c r="M69" s="8" t="n">
         <f aca="false">IF(K69="","",IF(J69="USD",ROUND(K69*설정!$C$4,0),K69))</f>
-        <v>366000</v>
+        <v>1997232</v>
       </c>
       <c r="N69" s="8" t="n">
         <f aca="false">IF(M69="","",IF(AND(I69="과세",L69="VAT포함"),ROUND(M69/(1+설정!$C$5),0),M69))</f>
-        <v>366000</v>
+        <v>1997232</v>
       </c>
       <c r="O69" s="8" t="n">
         <f aca="false">IF(M69="","",IF(I69="과세",IF(L69="VAT포함",M69-N69,ROUND(N69*설정!$C$5,0)),0))</f>
@@ -8835,7 +9209,7 @@
       </c>
       <c r="P69" s="8" t="n">
         <f aca="false">IF(M69="","",N69+O69)</f>
-        <v>366000</v>
+        <v>1997232</v>
       </c>
       <c r="Q69" s="26"/>
       <c r="R69" s="8" t="str">
@@ -8851,7 +9225,7 @@
       </c>
       <c r="B70" s="22"/>
       <c r="C70" s="23" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D70" s="26" t="s">
         <v>7</v>
@@ -8862,45 +9236,41 @@
         <v/>
       </c>
       <c r="G70" s="25"/>
-      <c r="H70" s="23" t="s">
-        <v>114</v>
+      <c r="H70" s="25" t="s">
+        <v>110</v>
       </c>
       <c r="I70" s="24" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="J70" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K70" s="27" t="n">
-        <v>101200</v>
-      </c>
-      <c r="L70" s="26" t="s">
-        <v>60</v>
-      </c>
+        <v>30800</v>
+      </c>
+      <c r="L70" s="26"/>
       <c r="M70" s="8" t="n">
         <f aca="false">IF(K70="","",IF(J70="USD",ROUND(K70*설정!$C$4,0),K70))</f>
-        <v>101200</v>
+        <v>30800</v>
       </c>
       <c r="N70" s="8" t="n">
         <f aca="false">IF(M70="","",IF(AND(I70="과세",L70="VAT포함"),ROUND(M70/(1+설정!$C$5),0),M70))</f>
-        <v>92000</v>
+        <v>30800</v>
       </c>
       <c r="O70" s="8" t="n">
         <f aca="false">IF(M70="","",IF(I70="과세",IF(L70="VAT포함",M70-N70,ROUND(N70*설정!$C$5,0)),0))</f>
-        <v>9200</v>
+        <v>0</v>
       </c>
       <c r="P70" s="8" t="n">
         <f aca="false">IF(M70="","",N70+O70)</f>
-        <v>101200</v>
+        <v>30800</v>
       </c>
       <c r="Q70" s="26"/>
       <c r="R70" s="8" t="str">
         <f aca="false">IF(OR(M70="",Q70&lt;&gt;"Y"),"",ROUND(N70*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S70" s="23" t="s">
-        <v>115</v>
-      </c>
+      <c r="S70" s="25"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="21" t="n">
@@ -8909,7 +9279,7 @@
       </c>
       <c r="B71" s="22"/>
       <c r="C71" s="23" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D71" s="26" t="s">
         <v>7</v>
@@ -8920,26 +9290,26 @@
         <v/>
       </c>
       <c r="G71" s="25"/>
-      <c r="H71" s="23" t="s">
-        <v>113</v>
+      <c r="H71" s="25" t="s">
+        <v>102</v>
       </c>
       <c r="I71" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J71" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K71" s="27" t="n">
-        <v>1342000</v>
+        <v>2029300</v>
       </c>
       <c r="L71" s="26"/>
       <c r="M71" s="8" t="n">
         <f aca="false">IF(K71="","",IF(J71="USD",ROUND(K71*설정!$C$4,0),K71))</f>
-        <v>1342000</v>
+        <v>2029300</v>
       </c>
       <c r="N71" s="8" t="n">
         <f aca="false">IF(M71="","",IF(AND(I71="과세",L71="VAT포함"),ROUND(M71/(1+설정!$C$5),0),M71))</f>
-        <v>1342000</v>
+        <v>2029300</v>
       </c>
       <c r="O71" s="8" t="n">
         <f aca="false">IF(M71="","",IF(I71="과세",IF(L71="VAT포함",M71-N71,ROUND(N71*설정!$C$5,0)),0))</f>
@@ -8947,7 +9317,7 @@
       </c>
       <c r="P71" s="8" t="n">
         <f aca="false">IF(M71="","",N71+O71)</f>
-        <v>1342000</v>
+        <v>2029300</v>
       </c>
       <c r="Q71" s="26"/>
       <c r="R71" s="8" t="str">
@@ -8963,10 +9333,10 @@
       </c>
       <c r="B72" s="22"/>
       <c r="C72" s="23" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D72" s="26" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E72" s="25"/>
       <c r="F72" s="7" t="str">
@@ -8974,26 +9344,26 @@
         <v/>
       </c>
       <c r="G72" s="25"/>
-      <c r="H72" s="23" t="s">
-        <v>113</v>
+      <c r="H72" s="25" t="s">
+        <v>97</v>
       </c>
       <c r="I72" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J72" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K72" s="27" t="n">
-        <v>392400</v>
+        <v>41976</v>
       </c>
       <c r="L72" s="26"/>
       <c r="M72" s="8" t="n">
         <f aca="false">IF(K72="","",IF(J72="USD",ROUND(K72*설정!$C$4,0),K72))</f>
-        <v>392400</v>
+        <v>41976</v>
       </c>
       <c r="N72" s="8" t="n">
         <f aca="false">IF(M72="","",IF(AND(I72="과세",L72="VAT포함"),ROUND(M72/(1+설정!$C$5),0),M72))</f>
-        <v>392400</v>
+        <v>41976</v>
       </c>
       <c r="O72" s="8" t="n">
         <f aca="false">IF(M72="","",IF(I72="과세",IF(L72="VAT포함",M72-N72,ROUND(N72*설정!$C$5,0)),0))</f>
@@ -9001,16 +9371,14 @@
       </c>
       <c r="P72" s="8" t="n">
         <f aca="false">IF(M72="","",N72+O72)</f>
-        <v>392400</v>
+        <v>41976</v>
       </c>
       <c r="Q72" s="26"/>
       <c r="R72" s="8" t="str">
         <f aca="false">IF(OR(M72="",Q72&lt;&gt;"Y"),"",ROUND(N72*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S72" s="23" t="s">
-        <v>116</v>
-      </c>
+      <c r="S72" s="25"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="21" t="n">
@@ -9019,10 +9387,10 @@
       </c>
       <c r="B73" s="22"/>
       <c r="C73" s="23" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D73" s="26" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E73" s="25"/>
       <c r="F73" s="7" t="str">
@@ -9030,45 +9398,41 @@
         <v/>
       </c>
       <c r="G73" s="25"/>
-      <c r="H73" s="23" t="s">
-        <v>114</v>
+      <c r="H73" s="25" t="s">
+        <v>111</v>
       </c>
       <c r="I73" s="24" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="J73" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K73" s="27" t="n">
-        <v>101200</v>
-      </c>
-      <c r="L73" s="26" t="s">
-        <v>60</v>
-      </c>
+        <v>1050000</v>
+      </c>
+      <c r="L73" s="26"/>
       <c r="M73" s="8" t="n">
         <f aca="false">IF(K73="","",IF(J73="USD",ROUND(K73*설정!$C$4,0),K73))</f>
-        <v>101200</v>
+        <v>1050000</v>
       </c>
       <c r="N73" s="8" t="n">
         <f aca="false">IF(M73="","",IF(AND(I73="과세",L73="VAT포함"),ROUND(M73/(1+설정!$C$5),0),M73))</f>
-        <v>92000</v>
+        <v>1050000</v>
       </c>
       <c r="O73" s="8" t="n">
         <f aca="false">IF(M73="","",IF(I73="과세",IF(L73="VAT포함",M73-N73,ROUND(N73*설정!$C$5,0)),0))</f>
-        <v>9200</v>
+        <v>0</v>
       </c>
       <c r="P73" s="8" t="n">
         <f aca="false">IF(M73="","",N73+O73)</f>
-        <v>101200</v>
+        <v>1050000</v>
       </c>
       <c r="Q73" s="26"/>
       <c r="R73" s="8" t="str">
         <f aca="false">IF(OR(M73="",Q73&lt;&gt;"Y"),"",ROUND(N73*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S73" s="23" t="s">
-        <v>115</v>
-      </c>
+      <c r="S73" s="25"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="21" t="n">
@@ -9077,7 +9441,7 @@
       </c>
       <c r="B74" s="22"/>
       <c r="C74" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D74" s="26" t="s">
         <v>4</v>
@@ -9089,25 +9453,25 @@
       </c>
       <c r="G74" s="25"/>
       <c r="H74" s="23" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I74" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J74" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K74" s="27" t="n">
-        <v>536600</v>
+        <v>28656495</v>
       </c>
       <c r="L74" s="26"/>
       <c r="M74" s="8" t="n">
         <f aca="false">IF(K74="","",IF(J74="USD",ROUND(K74*설정!$C$4,0),K74))</f>
-        <v>536600</v>
+        <v>28656495</v>
       </c>
       <c r="N74" s="8" t="n">
         <f aca="false">IF(M74="","",IF(AND(I74="과세",L74="VAT포함"),ROUND(M74/(1+설정!$C$5),0),M74))</f>
-        <v>536600</v>
+        <v>28656495</v>
       </c>
       <c r="O74" s="8" t="n">
         <f aca="false">IF(M74="","",IF(I74="과세",IF(L74="VAT포함",M74-N74,ROUND(N74*설정!$C$5,0)),0))</f>
@@ -9115,7 +9479,7 @@
       </c>
       <c r="P74" s="8" t="n">
         <f aca="false">IF(M74="","",N74+O74)</f>
-        <v>536600</v>
+        <v>28656495</v>
       </c>
       <c r="Q74" s="26"/>
       <c r="R74" s="8" t="str">
@@ -9123,7 +9487,7 @@
         <v/>
       </c>
       <c r="S74" s="23" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9133,7 +9497,7 @@
       </c>
       <c r="B75" s="22"/>
       <c r="C75" s="23" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D75" s="26" t="s">
         <v>4</v>
@@ -9144,26 +9508,26 @@
         <v/>
       </c>
       <c r="G75" s="25"/>
-      <c r="H75" s="25" t="s">
-        <v>118</v>
+      <c r="H75" s="23" t="s">
+        <v>114</v>
       </c>
       <c r="I75" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J75" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K75" s="27" t="n">
-        <v>7006800</v>
+        <v>5146892</v>
       </c>
       <c r="L75" s="26"/>
       <c r="M75" s="8" t="n">
         <f aca="false">IF(K75="","",IF(J75="USD",ROUND(K75*설정!$C$4,0),K75))</f>
-        <v>7006800</v>
+        <v>5146892</v>
       </c>
       <c r="N75" s="8" t="n">
         <f aca="false">IF(M75="","",IF(AND(I75="과세",L75="VAT포함"),ROUND(M75/(1+설정!$C$5),0),M75))</f>
-        <v>7006800</v>
+        <v>5146892</v>
       </c>
       <c r="O75" s="8" t="n">
         <f aca="false">IF(M75="","",IF(I75="과세",IF(L75="VAT포함",M75-N75,ROUND(N75*설정!$C$5,0)),0))</f>
@@ -9171,14 +9535,16 @@
       </c>
       <c r="P75" s="8" t="n">
         <f aca="false">IF(M75="","",N75+O75)</f>
-        <v>7006800</v>
+        <v>5146892</v>
       </c>
       <c r="Q75" s="26"/>
       <c r="R75" s="8" t="str">
         <f aca="false">IF(OR(M75="",Q75&lt;&gt;"Y"),"",ROUND(N75*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S75" s="25"/>
+      <c r="S75" s="23" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="21" t="n">
@@ -9187,7 +9553,7 @@
       </c>
       <c r="B76" s="22"/>
       <c r="C76" s="23" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D76" s="26" t="s">
         <v>4</v>
@@ -9198,26 +9564,26 @@
         <v/>
       </c>
       <c r="G76" s="25"/>
-      <c r="H76" s="25" t="s">
-        <v>119</v>
+      <c r="H76" s="23" t="s">
+        <v>116</v>
       </c>
       <c r="I76" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J76" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K76" s="27" t="n">
-        <v>3200000</v>
+        <v>878683</v>
       </c>
       <c r="L76" s="26"/>
       <c r="M76" s="8" t="n">
         <f aca="false">IF(K76="","",IF(J76="USD",ROUND(K76*설정!$C$4,0),K76))</f>
-        <v>3200000</v>
+        <v>878683</v>
       </c>
       <c r="N76" s="8" t="n">
         <f aca="false">IF(M76="","",IF(AND(I76="과세",L76="VAT포함"),ROUND(M76/(1+설정!$C$5),0),M76))</f>
-        <v>3200000</v>
+        <v>878683</v>
       </c>
       <c r="O76" s="8" t="n">
         <f aca="false">IF(M76="","",IF(I76="과세",IF(L76="VAT포함",M76-N76,ROUND(N76*설정!$C$5,0)),0))</f>
@@ -9225,14 +9591,16 @@
       </c>
       <c r="P76" s="8" t="n">
         <f aca="false">IF(M76="","",N76+O76)</f>
-        <v>3200000</v>
+        <v>878683</v>
       </c>
       <c r="Q76" s="26"/>
       <c r="R76" s="8" t="str">
         <f aca="false">IF(OR(M76="",Q76&lt;&gt;"Y"),"",ROUND(N76*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S76" s="25"/>
+      <c r="S76" s="23" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="21" t="n">
@@ -9241,10 +9609,10 @@
       </c>
       <c r="B77" s="22"/>
       <c r="C77" s="23" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D77" s="26" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E77" s="25"/>
       <c r="F77" s="7" t="str">
@@ -9252,26 +9620,26 @@
         <v/>
       </c>
       <c r="G77" s="25"/>
-      <c r="H77" s="25" t="s">
-        <v>73</v>
+      <c r="H77" s="23" t="s">
+        <v>117</v>
       </c>
       <c r="I77" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J77" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K77" s="27" t="n">
-        <v>3120000</v>
+        <v>1869000</v>
       </c>
       <c r="L77" s="26"/>
       <c r="M77" s="8" t="n">
         <f aca="false">IF(K77="","",IF(J77="USD",ROUND(K77*설정!$C$4,0),K77))</f>
-        <v>3120000</v>
+        <v>1869000</v>
       </c>
       <c r="N77" s="8" t="n">
         <f aca="false">IF(M77="","",IF(AND(I77="과세",L77="VAT포함"),ROUND(M77/(1+설정!$C$5),0),M77))</f>
-        <v>3120000</v>
+        <v>1869000</v>
       </c>
       <c r="O77" s="8" t="n">
         <f aca="false">IF(M77="","",IF(I77="과세",IF(L77="VAT포함",M77-N77,ROUND(N77*설정!$C$5,0)),0))</f>
@@ -9279,14 +9647,16 @@
       </c>
       <c r="P77" s="8" t="n">
         <f aca="false">IF(M77="","",N77+O77)</f>
-        <v>3120000</v>
+        <v>1869000</v>
       </c>
       <c r="Q77" s="26"/>
       <c r="R77" s="8" t="str">
         <f aca="false">IF(OR(M77="",Q77&lt;&gt;"Y"),"",ROUND(N77*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S77" s="25"/>
+      <c r="S77" s="23" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="21" t="n">
@@ -9295,10 +9665,10 @@
       </c>
       <c r="B78" s="22"/>
       <c r="C78" s="23" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D78" s="26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E78" s="25"/>
       <c r="F78" s="7" t="str">
@@ -9306,26 +9676,26 @@
         <v/>
       </c>
       <c r="G78" s="25"/>
-      <c r="H78" s="25" t="s">
-        <v>73</v>
+      <c r="H78" s="23" t="s">
+        <v>112</v>
       </c>
       <c r="I78" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J78" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K78" s="27" t="n">
-        <v>18017500</v>
+        <v>39515305</v>
       </c>
       <c r="L78" s="26"/>
       <c r="M78" s="8" t="n">
         <f aca="false">IF(K78="","",IF(J78="USD",ROUND(K78*설정!$C$4,0),K78))</f>
-        <v>18017500</v>
+        <v>39515305</v>
       </c>
       <c r="N78" s="8" t="n">
         <f aca="false">IF(M78="","",IF(AND(I78="과세",L78="VAT포함"),ROUND(M78/(1+설정!$C$5),0),M78))</f>
-        <v>18017500</v>
+        <v>39515305</v>
       </c>
       <c r="O78" s="8" t="n">
         <f aca="false">IF(M78="","",IF(I78="과세",IF(L78="VAT포함",M78-N78,ROUND(N78*설정!$C$5,0)),0))</f>
@@ -9333,14 +9703,16 @@
       </c>
       <c r="P78" s="8" t="n">
         <f aca="false">IF(M78="","",N78+O78)</f>
-        <v>18017500</v>
+        <v>39515305</v>
       </c>
       <c r="Q78" s="26"/>
       <c r="R78" s="8" t="str">
         <f aca="false">IF(OR(M78="",Q78&lt;&gt;"Y"),"",ROUND(N78*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S78" s="25"/>
+      <c r="S78" s="23" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="21" t="n">
@@ -9349,10 +9721,10 @@
       </c>
       <c r="B79" s="22"/>
       <c r="C79" s="23" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D79" s="26" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E79" s="25"/>
       <c r="F79" s="7" t="str">
@@ -9360,26 +9732,26 @@
         <v/>
       </c>
       <c r="G79" s="25"/>
-      <c r="H79" s="25" t="s">
-        <v>73</v>
+      <c r="H79" s="23" t="s">
+        <v>114</v>
       </c>
       <c r="I79" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J79" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K79" s="27" t="n">
-        <v>9932500</v>
+        <v>5740259</v>
       </c>
       <c r="L79" s="26"/>
       <c r="M79" s="8" t="n">
         <f aca="false">IF(K79="","",IF(J79="USD",ROUND(K79*설정!$C$4,0),K79))</f>
-        <v>9932500</v>
+        <v>5740259</v>
       </c>
       <c r="N79" s="8" t="n">
         <f aca="false">IF(M79="","",IF(AND(I79="과세",L79="VAT포함"),ROUND(M79/(1+설정!$C$5),0),M79))</f>
-        <v>9932500</v>
+        <v>5740259</v>
       </c>
       <c r="O79" s="8" t="n">
         <f aca="false">IF(M79="","",IF(I79="과세",IF(L79="VAT포함",M79-N79,ROUND(N79*설정!$C$5,0)),0))</f>
@@ -9387,14 +9759,16 @@
       </c>
       <c r="P79" s="8" t="n">
         <f aca="false">IF(M79="","",N79+O79)</f>
-        <v>9932500</v>
+        <v>5740259</v>
       </c>
       <c r="Q79" s="26"/>
       <c r="R79" s="8" t="str">
         <f aca="false">IF(OR(M79="",Q79&lt;&gt;"Y"),"",ROUND(N79*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S79" s="25"/>
+      <c r="S79" s="23" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="21" t="n">
@@ -9403,10 +9777,10 @@
       </c>
       <c r="B80" s="22"/>
       <c r="C80" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="D80" s="24" t="s">
-        <v>56</v>
+        <v>22</v>
+      </c>
+      <c r="D80" s="26" t="s">
+        <v>6</v>
       </c>
       <c r="E80" s="25"/>
       <c r="F80" s="7" t="str">
@@ -9414,26 +9788,26 @@
         <v/>
       </c>
       <c r="G80" s="25"/>
-      <c r="H80" s="25" t="s">
-        <v>73</v>
+      <c r="H80" s="23" t="s">
+        <v>112</v>
       </c>
       <c r="I80" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J80" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K80" s="27" t="n">
-        <v>12600000</v>
+        <v>48315826</v>
       </c>
       <c r="L80" s="26"/>
       <c r="M80" s="8" t="n">
         <f aca="false">IF(K80="","",IF(J80="USD",ROUND(K80*설정!$C$4,0),K80))</f>
-        <v>12600000</v>
+        <v>48315826</v>
       </c>
       <c r="N80" s="8" t="n">
         <f aca="false">IF(M80="","",IF(AND(I80="과세",L80="VAT포함"),ROUND(M80/(1+설정!$C$5),0),M80))</f>
-        <v>12600000</v>
+        <v>48315826</v>
       </c>
       <c r="O80" s="8" t="n">
         <f aca="false">IF(M80="","",IF(I80="과세",IF(L80="VAT포함",M80-N80,ROUND(N80*설정!$C$5,0)),0))</f>
@@ -9441,305 +9815,399 @@
       </c>
       <c r="P80" s="8" t="n">
         <f aca="false">IF(M80="","",N80+O80)</f>
-        <v>12600000</v>
-      </c>
-      <c r="Q80" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="R80" s="8" t="n">
+        <v>48315826</v>
+      </c>
+      <c r="Q80" s="26"/>
+      <c r="R80" s="8" t="str">
         <f aca="false">IF(OR(M80="",Q80&lt;&gt;"Y"),"",ROUND(N80*설정!$C$5,0))</f>
-        <v>1260000</v>
+        <v/>
       </c>
       <c r="S80" s="23" t="s">
-        <v>75</v>
+        <v>119</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="21" t="str">
+      <c r="A81" s="21" t="n">
         <f aca="false">IF(C81="","",COUNTA($C$5:C81))</f>
-        <v/>
+        <v>77</v>
       </c>
       <c r="B81" s="22"/>
-      <c r="C81" s="23"/>
-      <c r="D81" s="26"/>
+      <c r="C81" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D81" s="26" t="s">
+        <v>6</v>
+      </c>
       <c r="E81" s="25"/>
       <c r="F81" s="7" t="str">
         <f aca="false">IF(E81="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E81,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
         <v/>
       </c>
       <c r="G81" s="25"/>
-      <c r="H81" s="25"/>
-      <c r="I81" s="24"/>
-      <c r="J81" s="26"/>
-      <c r="K81" s="27"/>
+      <c r="H81" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="I81" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="J81" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K81" s="27" t="n">
+        <v>9371766</v>
+      </c>
       <c r="L81" s="26"/>
-      <c r="M81" s="8" t="str">
+      <c r="M81" s="8" t="n">
         <f aca="false">IF(K81="","",IF(J81="USD",ROUND(K81*설정!$C$4,0),K81))</f>
-        <v/>
-      </c>
-      <c r="N81" s="8" t="str">
+        <v>9371766</v>
+      </c>
+      <c r="N81" s="8" t="n">
         <f aca="false">IF(M81="","",IF(AND(I81="과세",L81="VAT포함"),ROUND(M81/(1+설정!$C$5),0),M81))</f>
-        <v/>
-      </c>
-      <c r="O81" s="8" t="str">
+        <v>9371766</v>
+      </c>
+      <c r="O81" s="8" t="n">
         <f aca="false">IF(M81="","",IF(I81="과세",IF(L81="VAT포함",M81-N81,ROUND(N81*설정!$C$5,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P81" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P81" s="8" t="n">
         <f aca="false">IF(M81="","",N81+O81)</f>
-        <v/>
+        <v>9371766</v>
       </c>
       <c r="Q81" s="26"/>
       <c r="R81" s="8" t="str">
         <f aca="false">IF(OR(M81="",Q81&lt;&gt;"Y"),"",ROUND(N81*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S81" s="25"/>
+      <c r="S81" s="23" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="21" t="str">
+      <c r="A82" s="21" t="n">
         <f aca="false">IF(C82="","",COUNTA($C$5:C82))</f>
-        <v/>
+        <v>78</v>
       </c>
       <c r="B82" s="22"/>
-      <c r="C82" s="23"/>
-      <c r="D82" s="26"/>
+      <c r="C82" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D82" s="26" t="s">
+        <v>6</v>
+      </c>
       <c r="E82" s="25"/>
       <c r="F82" s="7" t="str">
         <f aca="false">IF(E82="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E82,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
         <v/>
       </c>
       <c r="G82" s="25"/>
-      <c r="H82" s="25"/>
-      <c r="I82" s="24"/>
-      <c r="J82" s="26"/>
-      <c r="K82" s="27"/>
+      <c r="H82" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="I82" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="J82" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K82" s="27" t="n">
+        <v>1869000</v>
+      </c>
       <c r="L82" s="26"/>
-      <c r="M82" s="8" t="str">
+      <c r="M82" s="8" t="n">
         <f aca="false">IF(K82="","",IF(J82="USD",ROUND(K82*설정!$C$4,0),K82))</f>
-        <v/>
-      </c>
-      <c r="N82" s="8" t="str">
+        <v>1869000</v>
+      </c>
+      <c r="N82" s="8" t="n">
         <f aca="false">IF(M82="","",IF(AND(I82="과세",L82="VAT포함"),ROUND(M82/(1+설정!$C$5),0),M82))</f>
-        <v/>
-      </c>
-      <c r="O82" s="8" t="str">
+        <v>1869000</v>
+      </c>
+      <c r="O82" s="8" t="n">
         <f aca="false">IF(M82="","",IF(I82="과세",IF(L82="VAT포함",M82-N82,ROUND(N82*설정!$C$5,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P82" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P82" s="8" t="n">
         <f aca="false">IF(M82="","",N82+O82)</f>
-        <v/>
+        <v>1869000</v>
       </c>
       <c r="Q82" s="26"/>
       <c r="R82" s="8" t="str">
         <f aca="false">IF(OR(M82="",Q82&lt;&gt;"Y"),"",ROUND(N82*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S82" s="25"/>
+      <c r="S82" s="23" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="21" t="str">
+      <c r="A83" s="21" t="n">
         <f aca="false">IF(C83="","",COUNTA($C$5:C83))</f>
-        <v/>
+        <v>79</v>
       </c>
       <c r="B83" s="22"/>
-      <c r="C83" s="23"/>
-      <c r="D83" s="26"/>
+      <c r="C83" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D83" s="26" t="s">
+        <v>7</v>
+      </c>
       <c r="E83" s="25"/>
       <c r="F83" s="7" t="str">
         <f aca="false">IF(E83="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E83,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
         <v/>
       </c>
       <c r="G83" s="25"/>
-      <c r="H83" s="25"/>
-      <c r="I83" s="24"/>
-      <c r="J83" s="26"/>
-      <c r="K83" s="27"/>
+      <c r="H83" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="I83" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="J83" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K83" s="27" t="n">
+        <v>36479048</v>
+      </c>
       <c r="L83" s="26"/>
-      <c r="M83" s="8" t="str">
+      <c r="M83" s="8" t="n">
         <f aca="false">IF(K83="","",IF(J83="USD",ROUND(K83*설정!$C$4,0),K83))</f>
-        <v/>
-      </c>
-      <c r="N83" s="8" t="str">
+        <v>36479048</v>
+      </c>
+      <c r="N83" s="8" t="n">
         <f aca="false">IF(M83="","",IF(AND(I83="과세",L83="VAT포함"),ROUND(M83/(1+설정!$C$5),0),M83))</f>
-        <v/>
-      </c>
-      <c r="O83" s="8" t="str">
+        <v>36479048</v>
+      </c>
+      <c r="O83" s="8" t="n">
         <f aca="false">IF(M83="","",IF(I83="과세",IF(L83="VAT포함",M83-N83,ROUND(N83*설정!$C$5,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P83" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P83" s="8" t="n">
         <f aca="false">IF(M83="","",N83+O83)</f>
-        <v/>
+        <v>36479048</v>
       </c>
       <c r="Q83" s="26"/>
       <c r="R83" s="8" t="str">
         <f aca="false">IF(OR(M83="",Q83&lt;&gt;"Y"),"",ROUND(N83*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S83" s="25"/>
+      <c r="S83" s="23" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="21" t="str">
+      <c r="A84" s="21" t="n">
         <f aca="false">IF(C84="","",COUNTA($C$5:C84))</f>
-        <v/>
+        <v>80</v>
       </c>
       <c r="B84" s="22"/>
-      <c r="C84" s="23"/>
-      <c r="D84" s="26"/>
+      <c r="C84" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D84" s="26" t="s">
+        <v>7</v>
+      </c>
       <c r="E84" s="25"/>
       <c r="F84" s="7" t="str">
         <f aca="false">IF(E84="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E84,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
         <v/>
       </c>
       <c r="G84" s="25"/>
-      <c r="H84" s="25"/>
-      <c r="I84" s="24"/>
-      <c r="J84" s="26"/>
-      <c r="K84" s="27"/>
+      <c r="H84" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="I84" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="J84" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K84" s="27" t="n">
+        <v>14223063</v>
+      </c>
       <c r="L84" s="26"/>
-      <c r="M84" s="8" t="str">
+      <c r="M84" s="8" t="n">
         <f aca="false">IF(K84="","",IF(J84="USD",ROUND(K84*설정!$C$4,0),K84))</f>
-        <v/>
-      </c>
-      <c r="N84" s="8" t="str">
+        <v>14223063</v>
+      </c>
+      <c r="N84" s="8" t="n">
         <f aca="false">IF(M84="","",IF(AND(I84="과세",L84="VAT포함"),ROUND(M84/(1+설정!$C$5),0),M84))</f>
-        <v/>
-      </c>
-      <c r="O84" s="8" t="str">
+        <v>14223063</v>
+      </c>
+      <c r="O84" s="8" t="n">
         <f aca="false">IF(M84="","",IF(I84="과세",IF(L84="VAT포함",M84-N84,ROUND(N84*설정!$C$5,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P84" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P84" s="8" t="n">
         <f aca="false">IF(M84="","",N84+O84)</f>
-        <v/>
+        <v>14223063</v>
       </c>
       <c r="Q84" s="26"/>
       <c r="R84" s="8" t="str">
         <f aca="false">IF(OR(M84="",Q84&lt;&gt;"Y"),"",ROUND(N84*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S84" s="25"/>
+      <c r="S84" s="23" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="21" t="str">
+      <c r="A85" s="21" t="n">
         <f aca="false">IF(C85="","",COUNTA($C$5:C85))</f>
-        <v/>
+        <v>81</v>
       </c>
       <c r="B85" s="22"/>
-      <c r="C85" s="23"/>
-      <c r="D85" s="26"/>
+      <c r="C85" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D85" s="26" t="s">
+        <v>7</v>
+      </c>
       <c r="E85" s="25"/>
       <c r="F85" s="7" t="str">
         <f aca="false">IF(E85="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E85,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
         <v/>
       </c>
       <c r="G85" s="25"/>
-      <c r="H85" s="25"/>
-      <c r="I85" s="24"/>
-      <c r="J85" s="26"/>
-      <c r="K85" s="27"/>
+      <c r="H85" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="I85" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="J85" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K85" s="27" t="n">
+        <v>1345105</v>
+      </c>
       <c r="L85" s="26"/>
-      <c r="M85" s="8" t="str">
+      <c r="M85" s="8" t="n">
         <f aca="false">IF(K85="","",IF(J85="USD",ROUND(K85*설정!$C$4,0),K85))</f>
-        <v/>
-      </c>
-      <c r="N85" s="8" t="str">
+        <v>1345105</v>
+      </c>
+      <c r="N85" s="8" t="n">
         <f aca="false">IF(M85="","",IF(AND(I85="과세",L85="VAT포함"),ROUND(M85/(1+설정!$C$5),0),M85))</f>
-        <v/>
-      </c>
-      <c r="O85" s="8" t="str">
+        <v>1345105</v>
+      </c>
+      <c r="O85" s="8" t="n">
         <f aca="false">IF(M85="","",IF(I85="과세",IF(L85="VAT포함",M85-N85,ROUND(N85*설정!$C$5,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P85" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P85" s="8" t="n">
         <f aca="false">IF(M85="","",N85+O85)</f>
-        <v/>
+        <v>1345105</v>
       </c>
       <c r="Q85" s="26"/>
       <c r="R85" s="8" t="str">
         <f aca="false">IF(OR(M85="",Q85&lt;&gt;"Y"),"",ROUND(N85*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S85" s="25"/>
+      <c r="S85" s="23" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="21" t="str">
+      <c r="A86" s="21" t="n">
         <f aca="false">IF(C86="","",COUNTA($C$5:C86))</f>
-        <v/>
+        <v>82</v>
       </c>
       <c r="B86" s="22"/>
-      <c r="C86" s="23"/>
-      <c r="D86" s="26"/>
+      <c r="C86" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D86" s="26" t="s">
+        <v>7</v>
+      </c>
       <c r="E86" s="25"/>
       <c r="F86" s="7" t="str">
         <f aca="false">IF(E86="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E86,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
         <v/>
       </c>
       <c r="G86" s="25"/>
-      <c r="H86" s="25"/>
-      <c r="I86" s="24"/>
-      <c r="J86" s="26"/>
-      <c r="K86" s="27"/>
+      <c r="H86" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="I86" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="J86" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K86" s="27" t="n">
+        <v>1869000</v>
+      </c>
       <c r="L86" s="26"/>
-      <c r="M86" s="8" t="str">
+      <c r="M86" s="8" t="n">
         <f aca="false">IF(K86="","",IF(J86="USD",ROUND(K86*설정!$C$4,0),K86))</f>
-        <v/>
-      </c>
-      <c r="N86" s="8" t="str">
+        <v>1869000</v>
+      </c>
+      <c r="N86" s="8" t="n">
         <f aca="false">IF(M86="","",IF(AND(I86="과세",L86="VAT포함"),ROUND(M86/(1+설정!$C$5),0),M86))</f>
-        <v/>
-      </c>
-      <c r="O86" s="8" t="str">
+        <v>1869000</v>
+      </c>
+      <c r="O86" s="8" t="n">
         <f aca="false">IF(M86="","",IF(I86="과세",IF(L86="VAT포함",M86-N86,ROUND(N86*설정!$C$5,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P86" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P86" s="8" t="n">
         <f aca="false">IF(M86="","",N86+O86)</f>
-        <v/>
+        <v>1869000</v>
       </c>
       <c r="Q86" s="26"/>
       <c r="R86" s="8" t="str">
         <f aca="false">IF(OR(M86="",Q86&lt;&gt;"Y"),"",ROUND(N86*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S86" s="25"/>
+      <c r="S86" s="23" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="21" t="str">
+      <c r="A87" s="21" t="n">
         <f aca="false">IF(C87="","",COUNTA($C$5:C87))</f>
-        <v/>
+        <v>83</v>
       </c>
       <c r="B87" s="22"/>
-      <c r="C87" s="23"/>
-      <c r="D87" s="26"/>
+      <c r="C87" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D87" s="26" t="s">
+        <v>5</v>
+      </c>
       <c r="E87" s="25"/>
       <c r="F87" s="7" t="str">
         <f aca="false">IF(E87="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E87,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
         <v/>
       </c>
       <c r="G87" s="25"/>
-      <c r="H87" s="25"/>
-      <c r="I87" s="24"/>
-      <c r="J87" s="26"/>
-      <c r="K87" s="27"/>
+      <c r="H87" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="I87" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="J87" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K87" s="27" t="n">
+        <v>366000</v>
+      </c>
       <c r="L87" s="26"/>
-      <c r="M87" s="8" t="str">
+      <c r="M87" s="8" t="n">
         <f aca="false">IF(K87="","",IF(J87="USD",ROUND(K87*설정!$C$4,0),K87))</f>
-        <v/>
-      </c>
-      <c r="N87" s="8" t="str">
+        <v>366000</v>
+      </c>
+      <c r="N87" s="8" t="n">
         <f aca="false">IF(M87="","",IF(AND(I87="과세",L87="VAT포함"),ROUND(M87/(1+설정!$C$5),0),M87))</f>
-        <v/>
-      </c>
-      <c r="O87" s="8" t="str">
+        <v>366000</v>
+      </c>
+      <c r="O87" s="8" t="n">
         <f aca="false">IF(M87="","",IF(I87="과세",IF(L87="VAT포함",M87-N87,ROUND(N87*설정!$C$5,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P87" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P87" s="8" t="n">
         <f aca="false">IF(M87="","",N87+O87)</f>
-        <v/>
+        <v>366000</v>
       </c>
       <c r="Q87" s="26"/>
       <c r="R87" s="8" t="str">
@@ -9749,81 +10217,109 @@
       <c r="S87" s="25"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="21" t="str">
+      <c r="A88" s="21" t="n">
         <f aca="false">IF(C88="","",COUNTA($C$5:C88))</f>
-        <v/>
+        <v>84</v>
       </c>
       <c r="B88" s="22"/>
-      <c r="C88" s="23"/>
-      <c r="D88" s="26"/>
+      <c r="C88" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D88" s="26" t="s">
+        <v>5</v>
+      </c>
       <c r="E88" s="25"/>
       <c r="F88" s="7" t="str">
         <f aca="false">IF(E88="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E88,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
         <v/>
       </c>
       <c r="G88" s="25"/>
-      <c r="H88" s="25"/>
-      <c r="I88" s="24"/>
-      <c r="J88" s="26"/>
-      <c r="K88" s="27"/>
-      <c r="L88" s="26"/>
-      <c r="M88" s="8" t="str">
+      <c r="H88" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="I88" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="J88" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K88" s="27" t="n">
+        <v>101200</v>
+      </c>
+      <c r="L88" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="M88" s="8" t="n">
         <f aca="false">IF(K88="","",IF(J88="USD",ROUND(K88*설정!$C$4,0),K88))</f>
-        <v/>
-      </c>
-      <c r="N88" s="8" t="str">
+        <v>101200</v>
+      </c>
+      <c r="N88" s="8" t="n">
         <f aca="false">IF(M88="","",IF(AND(I88="과세",L88="VAT포함"),ROUND(M88/(1+설정!$C$5),0),M88))</f>
-        <v/>
-      </c>
-      <c r="O88" s="8" t="str">
+        <v>92000</v>
+      </c>
+      <c r="O88" s="8" t="n">
         <f aca="false">IF(M88="","",IF(I88="과세",IF(L88="VAT포함",M88-N88,ROUND(N88*설정!$C$5,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P88" s="8" t="str">
+        <v>9200</v>
+      </c>
+      <c r="P88" s="8" t="n">
         <f aca="false">IF(M88="","",N88+O88)</f>
-        <v/>
+        <v>101200</v>
       </c>
       <c r="Q88" s="26"/>
       <c r="R88" s="8" t="str">
         <f aca="false">IF(OR(M88="",Q88&lt;&gt;"Y"),"",ROUND(N88*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S88" s="25"/>
+      <c r="S88" s="23" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="21" t="str">
+      <c r="A89" s="21" t="n">
         <f aca="false">IF(C89="","",COUNTA($C$5:C89))</f>
-        <v/>
+        <v>85</v>
       </c>
       <c r="B89" s="22"/>
-      <c r="C89" s="23"/>
-      <c r="D89" s="26"/>
+      <c r="C89" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D89" s="26" t="s">
+        <v>5</v>
+      </c>
       <c r="E89" s="25"/>
       <c r="F89" s="7" t="str">
         <f aca="false">IF(E89="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E89,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
         <v/>
       </c>
       <c r="G89" s="25"/>
-      <c r="H89" s="25"/>
-      <c r="I89" s="24"/>
-      <c r="J89" s="26"/>
-      <c r="K89" s="27"/>
+      <c r="H89" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="I89" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="J89" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K89" s="27" t="n">
+        <v>1342000</v>
+      </c>
       <c r="L89" s="26"/>
-      <c r="M89" s="8" t="str">
+      <c r="M89" s="8" t="n">
         <f aca="false">IF(K89="","",IF(J89="USD",ROUND(K89*설정!$C$4,0),K89))</f>
-        <v/>
-      </c>
-      <c r="N89" s="8" t="str">
+        <v>1342000</v>
+      </c>
+      <c r="N89" s="8" t="n">
         <f aca="false">IF(M89="","",IF(AND(I89="과세",L89="VAT포함"),ROUND(M89/(1+설정!$C$5),0),M89))</f>
-        <v/>
-      </c>
-      <c r="O89" s="8" t="str">
+        <v>1342000</v>
+      </c>
+      <c r="O89" s="8" t="n">
         <f aca="false">IF(M89="","",IF(I89="과세",IF(L89="VAT포함",M89-N89,ROUND(N89*설정!$C$5,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P89" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P89" s="8" t="n">
         <f aca="false">IF(M89="","",N89+O89)</f>
-        <v/>
+        <v>1342000</v>
       </c>
       <c r="Q89" s="26"/>
       <c r="R89" s="8" t="str">
@@ -9833,39 +10329,51 @@
       <c r="S89" s="25"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="21" t="str">
+      <c r="A90" s="21" t="n">
         <f aca="false">IF(C90="","",COUNTA($C$5:C90))</f>
-        <v/>
+        <v>86</v>
       </c>
       <c r="B90" s="22"/>
-      <c r="C90" s="23"/>
-      <c r="D90" s="26"/>
+      <c r="C90" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D90" s="26" t="s">
+        <v>6</v>
+      </c>
       <c r="E90" s="25"/>
       <c r="F90" s="7" t="str">
         <f aca="false">IF(E90="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E90,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
         <v/>
       </c>
       <c r="G90" s="25"/>
-      <c r="H90" s="25"/>
-      <c r="I90" s="24"/>
-      <c r="J90" s="26"/>
-      <c r="K90" s="27"/>
+      <c r="H90" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="I90" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="J90" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K90" s="27" t="n">
+        <v>366000</v>
+      </c>
       <c r="L90" s="26"/>
-      <c r="M90" s="8" t="str">
+      <c r="M90" s="8" t="n">
         <f aca="false">IF(K90="","",IF(J90="USD",ROUND(K90*설정!$C$4,0),K90))</f>
-        <v/>
-      </c>
-      <c r="N90" s="8" t="str">
+        <v>366000</v>
+      </c>
+      <c r="N90" s="8" t="n">
         <f aca="false">IF(M90="","",IF(AND(I90="과세",L90="VAT포함"),ROUND(M90/(1+설정!$C$5),0),M90))</f>
-        <v/>
-      </c>
-      <c r="O90" s="8" t="str">
+        <v>366000</v>
+      </c>
+      <c r="O90" s="8" t="n">
         <f aca="false">IF(M90="","",IF(I90="과세",IF(L90="VAT포함",M90-N90,ROUND(N90*설정!$C$5,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P90" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P90" s="8" t="n">
         <f aca="false">IF(M90="","",N90+O90)</f>
-        <v/>
+        <v>366000</v>
       </c>
       <c r="Q90" s="26"/>
       <c r="R90" s="8" t="str">
@@ -9875,81 +10383,109 @@
       <c r="S90" s="25"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="21" t="str">
+      <c r="A91" s="21" t="n">
         <f aca="false">IF(C91="","",COUNTA($C$5:C91))</f>
-        <v/>
+        <v>87</v>
       </c>
       <c r="B91" s="22"/>
-      <c r="C91" s="23"/>
-      <c r="D91" s="26"/>
+      <c r="C91" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D91" s="26" t="s">
+        <v>6</v>
+      </c>
       <c r="E91" s="25"/>
       <c r="F91" s="7" t="str">
         <f aca="false">IF(E91="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E91,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
         <v/>
       </c>
       <c r="G91" s="25"/>
-      <c r="H91" s="25"/>
-      <c r="I91" s="24"/>
-      <c r="J91" s="26"/>
-      <c r="K91" s="27"/>
-      <c r="L91" s="26"/>
-      <c r="M91" s="8" t="str">
+      <c r="H91" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="I91" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="J91" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K91" s="27" t="n">
+        <v>101200</v>
+      </c>
+      <c r="L91" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="M91" s="8" t="n">
         <f aca="false">IF(K91="","",IF(J91="USD",ROUND(K91*설정!$C$4,0),K91))</f>
-        <v/>
-      </c>
-      <c r="N91" s="8" t="str">
+        <v>101200</v>
+      </c>
+      <c r="N91" s="8" t="n">
         <f aca="false">IF(M91="","",IF(AND(I91="과세",L91="VAT포함"),ROUND(M91/(1+설정!$C$5),0),M91))</f>
-        <v/>
-      </c>
-      <c r="O91" s="8" t="str">
+        <v>92000</v>
+      </c>
+      <c r="O91" s="8" t="n">
         <f aca="false">IF(M91="","",IF(I91="과세",IF(L91="VAT포함",M91-N91,ROUND(N91*설정!$C$5,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P91" s="8" t="str">
+        <v>9200</v>
+      </c>
+      <c r="P91" s="8" t="n">
         <f aca="false">IF(M91="","",N91+O91)</f>
-        <v/>
+        <v>101200</v>
       </c>
       <c r="Q91" s="26"/>
       <c r="R91" s="8" t="str">
         <f aca="false">IF(OR(M91="",Q91&lt;&gt;"Y"),"",ROUND(N91*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S91" s="25"/>
+      <c r="S91" s="23" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="21" t="str">
+      <c r="A92" s="21" t="n">
         <f aca="false">IF(C92="","",COUNTA($C$5:C92))</f>
-        <v/>
+        <v>88</v>
       </c>
       <c r="B92" s="22"/>
-      <c r="C92" s="23"/>
-      <c r="D92" s="26"/>
+      <c r="C92" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D92" s="26" t="s">
+        <v>6</v>
+      </c>
       <c r="E92" s="25"/>
       <c r="F92" s="7" t="str">
         <f aca="false">IF(E92="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E92,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
         <v/>
       </c>
       <c r="G92" s="25"/>
-      <c r="H92" s="25"/>
-      <c r="I92" s="24"/>
-      <c r="J92" s="26"/>
-      <c r="K92" s="27"/>
+      <c r="H92" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="I92" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="J92" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K92" s="27" t="n">
+        <v>1342000</v>
+      </c>
       <c r="L92" s="26"/>
-      <c r="M92" s="8" t="str">
+      <c r="M92" s="8" t="n">
         <f aca="false">IF(K92="","",IF(J92="USD",ROUND(K92*설정!$C$4,0),K92))</f>
-        <v/>
-      </c>
-      <c r="N92" s="8" t="str">
+        <v>1342000</v>
+      </c>
+      <c r="N92" s="8" t="n">
         <f aca="false">IF(M92="","",IF(AND(I92="과세",L92="VAT포함"),ROUND(M92/(1+설정!$C$5),0),M92))</f>
-        <v/>
-      </c>
-      <c r="O92" s="8" t="str">
+        <v>1342000</v>
+      </c>
+      <c r="O92" s="8" t="n">
         <f aca="false">IF(M92="","",IF(I92="과세",IF(L92="VAT포함",M92-N92,ROUND(N92*설정!$C$5,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P92" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P92" s="8" t="n">
         <f aca="false">IF(M92="","",N92+O92)</f>
-        <v/>
+        <v>1342000</v>
       </c>
       <c r="Q92" s="26"/>
       <c r="R92" s="8" t="str">
@@ -9959,39 +10495,51 @@
       <c r="S92" s="25"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="21" t="str">
+      <c r="A93" s="21" t="n">
         <f aca="false">IF(C93="","",COUNTA($C$5:C93))</f>
-        <v/>
+        <v>89</v>
       </c>
       <c r="B93" s="22"/>
-      <c r="C93" s="23"/>
-      <c r="D93" s="26"/>
+      <c r="C93" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D93" s="26" t="s">
+        <v>7</v>
+      </c>
       <c r="E93" s="25"/>
       <c r="F93" s="7" t="str">
         <f aca="false">IF(E93="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E93,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
         <v/>
       </c>
       <c r="G93" s="25"/>
-      <c r="H93" s="25"/>
-      <c r="I93" s="24"/>
-      <c r="J93" s="26"/>
-      <c r="K93" s="27"/>
+      <c r="H93" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="I93" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="J93" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K93" s="27" t="n">
+        <v>366000</v>
+      </c>
       <c r="L93" s="26"/>
-      <c r="M93" s="8" t="str">
+      <c r="M93" s="8" t="n">
         <f aca="false">IF(K93="","",IF(J93="USD",ROUND(K93*설정!$C$4,0),K93))</f>
-        <v/>
-      </c>
-      <c r="N93" s="8" t="str">
+        <v>366000</v>
+      </c>
+      <c r="N93" s="8" t="n">
         <f aca="false">IF(M93="","",IF(AND(I93="과세",L93="VAT포함"),ROUND(M93/(1+설정!$C$5),0),M93))</f>
-        <v/>
-      </c>
-      <c r="O93" s="8" t="str">
+        <v>366000</v>
+      </c>
+      <c r="O93" s="8" t="n">
         <f aca="false">IF(M93="","",IF(I93="과세",IF(L93="VAT포함",M93-N93,ROUND(N93*설정!$C$5,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P93" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P93" s="8" t="n">
         <f aca="false">IF(M93="","",N93+O93)</f>
-        <v/>
+        <v>366000</v>
       </c>
       <c r="Q93" s="26"/>
       <c r="R93" s="8" t="str">
@@ -10001,81 +10549,109 @@
       <c r="S93" s="25"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="21" t="str">
+      <c r="A94" s="21" t="n">
         <f aca="false">IF(C94="","",COUNTA($C$5:C94))</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="B94" s="22"/>
-      <c r="C94" s="23"/>
-      <c r="D94" s="26"/>
+      <c r="C94" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D94" s="26" t="s">
+        <v>7</v>
+      </c>
       <c r="E94" s="25"/>
       <c r="F94" s="7" t="str">
         <f aca="false">IF(E94="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E94,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
         <v/>
       </c>
       <c r="G94" s="25"/>
-      <c r="H94" s="25"/>
-      <c r="I94" s="24"/>
-      <c r="J94" s="26"/>
-      <c r="K94" s="27"/>
-      <c r="L94" s="26"/>
-      <c r="M94" s="8" t="str">
+      <c r="H94" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="I94" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="J94" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K94" s="27" t="n">
+        <v>101200</v>
+      </c>
+      <c r="L94" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="M94" s="8" t="n">
         <f aca="false">IF(K94="","",IF(J94="USD",ROUND(K94*설정!$C$4,0),K94))</f>
-        <v/>
-      </c>
-      <c r="N94" s="8" t="str">
+        <v>101200</v>
+      </c>
+      <c r="N94" s="8" t="n">
         <f aca="false">IF(M94="","",IF(AND(I94="과세",L94="VAT포함"),ROUND(M94/(1+설정!$C$5),0),M94))</f>
-        <v/>
-      </c>
-      <c r="O94" s="8" t="str">
+        <v>92000</v>
+      </c>
+      <c r="O94" s="8" t="n">
         <f aca="false">IF(M94="","",IF(I94="과세",IF(L94="VAT포함",M94-N94,ROUND(N94*설정!$C$5,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P94" s="8" t="str">
+        <v>9200</v>
+      </c>
+      <c r="P94" s="8" t="n">
         <f aca="false">IF(M94="","",N94+O94)</f>
-        <v/>
+        <v>101200</v>
       </c>
       <c r="Q94" s="26"/>
       <c r="R94" s="8" t="str">
         <f aca="false">IF(OR(M94="",Q94&lt;&gt;"Y"),"",ROUND(N94*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S94" s="25"/>
+      <c r="S94" s="23" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="21" t="str">
+      <c r="A95" s="21" t="n">
         <f aca="false">IF(C95="","",COUNTA($C$5:C95))</f>
-        <v/>
+        <v>91</v>
       </c>
       <c r="B95" s="22"/>
-      <c r="C95" s="23"/>
-      <c r="D95" s="26"/>
+      <c r="C95" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D95" s="26" t="s">
+        <v>7</v>
+      </c>
       <c r="E95" s="25"/>
       <c r="F95" s="7" t="str">
         <f aca="false">IF(E95="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E95,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
         <v/>
       </c>
       <c r="G95" s="25"/>
-      <c r="H95" s="25"/>
-      <c r="I95" s="24"/>
-      <c r="J95" s="26"/>
-      <c r="K95" s="27"/>
+      <c r="H95" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="I95" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="J95" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K95" s="27" t="n">
+        <v>1342000</v>
+      </c>
       <c r="L95" s="26"/>
-      <c r="M95" s="8" t="str">
+      <c r="M95" s="8" t="n">
         <f aca="false">IF(K95="","",IF(J95="USD",ROUND(K95*설정!$C$4,0),K95))</f>
-        <v/>
-      </c>
-      <c r="N95" s="8" t="str">
+        <v>1342000</v>
+      </c>
+      <c r="N95" s="8" t="n">
         <f aca="false">IF(M95="","",IF(AND(I95="과세",L95="VAT포함"),ROUND(M95/(1+설정!$C$5),0),M95))</f>
-        <v/>
-      </c>
-      <c r="O95" s="8" t="str">
+        <v>1342000</v>
+      </c>
+      <c r="O95" s="8" t="n">
         <f aca="false">IF(M95="","",IF(I95="과세",IF(L95="VAT포함",M95-N95,ROUND(N95*설정!$C$5,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P95" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P95" s="8" t="n">
         <f aca="false">IF(M95="","",N95+O95)</f>
-        <v/>
+        <v>1342000</v>
       </c>
       <c r="Q95" s="26"/>
       <c r="R95" s="8" t="str">
@@ -10085,165 +10661,221 @@
       <c r="S95" s="25"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="21" t="str">
+      <c r="A96" s="21" t="n">
         <f aca="false">IF(C96="","",COUNTA($C$5:C96))</f>
-        <v/>
+        <v>92</v>
       </c>
       <c r="B96" s="22"/>
-      <c r="C96" s="23"/>
-      <c r="D96" s="26"/>
+      <c r="C96" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D96" s="26" t="s">
+        <v>4</v>
+      </c>
       <c r="E96" s="25"/>
       <c r="F96" s="7" t="str">
         <f aca="false">IF(E96="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E96,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
         <v/>
       </c>
       <c r="G96" s="25"/>
-      <c r="H96" s="25"/>
-      <c r="I96" s="24"/>
-      <c r="J96" s="26"/>
-      <c r="K96" s="27"/>
+      <c r="H96" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="I96" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="J96" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K96" s="27" t="n">
+        <v>392400</v>
+      </c>
       <c r="L96" s="26"/>
-      <c r="M96" s="8" t="str">
+      <c r="M96" s="8" t="n">
         <f aca="false">IF(K96="","",IF(J96="USD",ROUND(K96*설정!$C$4,0),K96))</f>
-        <v/>
-      </c>
-      <c r="N96" s="8" t="str">
+        <v>392400</v>
+      </c>
+      <c r="N96" s="8" t="n">
         <f aca="false">IF(M96="","",IF(AND(I96="과세",L96="VAT포함"),ROUND(M96/(1+설정!$C$5),0),M96))</f>
-        <v/>
-      </c>
-      <c r="O96" s="8" t="str">
+        <v>392400</v>
+      </c>
+      <c r="O96" s="8" t="n">
         <f aca="false">IF(M96="","",IF(I96="과세",IF(L96="VAT포함",M96-N96,ROUND(N96*설정!$C$5,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P96" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P96" s="8" t="n">
         <f aca="false">IF(M96="","",N96+O96)</f>
-        <v/>
+        <v>392400</v>
       </c>
       <c r="Q96" s="26"/>
       <c r="R96" s="8" t="str">
         <f aca="false">IF(OR(M96="",Q96&lt;&gt;"Y"),"",ROUND(N96*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S96" s="25"/>
+      <c r="S96" s="23" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="21" t="str">
+      <c r="A97" s="21" t="n">
         <f aca="false">IF(C97="","",COUNTA($C$5:C97))</f>
-        <v/>
+        <v>93</v>
       </c>
       <c r="B97" s="22"/>
-      <c r="C97" s="23"/>
-      <c r="D97" s="26"/>
+      <c r="C97" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D97" s="26" t="s">
+        <v>4</v>
+      </c>
       <c r="E97" s="25"/>
       <c r="F97" s="7" t="str">
         <f aca="false">IF(E97="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E97,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
         <v/>
       </c>
       <c r="G97" s="25"/>
-      <c r="H97" s="25"/>
-      <c r="I97" s="24"/>
-      <c r="J97" s="26"/>
-      <c r="K97" s="27"/>
-      <c r="L97" s="26"/>
-      <c r="M97" s="8" t="str">
+      <c r="H97" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="I97" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="J97" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K97" s="27" t="n">
+        <v>101200</v>
+      </c>
+      <c r="L97" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="M97" s="8" t="n">
         <f aca="false">IF(K97="","",IF(J97="USD",ROUND(K97*설정!$C$4,0),K97))</f>
-        <v/>
-      </c>
-      <c r="N97" s="8" t="str">
+        <v>101200</v>
+      </c>
+      <c r="N97" s="8" t="n">
         <f aca="false">IF(M97="","",IF(AND(I97="과세",L97="VAT포함"),ROUND(M97/(1+설정!$C$5),0),M97))</f>
-        <v/>
-      </c>
-      <c r="O97" s="8" t="str">
+        <v>92000</v>
+      </c>
+      <c r="O97" s="8" t="n">
         <f aca="false">IF(M97="","",IF(I97="과세",IF(L97="VAT포함",M97-N97,ROUND(N97*설정!$C$5,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P97" s="8" t="str">
+        <v>9200</v>
+      </c>
+      <c r="P97" s="8" t="n">
         <f aca="false">IF(M97="","",N97+O97)</f>
-        <v/>
+        <v>101200</v>
       </c>
       <c r="Q97" s="26"/>
       <c r="R97" s="8" t="str">
         <f aca="false">IF(OR(M97="",Q97&lt;&gt;"Y"),"",ROUND(N97*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S97" s="25"/>
+      <c r="S97" s="23" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="21" t="str">
+      <c r="A98" s="21" t="n">
         <f aca="false">IF(C98="","",COUNTA($C$5:C98))</f>
-        <v/>
+        <v>94</v>
       </c>
       <c r="B98" s="22"/>
-      <c r="C98" s="23"/>
-      <c r="D98" s="26"/>
+      <c r="C98" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D98" s="26" t="s">
+        <v>4</v>
+      </c>
       <c r="E98" s="25"/>
       <c r="F98" s="7" t="str">
         <f aca="false">IF(E98="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E98,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
         <v/>
       </c>
       <c r="G98" s="25"/>
-      <c r="H98" s="25"/>
-      <c r="I98" s="24"/>
-      <c r="J98" s="26"/>
-      <c r="K98" s="27"/>
+      <c r="H98" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="I98" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="J98" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K98" s="27" t="n">
+        <v>536600</v>
+      </c>
       <c r="L98" s="26"/>
-      <c r="M98" s="8" t="str">
+      <c r="M98" s="8" t="n">
         <f aca="false">IF(K98="","",IF(J98="USD",ROUND(K98*설정!$C$4,0),K98))</f>
-        <v/>
-      </c>
-      <c r="N98" s="8" t="str">
+        <v>536600</v>
+      </c>
+      <c r="N98" s="8" t="n">
         <f aca="false">IF(M98="","",IF(AND(I98="과세",L98="VAT포함"),ROUND(M98/(1+설정!$C$5),0),M98))</f>
-        <v/>
-      </c>
-      <c r="O98" s="8" t="str">
+        <v>536600</v>
+      </c>
+      <c r="O98" s="8" t="n">
         <f aca="false">IF(M98="","",IF(I98="과세",IF(L98="VAT포함",M98-N98,ROUND(N98*설정!$C$5,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P98" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P98" s="8" t="n">
         <f aca="false">IF(M98="","",N98+O98)</f>
-        <v/>
+        <v>536600</v>
       </c>
       <c r="Q98" s="26"/>
       <c r="R98" s="8" t="str">
         <f aca="false">IF(OR(M98="",Q98&lt;&gt;"Y"),"",ROUND(N98*설정!$C$5,0))</f>
         <v/>
       </c>
-      <c r="S98" s="25"/>
+      <c r="S98" s="23" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="21" t="str">
+      <c r="A99" s="21" t="n">
         <f aca="false">IF(C99="","",COUNTA($C$5:C99))</f>
-        <v/>
+        <v>95</v>
       </c>
       <c r="B99" s="22"/>
-      <c r="C99" s="23"/>
-      <c r="D99" s="26"/>
+      <c r="C99" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D99" s="26" t="s">
+        <v>4</v>
+      </c>
       <c r="E99" s="25"/>
       <c r="F99" s="7" t="str">
         <f aca="false">IF(E99="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E99,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
         <v/>
       </c>
       <c r="G99" s="25"/>
-      <c r="H99" s="25"/>
-      <c r="I99" s="24"/>
-      <c r="J99" s="26"/>
-      <c r="K99" s="27"/>
+      <c r="H99" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="I99" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="J99" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K99" s="27" t="n">
+        <v>7006800</v>
+      </c>
       <c r="L99" s="26"/>
-      <c r="M99" s="8" t="str">
+      <c r="M99" s="8" t="n">
         <f aca="false">IF(K99="","",IF(J99="USD",ROUND(K99*설정!$C$4,0),K99))</f>
-        <v/>
-      </c>
-      <c r="N99" s="8" t="str">
+        <v>7006800</v>
+      </c>
+      <c r="N99" s="8" t="n">
         <f aca="false">IF(M99="","",IF(AND(I99="과세",L99="VAT포함"),ROUND(M99/(1+설정!$C$5),0),M99))</f>
-        <v/>
-      </c>
-      <c r="O99" s="8" t="str">
+        <v>7006800</v>
+      </c>
+      <c r="O99" s="8" t="n">
         <f aca="false">IF(M99="","",IF(I99="과세",IF(L99="VAT포함",M99-N99,ROUND(N99*설정!$C$5,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P99" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P99" s="8" t="n">
         <f aca="false">IF(M99="","",N99+O99)</f>
-        <v/>
+        <v>7006800</v>
       </c>
       <c r="Q99" s="26"/>
       <c r="R99" s="8" t="str">
@@ -10253,39 +10885,51 @@
       <c r="S99" s="25"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="21" t="str">
+      <c r="A100" s="21" t="n">
         <f aca="false">IF(C100="","",COUNTA($C$5:C100))</f>
-        <v/>
+        <v>96</v>
       </c>
       <c r="B100" s="22"/>
-      <c r="C100" s="23"/>
-      <c r="D100" s="26"/>
+      <c r="C100" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D100" s="26" t="s">
+        <v>4</v>
+      </c>
       <c r="E100" s="25"/>
       <c r="F100" s="7" t="str">
         <f aca="false">IF(E100="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E100,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
         <v/>
       </c>
       <c r="G100" s="25"/>
-      <c r="H100" s="25"/>
-      <c r="I100" s="24"/>
-      <c r="J100" s="26"/>
-      <c r="K100" s="27"/>
+      <c r="H100" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="I100" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="J100" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K100" s="27" t="n">
+        <v>3200000</v>
+      </c>
       <c r="L100" s="26"/>
-      <c r="M100" s="8" t="str">
+      <c r="M100" s="8" t="n">
         <f aca="false">IF(K100="","",IF(J100="USD",ROUND(K100*설정!$C$4,0),K100))</f>
-        <v/>
-      </c>
-      <c r="N100" s="8" t="str">
+        <v>3200000</v>
+      </c>
+      <c r="N100" s="8" t="n">
         <f aca="false">IF(M100="","",IF(AND(I100="과세",L100="VAT포함"),ROUND(M100/(1+설정!$C$5),0),M100))</f>
-        <v/>
-      </c>
-      <c r="O100" s="8" t="str">
+        <v>3200000</v>
+      </c>
+      <c r="O100" s="8" t="n">
         <f aca="false">IF(M100="","",IF(I100="과세",IF(L100="VAT포함",M100-N100,ROUND(N100*설정!$C$5,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P100" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P100" s="8" t="n">
         <f aca="false">IF(M100="","",N100+O100)</f>
-        <v/>
+        <v>3200000</v>
       </c>
       <c r="Q100" s="26"/>
       <c r="R100" s="8" t="str">
@@ -10295,39 +10939,51 @@
       <c r="S100" s="25"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="21" t="str">
+      <c r="A101" s="21" t="n">
         <f aca="false">IF(C101="","",COUNTA($C$5:C101))</f>
-        <v/>
+        <v>97</v>
       </c>
       <c r="B101" s="22"/>
-      <c r="C101" s="23"/>
-      <c r="D101" s="26"/>
+      <c r="C101" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D101" s="26" t="s">
+        <v>5</v>
+      </c>
       <c r="E101" s="25"/>
       <c r="F101" s="7" t="str">
         <f aca="false">IF(E101="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E101,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
         <v/>
       </c>
       <c r="G101" s="25"/>
-      <c r="H101" s="25"/>
-      <c r="I101" s="24"/>
-      <c r="J101" s="26"/>
-      <c r="K101" s="27"/>
+      <c r="H101" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="I101" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="J101" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K101" s="27" t="n">
+        <v>3120000</v>
+      </c>
       <c r="L101" s="26"/>
-      <c r="M101" s="8" t="str">
+      <c r="M101" s="8" t="n">
         <f aca="false">IF(K101="","",IF(J101="USD",ROUND(K101*설정!$C$4,0),K101))</f>
-        <v/>
-      </c>
-      <c r="N101" s="8" t="str">
+        <v>3120000</v>
+      </c>
+      <c r="N101" s="8" t="n">
         <f aca="false">IF(M101="","",IF(AND(I101="과세",L101="VAT포함"),ROUND(M101/(1+설정!$C$5),0),M101))</f>
-        <v/>
-      </c>
-      <c r="O101" s="8" t="str">
+        <v>3120000</v>
+      </c>
+      <c r="O101" s="8" t="n">
         <f aca="false">IF(M101="","",IF(I101="과세",IF(L101="VAT포함",M101-N101,ROUND(N101*설정!$C$5,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P101" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P101" s="8" t="n">
         <f aca="false">IF(M101="","",N101+O101)</f>
-        <v/>
+        <v>3120000</v>
       </c>
       <c r="Q101" s="26"/>
       <c r="R101" s="8" t="str">
@@ -10337,39 +10993,51 @@
       <c r="S101" s="25"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="21" t="str">
+      <c r="A102" s="21" t="n">
         <f aca="false">IF(C102="","",COUNTA($C$5:C102))</f>
-        <v/>
+        <v>98</v>
       </c>
       <c r="B102" s="22"/>
-      <c r="C102" s="23"/>
-      <c r="D102" s="26"/>
+      <c r="C102" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D102" s="26" t="s">
+        <v>6</v>
+      </c>
       <c r="E102" s="25"/>
       <c r="F102" s="7" t="str">
         <f aca="false">IF(E102="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E102,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
         <v/>
       </c>
       <c r="G102" s="25"/>
-      <c r="H102" s="25"/>
-      <c r="I102" s="24"/>
-      <c r="J102" s="26"/>
-      <c r="K102" s="27"/>
+      <c r="H102" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="I102" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="J102" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K102" s="27" t="n">
+        <v>18017500</v>
+      </c>
       <c r="L102" s="26"/>
-      <c r="M102" s="8" t="str">
+      <c r="M102" s="8" t="n">
         <f aca="false">IF(K102="","",IF(J102="USD",ROUND(K102*설정!$C$4,0),K102))</f>
-        <v/>
-      </c>
-      <c r="N102" s="8" t="str">
+        <v>18017500</v>
+      </c>
+      <c r="N102" s="8" t="n">
         <f aca="false">IF(M102="","",IF(AND(I102="과세",L102="VAT포함"),ROUND(M102/(1+설정!$C$5),0),M102))</f>
-        <v/>
-      </c>
-      <c r="O102" s="8" t="str">
+        <v>18017500</v>
+      </c>
+      <c r="O102" s="8" t="n">
         <f aca="false">IF(M102="","",IF(I102="과세",IF(L102="VAT포함",M102-N102,ROUND(N102*설정!$C$5,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P102" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P102" s="8" t="n">
         <f aca="false">IF(M102="","",N102+O102)</f>
-        <v/>
+        <v>18017500</v>
       </c>
       <c r="Q102" s="26"/>
       <c r="R102" s="8" t="str">
@@ -10379,39 +11047,51 @@
       <c r="S102" s="25"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="21" t="str">
+      <c r="A103" s="21" t="n">
         <f aca="false">IF(C103="","",COUNTA($C$5:C103))</f>
-        <v/>
+        <v>99</v>
       </c>
       <c r="B103" s="22"/>
-      <c r="C103" s="23"/>
-      <c r="D103" s="26"/>
+      <c r="C103" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D103" s="26" t="s">
+        <v>7</v>
+      </c>
       <c r="E103" s="25"/>
       <c r="F103" s="7" t="str">
         <f aca="false">IF(E103="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E103,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
         <v/>
       </c>
       <c r="G103" s="25"/>
-      <c r="H103" s="25"/>
-      <c r="I103" s="24"/>
-      <c r="J103" s="26"/>
-      <c r="K103" s="27"/>
+      <c r="H103" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="I103" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="J103" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K103" s="27" t="n">
+        <v>9932500</v>
+      </c>
       <c r="L103" s="26"/>
-      <c r="M103" s="8" t="str">
+      <c r="M103" s="8" t="n">
         <f aca="false">IF(K103="","",IF(J103="USD",ROUND(K103*설정!$C$4,0),K103))</f>
-        <v/>
-      </c>
-      <c r="N103" s="8" t="str">
+        <v>9932500</v>
+      </c>
+      <c r="N103" s="8" t="n">
         <f aca="false">IF(M103="","",IF(AND(I103="과세",L103="VAT포함"),ROUND(M103/(1+설정!$C$5),0),M103))</f>
-        <v/>
-      </c>
-      <c r="O103" s="8" t="str">
+        <v>9932500</v>
+      </c>
+      <c r="O103" s="8" t="n">
         <f aca="false">IF(M103="","",IF(I103="과세",IF(L103="VAT포함",M103-N103,ROUND(N103*설정!$C$5,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P103" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P103" s="8" t="n">
         <f aca="false">IF(M103="","",N103+O103)</f>
-        <v/>
+        <v>9932500</v>
       </c>
       <c r="Q103" s="26"/>
       <c r="R103" s="8" t="str">
@@ -10421,46 +11101,62 @@
       <c r="S103" s="25"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="21" t="str">
+      <c r="A104" s="21" t="n">
         <f aca="false">IF(C104="","",COUNTA($C$5:C104))</f>
-        <v/>
+        <v>100</v>
       </c>
       <c r="B104" s="22"/>
-      <c r="C104" s="23"/>
-      <c r="D104" s="26"/>
+      <c r="C104" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="D104" s="24" t="s">
+        <v>57</v>
+      </c>
       <c r="E104" s="25"/>
       <c r="F104" s="7" t="str">
         <f aca="false">IF(E104="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E104,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
         <v/>
       </c>
       <c r="G104" s="25"/>
-      <c r="H104" s="25"/>
-      <c r="I104" s="24"/>
-      <c r="J104" s="26"/>
-      <c r="K104" s="27"/>
+      <c r="H104" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="I104" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="J104" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K104" s="27" t="n">
+        <v>12600000</v>
+      </c>
       <c r="L104" s="26"/>
-      <c r="M104" s="8" t="str">
+      <c r="M104" s="8" t="n">
         <f aca="false">IF(K104="","",IF(J104="USD",ROUND(K104*설정!$C$4,0),K104))</f>
-        <v/>
-      </c>
-      <c r="N104" s="8" t="str">
+        <v>12600000</v>
+      </c>
+      <c r="N104" s="8" t="n">
         <f aca="false">IF(M104="","",IF(AND(I104="과세",L104="VAT포함"),ROUND(M104/(1+설정!$C$5),0),M104))</f>
-        <v/>
-      </c>
-      <c r="O104" s="8" t="str">
+        <v>12600000</v>
+      </c>
+      <c r="O104" s="8" t="n">
         <f aca="false">IF(M104="","",IF(I104="과세",IF(L104="VAT포함",M104-N104,ROUND(N104*설정!$C$5,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P104" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P104" s="8" t="n">
         <f aca="false">IF(M104="","",N104+O104)</f>
-        <v/>
-      </c>
-      <c r="Q104" s="26"/>
-      <c r="R104" s="8" t="str">
+        <v>12600000</v>
+      </c>
+      <c r="Q104" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="R104" s="8" t="n">
         <f aca="false">IF(OR(M104="",Q104&lt;&gt;"Y"),"",ROUND(N104*설정!$C$5,0))</f>
-        <v/>
-      </c>
-      <c r="S104" s="25"/>
+        <v>1260000</v>
+      </c>
+      <c r="S104" s="23" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="21" t="str">
@@ -15755,75 +16451,1083 @@
       <c r="S230" s="25"/>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="13"/>
-      <c r="B231" s="13"/>
-      <c r="C231" s="18" t="s">
+      <c r="A231" s="21" t="str">
+        <f aca="false">IF(C231="","",COUNTA($C$5:C231))</f>
+        <v/>
+      </c>
+      <c r="B231" s="22"/>
+      <c r="C231" s="23"/>
+      <c r="D231" s="26"/>
+      <c r="E231" s="25"/>
+      <c r="F231" s="7" t="str">
+        <f aca="false">IF(E231="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E231,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
+        <v/>
+      </c>
+      <c r="G231" s="25"/>
+      <c r="H231" s="25"/>
+      <c r="I231" s="24"/>
+      <c r="J231" s="26"/>
+      <c r="K231" s="27"/>
+      <c r="L231" s="26"/>
+      <c r="M231" s="8" t="str">
+        <f aca="false">IF(K231="","",IF(J231="USD",ROUND(K231*설정!$C$4,0),K231))</f>
+        <v/>
+      </c>
+      <c r="N231" s="8" t="str">
+        <f aca="false">IF(M231="","",IF(AND(I231="과세",L231="VAT포함"),ROUND(M231/(1+설정!$C$5),0),M231))</f>
+        <v/>
+      </c>
+      <c r="O231" s="8" t="str">
+        <f aca="false">IF(M231="","",IF(I231="과세",IF(L231="VAT포함",M231-N231,ROUND(N231*설정!$C$5,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P231" s="8" t="str">
+        <f aca="false">IF(M231="","",N231+O231)</f>
+        <v/>
+      </c>
+      <c r="Q231" s="26"/>
+      <c r="R231" s="8" t="str">
+        <f aca="false">IF(OR(M231="",Q231&lt;&gt;"Y"),"",ROUND(N231*설정!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="S231" s="25"/>
+    </row>
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="21" t="str">
+        <f aca="false">IF(C232="","",COUNTA($C$5:C232))</f>
+        <v/>
+      </c>
+      <c r="B232" s="22"/>
+      <c r="C232" s="23"/>
+      <c r="D232" s="26"/>
+      <c r="E232" s="25"/>
+      <c r="F232" s="7" t="str">
+        <f aca="false">IF(E232="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E232,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
+        <v/>
+      </c>
+      <c r="G232" s="25"/>
+      <c r="H232" s="25"/>
+      <c r="I232" s="24"/>
+      <c r="J232" s="26"/>
+      <c r="K232" s="27"/>
+      <c r="L232" s="26"/>
+      <c r="M232" s="8" t="str">
+        <f aca="false">IF(K232="","",IF(J232="USD",ROUND(K232*설정!$C$4,0),K232))</f>
+        <v/>
+      </c>
+      <c r="N232" s="8" t="str">
+        <f aca="false">IF(M232="","",IF(AND(I232="과세",L232="VAT포함"),ROUND(M232/(1+설정!$C$5),0),M232))</f>
+        <v/>
+      </c>
+      <c r="O232" s="8" t="str">
+        <f aca="false">IF(M232="","",IF(I232="과세",IF(L232="VAT포함",M232-N232,ROUND(N232*설정!$C$5,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P232" s="8" t="str">
+        <f aca="false">IF(M232="","",N232+O232)</f>
+        <v/>
+      </c>
+      <c r="Q232" s="26"/>
+      <c r="R232" s="8" t="str">
+        <f aca="false">IF(OR(M232="",Q232&lt;&gt;"Y"),"",ROUND(N232*설정!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="S232" s="25"/>
+    </row>
+    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A233" s="21" t="str">
+        <f aca="false">IF(C233="","",COUNTA($C$5:C233))</f>
+        <v/>
+      </c>
+      <c r="B233" s="22"/>
+      <c r="C233" s="23"/>
+      <c r="D233" s="26"/>
+      <c r="E233" s="25"/>
+      <c r="F233" s="7" t="str">
+        <f aca="false">IF(E233="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E233,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
+        <v/>
+      </c>
+      <c r="G233" s="25"/>
+      <c r="H233" s="25"/>
+      <c r="I233" s="24"/>
+      <c r="J233" s="26"/>
+      <c r="K233" s="27"/>
+      <c r="L233" s="26"/>
+      <c r="M233" s="8" t="str">
+        <f aca="false">IF(K233="","",IF(J233="USD",ROUND(K233*설정!$C$4,0),K233))</f>
+        <v/>
+      </c>
+      <c r="N233" s="8" t="str">
+        <f aca="false">IF(M233="","",IF(AND(I233="과세",L233="VAT포함"),ROUND(M233/(1+설정!$C$5),0),M233))</f>
+        <v/>
+      </c>
+      <c r="O233" s="8" t="str">
+        <f aca="false">IF(M233="","",IF(I233="과세",IF(L233="VAT포함",M233-N233,ROUND(N233*설정!$C$5,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P233" s="8" t="str">
+        <f aca="false">IF(M233="","",N233+O233)</f>
+        <v/>
+      </c>
+      <c r="Q233" s="26"/>
+      <c r="R233" s="8" t="str">
+        <f aca="false">IF(OR(M233="",Q233&lt;&gt;"Y"),"",ROUND(N233*설정!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="S233" s="25"/>
+    </row>
+    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A234" s="21" t="str">
+        <f aca="false">IF(C234="","",COUNTA($C$5:C234))</f>
+        <v/>
+      </c>
+      <c r="B234" s="22"/>
+      <c r="C234" s="23"/>
+      <c r="D234" s="26"/>
+      <c r="E234" s="25"/>
+      <c r="F234" s="7" t="str">
+        <f aca="false">IF(E234="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E234,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
+        <v/>
+      </c>
+      <c r="G234" s="25"/>
+      <c r="H234" s="25"/>
+      <c r="I234" s="24"/>
+      <c r="J234" s="26"/>
+      <c r="K234" s="27"/>
+      <c r="L234" s="26"/>
+      <c r="M234" s="8" t="str">
+        <f aca="false">IF(K234="","",IF(J234="USD",ROUND(K234*설정!$C$4,0),K234))</f>
+        <v/>
+      </c>
+      <c r="N234" s="8" t="str">
+        <f aca="false">IF(M234="","",IF(AND(I234="과세",L234="VAT포함"),ROUND(M234/(1+설정!$C$5),0),M234))</f>
+        <v/>
+      </c>
+      <c r="O234" s="8" t="str">
+        <f aca="false">IF(M234="","",IF(I234="과세",IF(L234="VAT포함",M234-N234,ROUND(N234*설정!$C$5,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P234" s="8" t="str">
+        <f aca="false">IF(M234="","",N234+O234)</f>
+        <v/>
+      </c>
+      <c r="Q234" s="26"/>
+      <c r="R234" s="8" t="str">
+        <f aca="false">IF(OR(M234="",Q234&lt;&gt;"Y"),"",ROUND(N234*설정!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="S234" s="25"/>
+    </row>
+    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A235" s="21" t="str">
+        <f aca="false">IF(C235="","",COUNTA($C$5:C235))</f>
+        <v/>
+      </c>
+      <c r="B235" s="22"/>
+      <c r="C235" s="23"/>
+      <c r="D235" s="26"/>
+      <c r="E235" s="25"/>
+      <c r="F235" s="7" t="str">
+        <f aca="false">IF(E235="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E235,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
+        <v/>
+      </c>
+      <c r="G235" s="25"/>
+      <c r="H235" s="25"/>
+      <c r="I235" s="24"/>
+      <c r="J235" s="26"/>
+      <c r="K235" s="27"/>
+      <c r="L235" s="26"/>
+      <c r="M235" s="8" t="str">
+        <f aca="false">IF(K235="","",IF(J235="USD",ROUND(K235*설정!$C$4,0),K235))</f>
+        <v/>
+      </c>
+      <c r="N235" s="8" t="str">
+        <f aca="false">IF(M235="","",IF(AND(I235="과세",L235="VAT포함"),ROUND(M235/(1+설정!$C$5),0),M235))</f>
+        <v/>
+      </c>
+      <c r="O235" s="8" t="str">
+        <f aca="false">IF(M235="","",IF(I235="과세",IF(L235="VAT포함",M235-N235,ROUND(N235*설정!$C$5,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P235" s="8" t="str">
+        <f aca="false">IF(M235="","",N235+O235)</f>
+        <v/>
+      </c>
+      <c r="Q235" s="26"/>
+      <c r="R235" s="8" t="str">
+        <f aca="false">IF(OR(M235="",Q235&lt;&gt;"Y"),"",ROUND(N235*설정!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="S235" s="25"/>
+    </row>
+    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A236" s="21" t="str">
+        <f aca="false">IF(C236="","",COUNTA($C$5:C236))</f>
+        <v/>
+      </c>
+      <c r="B236" s="22"/>
+      <c r="C236" s="23"/>
+      <c r="D236" s="26"/>
+      <c r="E236" s="25"/>
+      <c r="F236" s="7" t="str">
+        <f aca="false">IF(E236="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E236,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
+        <v/>
+      </c>
+      <c r="G236" s="25"/>
+      <c r="H236" s="25"/>
+      <c r="I236" s="24"/>
+      <c r="J236" s="26"/>
+      <c r="K236" s="27"/>
+      <c r="L236" s="26"/>
+      <c r="M236" s="8" t="str">
+        <f aca="false">IF(K236="","",IF(J236="USD",ROUND(K236*설정!$C$4,0),K236))</f>
+        <v/>
+      </c>
+      <c r="N236" s="8" t="str">
+        <f aca="false">IF(M236="","",IF(AND(I236="과세",L236="VAT포함"),ROUND(M236/(1+설정!$C$5),0),M236))</f>
+        <v/>
+      </c>
+      <c r="O236" s="8" t="str">
+        <f aca="false">IF(M236="","",IF(I236="과세",IF(L236="VAT포함",M236-N236,ROUND(N236*설정!$C$5,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P236" s="8" t="str">
+        <f aca="false">IF(M236="","",N236+O236)</f>
+        <v/>
+      </c>
+      <c r="Q236" s="26"/>
+      <c r="R236" s="8" t="str">
+        <f aca="false">IF(OR(M236="",Q236&lt;&gt;"Y"),"",ROUND(N236*설정!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="S236" s="25"/>
+    </row>
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="21" t="str">
+        <f aca="false">IF(C237="","",COUNTA($C$5:C237))</f>
+        <v/>
+      </c>
+      <c r="B237" s="22"/>
+      <c r="C237" s="23"/>
+      <c r="D237" s="26"/>
+      <c r="E237" s="25"/>
+      <c r="F237" s="7" t="str">
+        <f aca="false">IF(E237="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E237,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
+        <v/>
+      </c>
+      <c r="G237" s="25"/>
+      <c r="H237" s="25"/>
+      <c r="I237" s="24"/>
+      <c r="J237" s="26"/>
+      <c r="K237" s="27"/>
+      <c r="L237" s="26"/>
+      <c r="M237" s="8" t="str">
+        <f aca="false">IF(K237="","",IF(J237="USD",ROUND(K237*설정!$C$4,0),K237))</f>
+        <v/>
+      </c>
+      <c r="N237" s="8" t="str">
+        <f aca="false">IF(M237="","",IF(AND(I237="과세",L237="VAT포함"),ROUND(M237/(1+설정!$C$5),0),M237))</f>
+        <v/>
+      </c>
+      <c r="O237" s="8" t="str">
+        <f aca="false">IF(M237="","",IF(I237="과세",IF(L237="VAT포함",M237-N237,ROUND(N237*설정!$C$5,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P237" s="8" t="str">
+        <f aca="false">IF(M237="","",N237+O237)</f>
+        <v/>
+      </c>
+      <c r="Q237" s="26"/>
+      <c r="R237" s="8" t="str">
+        <f aca="false">IF(OR(M237="",Q237&lt;&gt;"Y"),"",ROUND(N237*설정!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="S237" s="25"/>
+    </row>
+    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A238" s="21" t="str">
+        <f aca="false">IF(C238="","",COUNTA($C$5:C238))</f>
+        <v/>
+      </c>
+      <c r="B238" s="22"/>
+      <c r="C238" s="23"/>
+      <c r="D238" s="26"/>
+      <c r="E238" s="25"/>
+      <c r="F238" s="7" t="str">
+        <f aca="false">IF(E238="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E238,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
+        <v/>
+      </c>
+      <c r="G238" s="25"/>
+      <c r="H238" s="25"/>
+      <c r="I238" s="24"/>
+      <c r="J238" s="26"/>
+      <c r="K238" s="27"/>
+      <c r="L238" s="26"/>
+      <c r="M238" s="8" t="str">
+        <f aca="false">IF(K238="","",IF(J238="USD",ROUND(K238*설정!$C$4,0),K238))</f>
+        <v/>
+      </c>
+      <c r="N238" s="8" t="str">
+        <f aca="false">IF(M238="","",IF(AND(I238="과세",L238="VAT포함"),ROUND(M238/(1+설정!$C$5),0),M238))</f>
+        <v/>
+      </c>
+      <c r="O238" s="8" t="str">
+        <f aca="false">IF(M238="","",IF(I238="과세",IF(L238="VAT포함",M238-N238,ROUND(N238*설정!$C$5,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P238" s="8" t="str">
+        <f aca="false">IF(M238="","",N238+O238)</f>
+        <v/>
+      </c>
+      <c r="Q238" s="26"/>
+      <c r="R238" s="8" t="str">
+        <f aca="false">IF(OR(M238="",Q238&lt;&gt;"Y"),"",ROUND(N238*설정!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="S238" s="25"/>
+    </row>
+    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A239" s="21" t="str">
+        <f aca="false">IF(C239="","",COUNTA($C$5:C239))</f>
+        <v/>
+      </c>
+      <c r="B239" s="22"/>
+      <c r="C239" s="23"/>
+      <c r="D239" s="26"/>
+      <c r="E239" s="25"/>
+      <c r="F239" s="7" t="str">
+        <f aca="false">IF(E239="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E239,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
+        <v/>
+      </c>
+      <c r="G239" s="25"/>
+      <c r="H239" s="25"/>
+      <c r="I239" s="24"/>
+      <c r="J239" s="26"/>
+      <c r="K239" s="27"/>
+      <c r="L239" s="26"/>
+      <c r="M239" s="8" t="str">
+        <f aca="false">IF(K239="","",IF(J239="USD",ROUND(K239*설정!$C$4,0),K239))</f>
+        <v/>
+      </c>
+      <c r="N239" s="8" t="str">
+        <f aca="false">IF(M239="","",IF(AND(I239="과세",L239="VAT포함"),ROUND(M239/(1+설정!$C$5),0),M239))</f>
+        <v/>
+      </c>
+      <c r="O239" s="8" t="str">
+        <f aca="false">IF(M239="","",IF(I239="과세",IF(L239="VAT포함",M239-N239,ROUND(N239*설정!$C$5,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P239" s="8" t="str">
+        <f aca="false">IF(M239="","",N239+O239)</f>
+        <v/>
+      </c>
+      <c r="Q239" s="26"/>
+      <c r="R239" s="8" t="str">
+        <f aca="false">IF(OR(M239="",Q239&lt;&gt;"Y"),"",ROUND(N239*설정!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="S239" s="25"/>
+    </row>
+    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A240" s="21" t="str">
+        <f aca="false">IF(C240="","",COUNTA($C$5:C240))</f>
+        <v/>
+      </c>
+      <c r="B240" s="22"/>
+      <c r="C240" s="23"/>
+      <c r="D240" s="26"/>
+      <c r="E240" s="25"/>
+      <c r="F240" s="7" t="str">
+        <f aca="false">IF(E240="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E240,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
+        <v/>
+      </c>
+      <c r="G240" s="25"/>
+      <c r="H240" s="25"/>
+      <c r="I240" s="24"/>
+      <c r="J240" s="26"/>
+      <c r="K240" s="27"/>
+      <c r="L240" s="26"/>
+      <c r="M240" s="8" t="str">
+        <f aca="false">IF(K240="","",IF(J240="USD",ROUND(K240*설정!$C$4,0),K240))</f>
+        <v/>
+      </c>
+      <c r="N240" s="8" t="str">
+        <f aca="false">IF(M240="","",IF(AND(I240="과세",L240="VAT포함"),ROUND(M240/(1+설정!$C$5),0),M240))</f>
+        <v/>
+      </c>
+      <c r="O240" s="8" t="str">
+        <f aca="false">IF(M240="","",IF(I240="과세",IF(L240="VAT포함",M240-N240,ROUND(N240*설정!$C$5,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P240" s="8" t="str">
+        <f aca="false">IF(M240="","",N240+O240)</f>
+        <v/>
+      </c>
+      <c r="Q240" s="26"/>
+      <c r="R240" s="8" t="str">
+        <f aca="false">IF(OR(M240="",Q240&lt;&gt;"Y"),"",ROUND(N240*설정!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="S240" s="25"/>
+    </row>
+    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A241" s="21" t="str">
+        <f aca="false">IF(C241="","",COUNTA($C$5:C241))</f>
+        <v/>
+      </c>
+      <c r="B241" s="22"/>
+      <c r="C241" s="23"/>
+      <c r="D241" s="26"/>
+      <c r="E241" s="25"/>
+      <c r="F241" s="7" t="str">
+        <f aca="false">IF(E241="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E241,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
+        <v/>
+      </c>
+      <c r="G241" s="25"/>
+      <c r="H241" s="25"/>
+      <c r="I241" s="24"/>
+      <c r="J241" s="26"/>
+      <c r="K241" s="27"/>
+      <c r="L241" s="26"/>
+      <c r="M241" s="8" t="str">
+        <f aca="false">IF(K241="","",IF(J241="USD",ROUND(K241*설정!$C$4,0),K241))</f>
+        <v/>
+      </c>
+      <c r="N241" s="8" t="str">
+        <f aca="false">IF(M241="","",IF(AND(I241="과세",L241="VAT포함"),ROUND(M241/(1+설정!$C$5),0),M241))</f>
+        <v/>
+      </c>
+      <c r="O241" s="8" t="str">
+        <f aca="false">IF(M241="","",IF(I241="과세",IF(L241="VAT포함",M241-N241,ROUND(N241*설정!$C$5,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P241" s="8" t="str">
+        <f aca="false">IF(M241="","",N241+O241)</f>
+        <v/>
+      </c>
+      <c r="Q241" s="26"/>
+      <c r="R241" s="8" t="str">
+        <f aca="false">IF(OR(M241="",Q241&lt;&gt;"Y"),"",ROUND(N241*설정!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="S241" s="25"/>
+    </row>
+    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A242" s="21" t="str">
+        <f aca="false">IF(C242="","",COUNTA($C$5:C242))</f>
+        <v/>
+      </c>
+      <c r="B242" s="22"/>
+      <c r="C242" s="23"/>
+      <c r="D242" s="26"/>
+      <c r="E242" s="25"/>
+      <c r="F242" s="7" t="str">
+        <f aca="false">IF(E242="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E242,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
+        <v/>
+      </c>
+      <c r="G242" s="25"/>
+      <c r="H242" s="25"/>
+      <c r="I242" s="24"/>
+      <c r="J242" s="26"/>
+      <c r="K242" s="27"/>
+      <c r="L242" s="26"/>
+      <c r="M242" s="8" t="str">
+        <f aca="false">IF(K242="","",IF(J242="USD",ROUND(K242*설정!$C$4,0),K242))</f>
+        <v/>
+      </c>
+      <c r="N242" s="8" t="str">
+        <f aca="false">IF(M242="","",IF(AND(I242="과세",L242="VAT포함"),ROUND(M242/(1+설정!$C$5),0),M242))</f>
+        <v/>
+      </c>
+      <c r="O242" s="8" t="str">
+        <f aca="false">IF(M242="","",IF(I242="과세",IF(L242="VAT포함",M242-N242,ROUND(N242*설정!$C$5,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P242" s="8" t="str">
+        <f aca="false">IF(M242="","",N242+O242)</f>
+        <v/>
+      </c>
+      <c r="Q242" s="26"/>
+      <c r="R242" s="8" t="str">
+        <f aca="false">IF(OR(M242="",Q242&lt;&gt;"Y"),"",ROUND(N242*설정!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="S242" s="25"/>
+    </row>
+    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="21" t="str">
+        <f aca="false">IF(C243="","",COUNTA($C$5:C243))</f>
+        <v/>
+      </c>
+      <c r="B243" s="22"/>
+      <c r="C243" s="23"/>
+      <c r="D243" s="26"/>
+      <c r="E243" s="25"/>
+      <c r="F243" s="7" t="str">
+        <f aca="false">IF(E243="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E243,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
+        <v/>
+      </c>
+      <c r="G243" s="25"/>
+      <c r="H243" s="25"/>
+      <c r="I243" s="24"/>
+      <c r="J243" s="26"/>
+      <c r="K243" s="27"/>
+      <c r="L243" s="26"/>
+      <c r="M243" s="8" t="str">
+        <f aca="false">IF(K243="","",IF(J243="USD",ROUND(K243*설정!$C$4,0),K243))</f>
+        <v/>
+      </c>
+      <c r="N243" s="8" t="str">
+        <f aca="false">IF(M243="","",IF(AND(I243="과세",L243="VAT포함"),ROUND(M243/(1+설정!$C$5),0),M243))</f>
+        <v/>
+      </c>
+      <c r="O243" s="8" t="str">
+        <f aca="false">IF(M243="","",IF(I243="과세",IF(L243="VAT포함",M243-N243,ROUND(N243*설정!$C$5,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P243" s="8" t="str">
+        <f aca="false">IF(M243="","",N243+O243)</f>
+        <v/>
+      </c>
+      <c r="Q243" s="26"/>
+      <c r="R243" s="8" t="str">
+        <f aca="false">IF(OR(M243="",Q243&lt;&gt;"Y"),"",ROUND(N243*설정!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="S243" s="25"/>
+    </row>
+    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A244" s="21" t="str">
+        <f aca="false">IF(C244="","",COUNTA($C$5:C244))</f>
+        <v/>
+      </c>
+      <c r="B244" s="22"/>
+      <c r="C244" s="23"/>
+      <c r="D244" s="26"/>
+      <c r="E244" s="25"/>
+      <c r="F244" s="7" t="str">
+        <f aca="false">IF(E244="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E244,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
+        <v/>
+      </c>
+      <c r="G244" s="25"/>
+      <c r="H244" s="25"/>
+      <c r="I244" s="24"/>
+      <c r="J244" s="26"/>
+      <c r="K244" s="27"/>
+      <c r="L244" s="26"/>
+      <c r="M244" s="8" t="str">
+        <f aca="false">IF(K244="","",IF(J244="USD",ROUND(K244*설정!$C$4,0),K244))</f>
+        <v/>
+      </c>
+      <c r="N244" s="8" t="str">
+        <f aca="false">IF(M244="","",IF(AND(I244="과세",L244="VAT포함"),ROUND(M244/(1+설정!$C$5),0),M244))</f>
+        <v/>
+      </c>
+      <c r="O244" s="8" t="str">
+        <f aca="false">IF(M244="","",IF(I244="과세",IF(L244="VAT포함",M244-N244,ROUND(N244*설정!$C$5,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P244" s="8" t="str">
+        <f aca="false">IF(M244="","",N244+O244)</f>
+        <v/>
+      </c>
+      <c r="Q244" s="26"/>
+      <c r="R244" s="8" t="str">
+        <f aca="false">IF(OR(M244="",Q244&lt;&gt;"Y"),"",ROUND(N244*설정!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="S244" s="25"/>
+    </row>
+    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A245" s="21" t="str">
+        <f aca="false">IF(C245="","",COUNTA($C$5:C245))</f>
+        <v/>
+      </c>
+      <c r="B245" s="22"/>
+      <c r="C245" s="23"/>
+      <c r="D245" s="26"/>
+      <c r="E245" s="25"/>
+      <c r="F245" s="7" t="str">
+        <f aca="false">IF(E245="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E245,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
+        <v/>
+      </c>
+      <c r="G245" s="25"/>
+      <c r="H245" s="25"/>
+      <c r="I245" s="24"/>
+      <c r="J245" s="26"/>
+      <c r="K245" s="27"/>
+      <c r="L245" s="26"/>
+      <c r="M245" s="8" t="str">
+        <f aca="false">IF(K245="","",IF(J245="USD",ROUND(K245*설정!$C$4,0),K245))</f>
+        <v/>
+      </c>
+      <c r="N245" s="8" t="str">
+        <f aca="false">IF(M245="","",IF(AND(I245="과세",L245="VAT포함"),ROUND(M245/(1+설정!$C$5),0),M245))</f>
+        <v/>
+      </c>
+      <c r="O245" s="8" t="str">
+        <f aca="false">IF(M245="","",IF(I245="과세",IF(L245="VAT포함",M245-N245,ROUND(N245*설정!$C$5,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P245" s="8" t="str">
+        <f aca="false">IF(M245="","",N245+O245)</f>
+        <v/>
+      </c>
+      <c r="Q245" s="26"/>
+      <c r="R245" s="8" t="str">
+        <f aca="false">IF(OR(M245="",Q245&lt;&gt;"Y"),"",ROUND(N245*설정!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="S245" s="25"/>
+    </row>
+    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A246" s="21" t="str">
+        <f aca="false">IF(C246="","",COUNTA($C$5:C246))</f>
+        <v/>
+      </c>
+      <c r="B246" s="22"/>
+      <c r="C246" s="23"/>
+      <c r="D246" s="26"/>
+      <c r="E246" s="25"/>
+      <c r="F246" s="7" t="str">
+        <f aca="false">IF(E246="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E246,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
+        <v/>
+      </c>
+      <c r="G246" s="25"/>
+      <c r="H246" s="25"/>
+      <c r="I246" s="24"/>
+      <c r="J246" s="26"/>
+      <c r="K246" s="27"/>
+      <c r="L246" s="26"/>
+      <c r="M246" s="8" t="str">
+        <f aca="false">IF(K246="","",IF(J246="USD",ROUND(K246*설정!$C$4,0),K246))</f>
+        <v/>
+      </c>
+      <c r="N246" s="8" t="str">
+        <f aca="false">IF(M246="","",IF(AND(I246="과세",L246="VAT포함"),ROUND(M246/(1+설정!$C$5),0),M246))</f>
+        <v/>
+      </c>
+      <c r="O246" s="8" t="str">
+        <f aca="false">IF(M246="","",IF(I246="과세",IF(L246="VAT포함",M246-N246,ROUND(N246*설정!$C$5,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P246" s="8" t="str">
+        <f aca="false">IF(M246="","",N246+O246)</f>
+        <v/>
+      </c>
+      <c r="Q246" s="26"/>
+      <c r="R246" s="8" t="str">
+        <f aca="false">IF(OR(M246="",Q246&lt;&gt;"Y"),"",ROUND(N246*설정!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="S246" s="25"/>
+    </row>
+    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A247" s="21" t="str">
+        <f aca="false">IF(C247="","",COUNTA($C$5:C247))</f>
+        <v/>
+      </c>
+      <c r="B247" s="22"/>
+      <c r="C247" s="23"/>
+      <c r="D247" s="26"/>
+      <c r="E247" s="25"/>
+      <c r="F247" s="7" t="str">
+        <f aca="false">IF(E247="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E247,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
+        <v/>
+      </c>
+      <c r="G247" s="25"/>
+      <c r="H247" s="25"/>
+      <c r="I247" s="24"/>
+      <c r="J247" s="26"/>
+      <c r="K247" s="27"/>
+      <c r="L247" s="26"/>
+      <c r="M247" s="8" t="str">
+        <f aca="false">IF(K247="","",IF(J247="USD",ROUND(K247*설정!$C$4,0),K247))</f>
+        <v/>
+      </c>
+      <c r="N247" s="8" t="str">
+        <f aca="false">IF(M247="","",IF(AND(I247="과세",L247="VAT포함"),ROUND(M247/(1+설정!$C$5),0),M247))</f>
+        <v/>
+      </c>
+      <c r="O247" s="8" t="str">
+        <f aca="false">IF(M247="","",IF(I247="과세",IF(L247="VAT포함",M247-N247,ROUND(N247*설정!$C$5,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P247" s="8" t="str">
+        <f aca="false">IF(M247="","",N247+O247)</f>
+        <v/>
+      </c>
+      <c r="Q247" s="26"/>
+      <c r="R247" s="8" t="str">
+        <f aca="false">IF(OR(M247="",Q247&lt;&gt;"Y"),"",ROUND(N247*설정!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="S247" s="25"/>
+    </row>
+    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A248" s="21" t="str">
+        <f aca="false">IF(C248="","",COUNTA($C$5:C248))</f>
+        <v/>
+      </c>
+      <c r="B248" s="22"/>
+      <c r="C248" s="23"/>
+      <c r="D248" s="26"/>
+      <c r="E248" s="25"/>
+      <c r="F248" s="7" t="str">
+        <f aca="false">IF(E248="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E248,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
+        <v/>
+      </c>
+      <c r="G248" s="25"/>
+      <c r="H248" s="25"/>
+      <c r="I248" s="24"/>
+      <c r="J248" s="26"/>
+      <c r="K248" s="27"/>
+      <c r="L248" s="26"/>
+      <c r="M248" s="8" t="str">
+        <f aca="false">IF(K248="","",IF(J248="USD",ROUND(K248*설정!$C$4,0),K248))</f>
+        <v/>
+      </c>
+      <c r="N248" s="8" t="str">
+        <f aca="false">IF(M248="","",IF(AND(I248="과세",L248="VAT포함"),ROUND(M248/(1+설정!$C$5),0),M248))</f>
+        <v/>
+      </c>
+      <c r="O248" s="8" t="str">
+        <f aca="false">IF(M248="","",IF(I248="과세",IF(L248="VAT포함",M248-N248,ROUND(N248*설정!$C$5,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P248" s="8" t="str">
+        <f aca="false">IF(M248="","",N248+O248)</f>
+        <v/>
+      </c>
+      <c r="Q248" s="26"/>
+      <c r="R248" s="8" t="str">
+        <f aca="false">IF(OR(M248="",Q248&lt;&gt;"Y"),"",ROUND(N248*설정!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="S248" s="25"/>
+    </row>
+    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A249" s="21" t="str">
+        <f aca="false">IF(C249="","",COUNTA($C$5:C249))</f>
+        <v/>
+      </c>
+      <c r="B249" s="22"/>
+      <c r="C249" s="23"/>
+      <c r="D249" s="26"/>
+      <c r="E249" s="25"/>
+      <c r="F249" s="7" t="str">
+        <f aca="false">IF(E249="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E249,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
+        <v/>
+      </c>
+      <c r="G249" s="25"/>
+      <c r="H249" s="25"/>
+      <c r="I249" s="24"/>
+      <c r="J249" s="26"/>
+      <c r="K249" s="27"/>
+      <c r="L249" s="26"/>
+      <c r="M249" s="8" t="str">
+        <f aca="false">IF(K249="","",IF(J249="USD",ROUND(K249*설정!$C$4,0),K249))</f>
+        <v/>
+      </c>
+      <c r="N249" s="8" t="str">
+        <f aca="false">IF(M249="","",IF(AND(I249="과세",L249="VAT포함"),ROUND(M249/(1+설정!$C$5),0),M249))</f>
+        <v/>
+      </c>
+      <c r="O249" s="8" t="str">
+        <f aca="false">IF(M249="","",IF(I249="과세",IF(L249="VAT포함",M249-N249,ROUND(N249*설정!$C$5,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P249" s="8" t="str">
+        <f aca="false">IF(M249="","",N249+O249)</f>
+        <v/>
+      </c>
+      <c r="Q249" s="26"/>
+      <c r="R249" s="8" t="str">
+        <f aca="false">IF(OR(M249="",Q249&lt;&gt;"Y"),"",ROUND(N249*설정!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="S249" s="25"/>
+    </row>
+    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A250" s="21" t="str">
+        <f aca="false">IF(C250="","",COUNTA($C$5:C250))</f>
+        <v/>
+      </c>
+      <c r="B250" s="22"/>
+      <c r="C250" s="23"/>
+      <c r="D250" s="26"/>
+      <c r="E250" s="25"/>
+      <c r="F250" s="7" t="str">
+        <f aca="false">IF(E250="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E250,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
+        <v/>
+      </c>
+      <c r="G250" s="25"/>
+      <c r="H250" s="25"/>
+      <c r="I250" s="24"/>
+      <c r="J250" s="26"/>
+      <c r="K250" s="27"/>
+      <c r="L250" s="26"/>
+      <c r="M250" s="8" t="str">
+        <f aca="false">IF(K250="","",IF(J250="USD",ROUND(K250*설정!$C$4,0),K250))</f>
+        <v/>
+      </c>
+      <c r="N250" s="8" t="str">
+        <f aca="false">IF(M250="","",IF(AND(I250="과세",L250="VAT포함"),ROUND(M250/(1+설정!$C$5),0),M250))</f>
+        <v/>
+      </c>
+      <c r="O250" s="8" t="str">
+        <f aca="false">IF(M250="","",IF(I250="과세",IF(L250="VAT포함",M250-N250,ROUND(N250*설정!$C$5,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P250" s="8" t="str">
+        <f aca="false">IF(M250="","",N250+O250)</f>
+        <v/>
+      </c>
+      <c r="Q250" s="26"/>
+      <c r="R250" s="8" t="str">
+        <f aca="false">IF(OR(M250="",Q250&lt;&gt;"Y"),"",ROUND(N250*설정!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="S250" s="25"/>
+    </row>
+    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A251" s="21" t="str">
+        <f aca="false">IF(C251="","",COUNTA($C$5:C251))</f>
+        <v/>
+      </c>
+      <c r="B251" s="22"/>
+      <c r="C251" s="23"/>
+      <c r="D251" s="26"/>
+      <c r="E251" s="25"/>
+      <c r="F251" s="7" t="str">
+        <f aca="false">IF(E251="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E251,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
+        <v/>
+      </c>
+      <c r="G251" s="25"/>
+      <c r="H251" s="25"/>
+      <c r="I251" s="24"/>
+      <c r="J251" s="26"/>
+      <c r="K251" s="27"/>
+      <c r="L251" s="26"/>
+      <c r="M251" s="8" t="str">
+        <f aca="false">IF(K251="","",IF(J251="USD",ROUND(K251*설정!$C$4,0),K251))</f>
+        <v/>
+      </c>
+      <c r="N251" s="8" t="str">
+        <f aca="false">IF(M251="","",IF(AND(I251="과세",L251="VAT포함"),ROUND(M251/(1+설정!$C$5),0),M251))</f>
+        <v/>
+      </c>
+      <c r="O251" s="8" t="str">
+        <f aca="false">IF(M251="","",IF(I251="과세",IF(L251="VAT포함",M251-N251,ROUND(N251*설정!$C$5,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P251" s="8" t="str">
+        <f aca="false">IF(M251="","",N251+O251)</f>
+        <v/>
+      </c>
+      <c r="Q251" s="26"/>
+      <c r="R251" s="8" t="str">
+        <f aca="false">IF(OR(M251="",Q251&lt;&gt;"Y"),"",ROUND(N251*설정!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="S251" s="25"/>
+    </row>
+    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A252" s="21" t="str">
+        <f aca="false">IF(C252="","",COUNTA($C$5:C252))</f>
+        <v/>
+      </c>
+      <c r="B252" s="22"/>
+      <c r="C252" s="23"/>
+      <c r="D252" s="26"/>
+      <c r="E252" s="25"/>
+      <c r="F252" s="7" t="str">
+        <f aca="false">IF(E252="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E252,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
+        <v/>
+      </c>
+      <c r="G252" s="25"/>
+      <c r="H252" s="25"/>
+      <c r="I252" s="24"/>
+      <c r="J252" s="26"/>
+      <c r="K252" s="27"/>
+      <c r="L252" s="26"/>
+      <c r="M252" s="8" t="str">
+        <f aca="false">IF(K252="","",IF(J252="USD",ROUND(K252*설정!$C$4,0),K252))</f>
+        <v/>
+      </c>
+      <c r="N252" s="8" t="str">
+        <f aca="false">IF(M252="","",IF(AND(I252="과세",L252="VAT포함"),ROUND(M252/(1+설정!$C$5),0),M252))</f>
+        <v/>
+      </c>
+      <c r="O252" s="8" t="str">
+        <f aca="false">IF(M252="","",IF(I252="과세",IF(L252="VAT포함",M252-N252,ROUND(N252*설정!$C$5,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P252" s="8" t="str">
+        <f aca="false">IF(M252="","",N252+O252)</f>
+        <v/>
+      </c>
+      <c r="Q252" s="26"/>
+      <c r="R252" s="8" t="str">
+        <f aca="false">IF(OR(M252="",Q252&lt;&gt;"Y"),"",ROUND(N252*설정!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="S252" s="25"/>
+    </row>
+    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A253" s="21" t="str">
+        <f aca="false">IF(C253="","",COUNTA($C$5:C253))</f>
+        <v/>
+      </c>
+      <c r="B253" s="22"/>
+      <c r="C253" s="23"/>
+      <c r="D253" s="26"/>
+      <c r="E253" s="25"/>
+      <c r="F253" s="7" t="str">
+        <f aca="false">IF(E253="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E253,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
+        <v/>
+      </c>
+      <c r="G253" s="25"/>
+      <c r="H253" s="25"/>
+      <c r="I253" s="24"/>
+      <c r="J253" s="26"/>
+      <c r="K253" s="27"/>
+      <c r="L253" s="26"/>
+      <c r="M253" s="8" t="str">
+        <f aca="false">IF(K253="","",IF(J253="USD",ROUND(K253*설정!$C$4,0),K253))</f>
+        <v/>
+      </c>
+      <c r="N253" s="8" t="str">
+        <f aca="false">IF(M253="","",IF(AND(I253="과세",L253="VAT포함"),ROUND(M253/(1+설정!$C$5),0),M253))</f>
+        <v/>
+      </c>
+      <c r="O253" s="8" t="str">
+        <f aca="false">IF(M253="","",IF(I253="과세",IF(L253="VAT포함",M253-N253,ROUND(N253*설정!$C$5,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P253" s="8" t="str">
+        <f aca="false">IF(M253="","",N253+O253)</f>
+        <v/>
+      </c>
+      <c r="Q253" s="26"/>
+      <c r="R253" s="8" t="str">
+        <f aca="false">IF(OR(M253="",Q253&lt;&gt;"Y"),"",ROUND(N253*설정!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="S253" s="25"/>
+    </row>
+    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A254" s="21" t="str">
+        <f aca="false">IF(C254="","",COUNTA($C$5:C254))</f>
+        <v/>
+      </c>
+      <c r="B254" s="22"/>
+      <c r="C254" s="23"/>
+      <c r="D254" s="26"/>
+      <c r="E254" s="25"/>
+      <c r="F254" s="7" t="str">
+        <f aca="false">IF(E254="","",IFERROR(INDEX(코드관리!$C$7:$C$66,MATCH(E254,코드관리!$B$7:$B$66,0)),"미등록 코드"))</f>
+        <v/>
+      </c>
+      <c r="G254" s="25"/>
+      <c r="H254" s="25"/>
+      <c r="I254" s="24"/>
+      <c r="J254" s="26"/>
+      <c r="K254" s="27"/>
+      <c r="L254" s="26"/>
+      <c r="M254" s="8" t="str">
+        <f aca="false">IF(K254="","",IF(J254="USD",ROUND(K254*설정!$C$4,0),K254))</f>
+        <v/>
+      </c>
+      <c r="N254" s="8" t="str">
+        <f aca="false">IF(M254="","",IF(AND(I254="과세",L254="VAT포함"),ROUND(M254/(1+설정!$C$5),0),M254))</f>
+        <v/>
+      </c>
+      <c r="O254" s="8" t="str">
+        <f aca="false">IF(M254="","",IF(I254="과세",IF(L254="VAT포함",M254-N254,ROUND(N254*설정!$C$5,0)),0))</f>
+        <v/>
+      </c>
+      <c r="P254" s="8" t="str">
+        <f aca="false">IF(M254="","",N254+O254)</f>
+        <v/>
+      </c>
+      <c r="Q254" s="26"/>
+      <c r="R254" s="8" t="str">
+        <f aca="false">IF(OR(M254="",Q254&lt;&gt;"Y"),"",ROUND(N254*설정!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="S254" s="25"/>
+    </row>
+    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A255" s="13"/>
+      <c r="B255" s="13"/>
+      <c r="C255" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D231" s="13"/>
-      <c r="E231" s="13"/>
-      <c r="F231" s="13"/>
-      <c r="G231" s="13"/>
-      <c r="H231" s="13"/>
-      <c r="I231" s="13"/>
-      <c r="J231" s="13"/>
-      <c r="K231" s="13"/>
-      <c r="L231" s="13"/>
-      <c r="M231" s="13" t="n">
-        <f aca="false">SUM(M5:M230)</f>
-        <v>714327440</v>
-      </c>
-      <c r="N231" s="13" t="n">
-        <f aca="false">SUM(N5:N230)</f>
-        <v>714172240</v>
-      </c>
-      <c r="O231" s="13" t="n">
-        <f aca="false">SUM(O5:O230)</f>
+      <c r="D255" s="13"/>
+      <c r="E255" s="13"/>
+      <c r="F255" s="13"/>
+      <c r="G255" s="13"/>
+      <c r="H255" s="13"/>
+      <c r="I255" s="13"/>
+      <c r="J255" s="13"/>
+      <c r="K255" s="13"/>
+      <c r="L255" s="13"/>
+      <c r="M255" s="13" t="n">
+        <f aca="false">SUM(M5:M254)</f>
+        <v>790175936</v>
+      </c>
+      <c r="N255" s="13" t="n">
+        <f aca="false">SUM(N5:N254)</f>
+        <v>790020736</v>
+      </c>
+      <c r="O255" s="13" t="n">
+        <f aca="false">SUM(O5:O254)</f>
         <v>155200</v>
       </c>
-      <c r="P231" s="13" t="n">
-        <f aca="false">SUM(P5:P230)</f>
-        <v>714327440</v>
-      </c>
-      <c r="Q231" s="13"/>
-      <c r="R231" s="13" t="n">
-        <f aca="false">SUM(R5:R230)</f>
+      <c r="P255" s="13" t="n">
+        <f aca="false">SUM(P5:P254)</f>
+        <v>790175936</v>
+      </c>
+      <c r="Q255" s="13"/>
+      <c r="R255" s="13" t="n">
+        <f aca="false">SUM(R5:R254)</f>
         <v>3990000</v>
       </c>
-      <c r="S231" s="13"/>
+      <c r="S255" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:S230"/>
+  <autoFilter ref="A4:S254"/>
   <dataValidations count="8">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C5:C230" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C5:C254" type="list">
       <formula1>설정!$F$10:$F$30</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D5:D230" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D5:D254" type="list">
       <formula1>설정!$B$10:$B$15</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E5:E230" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E5:E254" type="list">
       <formula1>코드관리!$B$7:$B$66</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I5:I230" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I5:I254" type="list">
       <formula1>설정!$C$10:$C$11</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J5:J230" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J5:J254" type="list">
       <formula1>설정!$E$10:$E$11</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L5:L230" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L5:L254" type="list">
       <formula1>설정!$D$10:$D$11</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="Q5:Q230" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="Q5:Q254" type="list">
       <formula1>"Y"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="날짜 형식으로 입력하세요 (예: 2026-09-30)" errorStyle="stop" errorTitle="일자" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B5:B230" type="date">
+    <dataValidation allowBlank="true" error="날짜 형식으로 입력하세요 (예: 2026-09-30)" errorStyle="stop" errorTitle="일자" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B5:B254" type="date">
       <formula1>36526</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -15861,46 +17565,46 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="28" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="29" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>3</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15908,17 +17612,17 @@
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
       <c r="G7" s="30" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="H7" s="30" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J7" s="30"/>
       <c r="K7" s="31" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16543,34 +18247,34 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="28" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="32" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C4" s="33" t="n">
         <v>1350</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="32" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="C5" s="34" t="n">
         <v>0.1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="15" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16578,16 +18282,16 @@
         <v>30</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16595,13 +18299,13 @@
         <v>4</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>16</v>
@@ -16612,13 +18316,13 @@
         <v>5</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" s="35" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>17</v>
@@ -16683,7 +18387,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
